--- a/outputs/forecast_income_by_tract.xlsx
+++ b/outputs/forecast_income_by_tract.xlsx
@@ -386,7 +386,7 @@
         <v>2024</v>
       </c>
       <c r="D2">
-        <v>180631.310591914</v>
+        <v>180631.3105919137</v>
       </c>
     </row>
     <row r="3">
@@ -412,7 +412,7 @@
         <v>2026</v>
       </c>
       <c r="D4">
-        <v>194584.458939971</v>
+        <v>209634.0531868873</v>
       </c>
     </row>
     <row r="5">
@@ -425,7 +425,7 @@
         <v>2027</v>
       </c>
       <c r="D5">
-        <v>209643.1204185263</v>
+        <v>225896.9803563379</v>
       </c>
     </row>
     <row r="6">
@@ -438,7 +438,7 @@
         <v>2028</v>
       </c>
       <c r="D6">
-        <v>225901.7396831354</v>
+        <v>243436.9339280337</v>
       </c>
     </row>
     <row r="7">
@@ -477,7 +477,7 @@
         <v>2026</v>
       </c>
       <c r="D9">
-        <v>75922.49023858304</v>
+        <v>79023.10551346494</v>
       </c>
     </row>
     <row r="10">
@@ -490,7 +490,7 @@
         <v>2027</v>
       </c>
       <c r="D10">
-        <v>79023.09380543733</v>
+        <v>82250.01235509907</v>
       </c>
     </row>
     <row r="11">
@@ -503,7 +503,7 @@
         <v>2028</v>
       </c>
       <c r="D11">
-        <v>82250.01185774468</v>
+        <v>85608.68831634402</v>
       </c>
     </row>
     <row r="12">
@@ -542,7 +542,7 @@
         <v>2026</v>
       </c>
       <c r="D14">
-        <v>63081.80764607847</v>
+        <v>64566.25838265953</v>
       </c>
     </row>
     <row r="15">
@@ -555,7 +555,7 @@
         <v>2027</v>
       </c>
       <c r="D15">
-        <v>64560.70453224726</v>
+        <v>66045.47383695377</v>
       </c>
     </row>
     <row r="16">
@@ -568,7 +568,7 @@
         <v>2028</v>
       </c>
       <c r="D16">
-        <v>66044.07724389592</v>
+        <v>67554.29249745322</v>
       </c>
     </row>
     <row r="17">
@@ -607,7 +607,7 @@
         <v>2026</v>
       </c>
       <c r="D19">
-        <v>69427.57915160312</v>
+        <v>74137.23130442682</v>
       </c>
     </row>
     <row r="20">
@@ -620,7 +620,7 @@
         <v>2027</v>
       </c>
       <c r="D20">
-        <v>74132.29063515601</v>
+        <v>79120.24207017527</v>
       </c>
     </row>
     <row r="21">
@@ -633,7 +633,7 @@
         <v>2028</v>
       </c>
       <c r="D21">
-        <v>79119.32417673593</v>
+        <v>84435.23889114471</v>
       </c>
     </row>
     <row r="22">
@@ -646,7 +646,7 @@
         <v>2024</v>
       </c>
       <c r="D22">
-        <v>141570.9757957378</v>
+        <v>141570.9757957373</v>
       </c>
     </row>
     <row r="23">
@@ -672,7 +672,7 @@
         <v>2026</v>
       </c>
       <c r="D24">
-        <v>148838.0584727518</v>
+        <v>157141.9407493962</v>
       </c>
     </row>
     <row r="25">
@@ -685,7 +685,7 @@
         <v>2027</v>
       </c>
       <c r="D25">
-        <v>156947.8621325962</v>
+        <v>165996.3160520391</v>
       </c>
     </row>
     <row r="26">
@@ -698,7 +698,7 @@
         <v>2028</v>
       </c>
       <c r="D26">
-        <v>166056.2181116225</v>
+        <v>175539.5035915257</v>
       </c>
     </row>
     <row r="27">
@@ -737,7 +737,7 @@
         <v>2026</v>
       </c>
       <c r="D29">
-        <v>64833.46340996962</v>
+        <v>66718.59116624978</v>
       </c>
     </row>
     <row r="30">
@@ -750,7 +750,7 @@
         <v>2027</v>
       </c>
       <c r="D30">
-        <v>66718.60241034372</v>
+        <v>68658.60777828885</v>
       </c>
     </row>
     <row r="31">
@@ -763,7 +763,7 @@
         <v>2028</v>
       </c>
       <c r="D31">
-        <v>68658.61102043085</v>
+        <v>70655.04542968259</v>
       </c>
     </row>
     <row r="32">
@@ -776,7 +776,7 @@
         <v>2024</v>
       </c>
       <c r="D32">
-        <v>53471.59844402014</v>
+        <v>53471.59844402005</v>
       </c>
     </row>
     <row r="33">
@@ -802,7 +802,7 @@
         <v>2026</v>
       </c>
       <c r="D34">
-        <v>54230.01355761635</v>
+        <v>55011.60176563617</v>
       </c>
     </row>
     <row r="35">
@@ -815,7 +815,7 @@
         <v>2027</v>
       </c>
       <c r="D35">
-        <v>55013.60074130591</v>
+        <v>55823.13743258743</v>
       </c>
     </row>
     <row r="36">
@@ -828,7 +828,7 @@
         <v>2028</v>
       </c>
       <c r="D36">
-        <v>55823.46396485809</v>
+        <v>56647.63899406238</v>
       </c>
     </row>
     <row r="37">
@@ -867,7 +867,7 @@
         <v>2026</v>
       </c>
       <c r="D39">
-        <v>162346.8715726701</v>
+        <v>169989.4263244495</v>
       </c>
     </row>
     <row r="40">
@@ -880,7 +880,7 @@
         <v>2027</v>
       </c>
       <c r="D40">
-        <v>165933.0847696933</v>
+        <v>169648.7532410552</v>
       </c>
     </row>
     <row r="41">
@@ -893,7 +893,7 @@
         <v>2028</v>
       </c>
       <c r="D41">
-        <v>173745.0855394711</v>
+        <v>181871.6500739449</v>
       </c>
     </row>
     <row r="42">
@@ -932,7 +932,7 @@
         <v>2026</v>
       </c>
       <c r="D44">
-        <v>73900.53114791015</v>
+        <v>75917.83263962164</v>
       </c>
     </row>
     <row r="45">
@@ -945,7 +945,7 @@
         <v>2027</v>
       </c>
       <c r="D45">
-        <v>75928.57885884255</v>
+        <v>77981.56206676856</v>
       </c>
     </row>
     <row r="46">
@@ -958,7 +958,7 @@
         <v>2028</v>
       </c>
       <c r="D46">
-        <v>77978.64420367977</v>
+        <v>80092.40013757529</v>
       </c>
     </row>
     <row r="47">
@@ -971,7 +971,7 @@
         <v>2024</v>
       </c>
       <c r="D47">
-        <v>62579.39029577826</v>
+        <v>62579.39029577804</v>
       </c>
     </row>
     <row r="48">
@@ -997,7 +997,7 @@
         <v>2026</v>
       </c>
       <c r="D49">
-        <v>66901.56198188622</v>
+        <v>71522.15216278625</v>
       </c>
     </row>
     <row r="50">
@@ -1010,7 +1010,7 @@
         <v>2027</v>
       </c>
       <c r="D50">
-        <v>71522.15288627948</v>
+        <v>76461.7600821864</v>
       </c>
     </row>
     <row r="51">
@@ -1023,7 +1023,7 @@
         <v>2028</v>
       </c>
       <c r="D51">
-        <v>76461.76007664591</v>
+        <v>81742.51720345898</v>
       </c>
     </row>
     <row r="52">
@@ -1036,7 +1036,7 @@
         <v>2024</v>
       </c>
       <c r="D52">
-        <v>96423.87928312928</v>
+        <v>96423.87928312911</v>
       </c>
     </row>
     <row r="53">
@@ -1062,7 +1062,7 @@
         <v>2026</v>
       </c>
       <c r="D54">
-        <v>102568.4871927674</v>
+        <v>108989.5305832137</v>
       </c>
     </row>
     <row r="55">
@@ -1075,7 +1075,7 @@
         <v>2027</v>
       </c>
       <c r="D55">
-        <v>109004.8988029844</v>
+        <v>115739.2857399791</v>
       </c>
     </row>
     <row r="56">
@@ -1088,7 +1088,7 @@
         <v>2028</v>
       </c>
       <c r="D56">
-        <v>115737.1064210358</v>
+        <v>122900.1125862091</v>
       </c>
     </row>
     <row r="57">
@@ -1127,7 +1127,7 @@
         <v>2026</v>
       </c>
       <c r="D59">
-        <v>48386.76264280629</v>
+        <v>49982.67958377033</v>
       </c>
     </row>
     <row r="60">
@@ -1140,7 +1140,7 @@
         <v>2027</v>
       </c>
       <c r="D60">
-        <v>50156.25135691225</v>
+        <v>51799.72252131449</v>
       </c>
     </row>
     <row r="61">
@@ -1153,7 +1153,7 @@
         <v>2028</v>
       </c>
       <c r="D61">
-        <v>51712.63355132396</v>
+        <v>53412.51134975319</v>
       </c>
     </row>
     <row r="62">
@@ -1192,7 +1192,7 @@
         <v>2026</v>
       </c>
       <c r="D64">
-        <v>65711.96656458701</v>
+        <v>71047.23125773195</v>
       </c>
     </row>
     <row r="65">
@@ -1205,7 +1205,7 @@
         <v>2027</v>
       </c>
       <c r="D65">
-        <v>71029.35886224163</v>
+        <v>76869.12083544086</v>
       </c>
     </row>
     <row r="66">
@@ -1218,7 +1218,7 @@
         <v>2028</v>
       </c>
       <c r="D66">
-        <v>76872.47579405272</v>
+        <v>83178.96905088762</v>
       </c>
     </row>
     <row r="67">
@@ -1257,7 +1257,7 @@
         <v>2026</v>
       </c>
       <c r="D69">
-        <v>74834.84446433853</v>
+        <v>78077.78741131301</v>
       </c>
     </row>
     <row r="70">
@@ -1270,7 +1270,7 @@
         <v>2027</v>
       </c>
       <c r="D70">
-        <v>76890.5071713236</v>
+        <v>79461.30449906683</v>
       </c>
     </row>
     <row r="71">
@@ -1283,7 +1283,7 @@
         <v>2028</v>
       </c>
       <c r="D71">
-        <v>80349.97161419904</v>
+        <v>83613.03635284601</v>
       </c>
     </row>
     <row r="72">
@@ -1322,7 +1322,7 @@
         <v>2026</v>
       </c>
       <c r="D74">
-        <v>46980.73948585224</v>
+        <v>48761.61492305171</v>
       </c>
     </row>
     <row r="75">
@@ -1335,7 +1335,7 @@
         <v>2027</v>
       </c>
       <c r="D75">
-        <v>48360.56246622763</v>
+        <v>50130.90098172462</v>
       </c>
     </row>
     <row r="76">
@@ -1348,7 +1348,7 @@
         <v>2028</v>
       </c>
       <c r="D76">
-        <v>50355.40086682154</v>
+        <v>52234.15606908246</v>
       </c>
     </row>
     <row r="77">
@@ -1361,7 +1361,7 @@
         <v>2024</v>
       </c>
       <c r="D77">
-        <v>80359.89986140917</v>
+        <v>80359.89986140888</v>
       </c>
     </row>
     <row r="78">
@@ -1387,7 +1387,7 @@
         <v>2026</v>
       </c>
       <c r="D79">
-        <v>83873.58059209104</v>
+        <v>87553.51476593524</v>
       </c>
     </row>
     <row r="80">
@@ -1400,7 +1400,7 @@
         <v>2027</v>
       </c>
       <c r="D80">
-        <v>87551.93455727307</v>
+        <v>91403.13177087497</v>
       </c>
     </row>
     <row r="81">
@@ -1413,7 +1413,7 @@
         <v>2028</v>
       </c>
       <c r="D81">
-        <v>91403.33832185523</v>
+        <v>95422.65845302044</v>
       </c>
     </row>
     <row r="82">
@@ -1426,7 +1426,7 @@
         <v>2024</v>
       </c>
       <c r="D82">
-        <v>101553.7334083988</v>
+        <v>101553.7334083984</v>
       </c>
     </row>
     <row r="83">
@@ -1452,7 +1452,7 @@
         <v>2026</v>
       </c>
       <c r="D84">
-        <v>107190.1495244338</v>
+        <v>113139.218215202</v>
       </c>
     </row>
     <row r="85">
@@ -1465,7 +1465,7 @@
         <v>2027</v>
       </c>
       <c r="D85">
-        <v>113139.2170438433</v>
+        <v>119418.2687172397</v>
       </c>
     </row>
     <row r="86">
@@ -1478,7 +1478,7 @@
         <v>2028</v>
       </c>
       <c r="D86">
-        <v>119418.2687091368</v>
+        <v>126045.7967227122</v>
       </c>
     </row>
     <row r="87">
@@ -1517,7 +1517,7 @@
         <v>2026</v>
       </c>
       <c r="D89">
-        <v>57377.93260153921</v>
+        <v>59531.20840320837</v>
       </c>
     </row>
     <row r="90">
@@ -1530,7 +1530,7 @@
         <v>2027</v>
       </c>
       <c r="D90">
-        <v>59886.94699559936</v>
+        <v>62071.89883176652</v>
       </c>
     </row>
     <row r="91">
@@ -1543,7 +1543,7 @@
         <v>2028</v>
       </c>
       <c r="D91">
-        <v>61901.62135016734</v>
+        <v>64189.84749292435</v>
       </c>
     </row>
     <row r="92">
@@ -1556,7 +1556,7 @@
         <v>2024</v>
       </c>
       <c r="D92">
-        <v>88500.97404403283</v>
+        <v>88500.97404403267</v>
       </c>
     </row>
     <row r="93">
@@ -1582,7 +1582,7 @@
         <v>2026</v>
       </c>
       <c r="D94">
-        <v>93896.95560503648</v>
+        <v>99623.4289993564</v>
       </c>
     </row>
     <row r="95">
@@ -1595,7 +1595,7 @@
         <v>2027</v>
       </c>
       <c r="D95">
-        <v>99623.87180633243</v>
+        <v>105702.1363351268</v>
       </c>
     </row>
     <row r="96">
@@ -1608,7 +1608,7 @@
         <v>2028</v>
       </c>
       <c r="D96">
-        <v>105702.275572961</v>
+        <v>112152.1904164699</v>
       </c>
     </row>
     <row r="97">
@@ -1621,7 +1621,7 @@
         <v>2024</v>
       </c>
       <c r="D97">
-        <v>69997.81792670018</v>
+        <v>69997.81792670005</v>
       </c>
     </row>
     <row r="98">
@@ -1647,7 +1647,7 @@
         <v>2026</v>
       </c>
       <c r="D99">
-        <v>66933.14128297378</v>
+        <v>64729.43886926753</v>
       </c>
     </row>
     <row r="100">
@@ -1660,7 +1660,7 @@
         <v>2027</v>
       </c>
       <c r="D100">
-        <v>66009.78879540254</v>
+        <v>67140.70673726891</v>
       </c>
     </row>
     <row r="101">
@@ -1673,7 +1673,7 @@
         <v>2028</v>
       </c>
       <c r="D101">
-        <v>67601.17296659207</v>
+        <v>71084.50509293495</v>
       </c>
     </row>
     <row r="102">
@@ -1712,7 +1712,7 @@
         <v>2026</v>
       </c>
       <c r="D104">
-        <v>132395.6635524695</v>
+        <v>138530.2199009507</v>
       </c>
     </row>
     <row r="105">
@@ -1725,7 +1725,7 @@
         <v>2027</v>
       </c>
       <c r="D105">
-        <v>138453.8751889353</v>
+        <v>144984.0078550536</v>
       </c>
     </row>
     <row r="106">
@@ -1738,7 +1738,7 @@
         <v>2028</v>
       </c>
       <c r="D106">
-        <v>145007.2581051264</v>
+        <v>151811.4741597728</v>
       </c>
     </row>
     <row r="107">
@@ -1751,7 +1751,7 @@
         <v>2024</v>
       </c>
       <c r="D107">
-        <v>41464.35542608402</v>
+        <v>41464.35542608394</v>
       </c>
     </row>
     <row r="108">
@@ -1777,7 +1777,7 @@
         <v>2026</v>
       </c>
       <c r="D109">
-        <v>46669.76116937702</v>
+        <v>48812.93235606001</v>
       </c>
     </row>
     <row r="110">
@@ -1790,7 +1790,7 @@
         <v>2027</v>
       </c>
       <c r="D110">
-        <v>51250.98792641859</v>
+        <v>54912.96671763246</v>
       </c>
     </row>
     <row r="111">
@@ -1803,7 +1803,7 @@
         <v>2028</v>
       </c>
       <c r="D111">
-        <v>53163.3340043929</v>
+        <v>56056.60878208934</v>
       </c>
     </row>
     <row r="112">
@@ -1816,7 +1816,7 @@
         <v>2024</v>
       </c>
       <c r="D112">
-        <v>70928.73265930376</v>
+        <v>70928.73265930363</v>
       </c>
     </row>
     <row r="113">
@@ -1842,7 +1842,7 @@
         <v>2026</v>
       </c>
       <c r="D114">
-        <v>74605.36750732413</v>
+        <v>76366.27541509739</v>
       </c>
     </row>
     <row r="115">
@@ -1855,7 +1855,7 @@
         <v>2027</v>
       </c>
       <c r="D115">
-        <v>77688.34977569766</v>
+        <v>80090.25329734047</v>
       </c>
     </row>
     <row r="116">
@@ -1868,7 +1868,7 @@
         <v>2028</v>
       </c>
       <c r="D116">
-        <v>79227.72070202135</v>
+        <v>81311.16978922303</v>
       </c>
     </row>
     <row r="117">
@@ -1881,7 +1881,7 @@
         <v>2024</v>
       </c>
       <c r="D117">
-        <v>98336.21700355185</v>
+        <v>98336.21700355168</v>
       </c>
     </row>
     <row r="118">
@@ -1907,7 +1907,7 @@
         <v>2026</v>
       </c>
       <c r="D119">
-        <v>98764.89464371858</v>
+        <v>99697.98950728023</v>
       </c>
     </row>
     <row r="120">
@@ -1920,7 +1920,7 @@
         <v>2027</v>
       </c>
       <c r="D120">
-        <v>99509.55530570334</v>
+        <v>100577.3153103183</v>
       </c>
     </row>
     <row r="121">
@@ -1933,7 +1933,7 @@
         <v>2028</v>
       </c>
       <c r="D121">
-        <v>100648.5732953477</v>
+        <v>101680.2089221248</v>
       </c>
     </row>
     <row r="122">
@@ -1946,7 +1946,7 @@
         <v>2024</v>
       </c>
       <c r="D122">
-        <v>54435.2500616707</v>
+        <v>54435.25006167061</v>
       </c>
     </row>
     <row r="123">
@@ -1972,7 +1972,7 @@
         <v>2026</v>
       </c>
       <c r="D124">
-        <v>56054.98758927135</v>
+        <v>57720.76189398599</v>
       </c>
     </row>
     <row r="125">
@@ -1985,7 +1985,7 @@
         <v>2027</v>
       </c>
       <c r="D125">
-        <v>57720.93126842501</v>
+        <v>59434.3377848151</v>
       </c>
     </row>
     <row r="126">
@@ -1998,7 +1998,7 @@
         <v>2028</v>
       </c>
       <c r="D126">
-        <v>59434.32410269188</v>
+        <v>61198.74292103395</v>
       </c>
     </row>
     <row r="127">
@@ -2011,7 +2011,7 @@
         <v>2024</v>
       </c>
       <c r="D127">
-        <v>45713.06227824729</v>
+        <v>45713.0622782472</v>
       </c>
     </row>
     <row r="128">
@@ -2037,7 +2037,7 @@
         <v>2026</v>
       </c>
       <c r="D129">
-        <v>47492.99769453985</v>
+        <v>48650.00606006431</v>
       </c>
     </row>
     <row r="130">
@@ -2050,7 +2050,7 @@
         <v>2027</v>
       </c>
       <c r="D130">
-        <v>49214.2130313915</v>
+        <v>50865.48644548649</v>
       </c>
     </row>
     <row r="131">
@@ -2063,7 +2063,7 @@
         <v>2028</v>
       </c>
       <c r="D131">
-        <v>50389.07470248699</v>
+        <v>51701.48882819166</v>
       </c>
     </row>
     <row r="132">
@@ -2076,7 +2076,7 @@
         <v>2024</v>
       </c>
       <c r="D132">
-        <v>80022.35022501578</v>
+        <v>80022.35022501592</v>
       </c>
     </row>
     <row r="133">
@@ -2102,7 +2102,7 @@
         <v>2026</v>
       </c>
       <c r="D134">
-        <v>93355.67059618354</v>
+        <v>108900.0857110127</v>
       </c>
     </row>
     <row r="135">
@@ -2115,7 +2115,7 @@
         <v>2027</v>
       </c>
       <c r="D135">
-        <v>108900.5054450135</v>
+        <v>127021.9805028134</v>
       </c>
     </row>
     <row r="136">
@@ -2128,7 +2128,7 @@
         <v>2028</v>
       </c>
       <c r="D136">
-        <v>127021.9609357434</v>
+        <v>148159.4433022813</v>
       </c>
     </row>
     <row r="137">
@@ -2167,7 +2167,7 @@
         <v>2026</v>
       </c>
       <c r="D139">
-        <v>47550.10209573113</v>
+        <v>50867.25212818594</v>
       </c>
     </row>
     <row r="140">
@@ -2180,7 +2180,7 @@
         <v>2027</v>
       </c>
       <c r="D140">
-        <v>50865.21923584013</v>
+        <v>54420.0688223551</v>
       </c>
     </row>
     <row r="141">
@@ -2193,7 +2193,7 @@
         <v>2028</v>
       </c>
       <c r="D141">
-        <v>54420.5074889553</v>
+        <v>58222.43946937784</v>
       </c>
     </row>
     <row r="142">
@@ -2206,7 +2206,7 @@
         <v>2024</v>
       </c>
       <c r="D142">
-        <v>89497.56693402561</v>
+        <v>89497.56693402529</v>
       </c>
     </row>
     <row r="143">
@@ -2232,7 +2232,7 @@
         <v>2026</v>
       </c>
       <c r="D144">
-        <v>91429.67724636366</v>
+        <v>94370.37761460713</v>
       </c>
     </row>
     <row r="145">
@@ -2245,7 +2245,7 @@
         <v>2027</v>
       </c>
       <c r="D145">
-        <v>93941.97205484469</v>
+        <v>97079.75845467858</v>
       </c>
     </row>
     <row r="146">
@@ -2258,7 +2258,7 @@
         <v>2028</v>
       </c>
       <c r="D146">
-        <v>97275.1063008343</v>
+        <v>100471.0086530499</v>
       </c>
     </row>
     <row r="147">
@@ -2297,7 +2297,7 @@
         <v>2026</v>
       </c>
       <c r="D149">
-        <v>65885.38564176088</v>
+        <v>68839.26138132795</v>
       </c>
     </row>
     <row r="150">
@@ -2310,7 +2310,7 @@
         <v>2027</v>
       </c>
       <c r="D150">
-        <v>68760.9647134016</v>
+        <v>71457.23344435367</v>
       </c>
     </row>
     <row r="151">
@@ -2323,7 +2323,7 @@
         <v>2028</v>
       </c>
       <c r="D151">
-        <v>71427.56433717175</v>
+        <v>74082.41362032449</v>
       </c>
     </row>
     <row r="152">
@@ -2336,7 +2336,7 @@
         <v>2024</v>
       </c>
       <c r="D152">
-        <v>126520.4340075858</v>
+        <v>126520.4340075853</v>
       </c>
     </row>
     <row r="153">
@@ -2362,7 +2362,7 @@
         <v>2026</v>
       </c>
       <c r="D154">
-        <v>133685.859527305</v>
+        <v>141257.0955865994</v>
       </c>
     </row>
     <row r="155">
@@ -2375,7 +2375,7 @@
         <v>2027</v>
       </c>
       <c r="D155">
-        <v>141257.0955851225</v>
+        <v>149257.1250730488</v>
       </c>
     </row>
     <row r="156">
@@ -2388,7 +2388,7 @@
         <v>2028</v>
       </c>
       <c r="D156">
-        <v>149257.1250731562</v>
+        <v>157710.2324850102</v>
       </c>
     </row>
     <row r="157">
@@ -2401,7 +2401,7 @@
         <v>2024</v>
       </c>
       <c r="D157">
-        <v>139730.3776346512</v>
+        <v>139730.3776346507</v>
       </c>
     </row>
     <row r="158">
@@ -2427,7 +2427,7 @@
         <v>2026</v>
       </c>
       <c r="D159">
-        <v>148183.7902449993</v>
+        <v>158037.5626344932</v>
       </c>
     </row>
     <row r="160">
@@ -2440,7 +2440,7 @@
         <v>2027</v>
       </c>
       <c r="D160">
-        <v>157441.0040379074</v>
+        <v>167587.7568258792</v>
       </c>
     </row>
     <row r="161">
@@ -2453,7 +2453,7 @@
         <v>2028</v>
       </c>
       <c r="D161">
-        <v>168013.2393064467</v>
+        <v>179072.0908072399</v>
       </c>
     </row>
     <row r="162">
@@ -2466,7 +2466,7 @@
         <v>2024</v>
       </c>
       <c r="D162">
-        <v>78023.85050001738</v>
+        <v>78023.85050001724</v>
       </c>
     </row>
     <row r="163">
@@ -2492,7 +2492,7 @@
         <v>2026</v>
       </c>
       <c r="D164">
-        <v>82049.91168483184</v>
+        <v>86475.40122568439</v>
       </c>
     </row>
     <row r="165">
@@ -2505,7 +2505,7 @@
         <v>2027</v>
       </c>
       <c r="D165">
-        <v>86438.38802234153</v>
+        <v>91224.81742104013</v>
       </c>
     </row>
     <row r="166">
@@ -2518,7 +2518,7 @@
         <v>2028</v>
       </c>
       <c r="D166">
-        <v>91232.35226831287</v>
+        <v>96258.92983491058</v>
       </c>
     </row>
     <row r="167">
@@ -2531,7 +2531,7 @@
         <v>2024</v>
       </c>
       <c r="D167">
-        <v>81347.57592353952</v>
+        <v>81347.57592353967</v>
       </c>
     </row>
     <row r="168">
@@ -2557,7 +2557,7 @@
         <v>2026</v>
       </c>
       <c r="D169">
-        <v>88302.41468495964</v>
+        <v>95887.13081248093</v>
       </c>
     </row>
     <row r="170">
@@ -2570,7 +2570,7 @@
         <v>2027</v>
       </c>
       <c r="D170">
-        <v>95882.22873127637</v>
+        <v>104145.6746857514</v>
       </c>
     </row>
     <row r="171">
@@ -2583,7 +2583,7 @@
         <v>2028</v>
       </c>
       <c r="D171">
-        <v>104146.4145760776</v>
+        <v>113117.9193142829</v>
       </c>
     </row>
     <row r="172">
@@ -2596,7 +2596,7 @@
         <v>2024</v>
       </c>
       <c r="D172">
-        <v>88045.46448533403</v>
+        <v>88045.46448533388</v>
       </c>
     </row>
     <row r="173">
@@ -2622,7 +2622,7 @@
         <v>2026</v>
       </c>
       <c r="D174">
-        <v>96347.2212540991</v>
+        <v>103986.6065095554</v>
       </c>
     </row>
     <row r="175">
@@ -2635,7 +2635,7 @@
         <v>2027</v>
       </c>
       <c r="D175">
-        <v>104866.9644804444</v>
+        <v>113528.6565443515</v>
       </c>
     </row>
     <row r="176">
@@ -2648,7 +2648,7 @@
         <v>2028</v>
       </c>
       <c r="D176">
-        <v>112945.5394220875</v>
+        <v>122046.224052566</v>
       </c>
     </row>
     <row r="177">
@@ -2661,7 +2661,7 @@
         <v>2024</v>
       </c>
       <c r="D177">
-        <v>70416.75531365995</v>
+        <v>70416.75531365981</v>
       </c>
     </row>
     <row r="178">
@@ -2687,7 +2687,7 @@
         <v>2026</v>
       </c>
       <c r="D179">
-        <v>73342.22935530845</v>
+        <v>76167.19234271438</v>
       </c>
     </row>
     <row r="180">
@@ -2700,7 +2700,7 @@
         <v>2027</v>
       </c>
       <c r="D180">
-        <v>76261.35098933089</v>
+        <v>79163.89841726338</v>
       </c>
     </row>
     <row r="181">
@@ -2713,7 +2713,7 @@
         <v>2028</v>
       </c>
       <c r="D181">
-        <v>79122.40204484221</v>
+        <v>82149.18708800731</v>
       </c>
     </row>
     <row r="182">
@@ -2726,7 +2726,7 @@
         <v>2024</v>
       </c>
       <c r="D182">
-        <v>136485.240273463</v>
+        <v>136485.2402734627</v>
       </c>
     </row>
     <row r="183">
@@ -2752,7 +2752,7 @@
         <v>2026</v>
       </c>
       <c r="D184">
-        <v>147828.0410316904</v>
+        <v>160100.5898754313</v>
       </c>
     </row>
     <row r="185">
@@ -2765,7 +2765,7 @@
         <v>2027</v>
       </c>
       <c r="D185">
-        <v>160098.9889788739</v>
+        <v>173372.8112284421</v>
       </c>
     </row>
     <row r="186">
@@ -2778,7 +2778,7 @@
         <v>2028</v>
       </c>
       <c r="D186">
-        <v>173372.5962686347</v>
+        <v>187744.5916484166</v>
       </c>
     </row>
     <row r="187">
@@ -2791,7 +2791,7 @@
         <v>2024</v>
       </c>
       <c r="D187">
-        <v>206453.2746910729</v>
+        <v>206453.2746910722</v>
       </c>
     </row>
     <row r="188">
@@ -2817,7 +2817,7 @@
         <v>2026</v>
       </c>
       <c r="D189">
-        <v>220077.87710413</v>
+        <v>234593.803697442</v>
       </c>
     </row>
     <row r="190">
@@ -2830,7 +2830,7 @@
         <v>2027</v>
       </c>
       <c r="D190">
-        <v>234593.1401764006</v>
+        <v>250056.7240459544</v>
       </c>
     </row>
     <row r="191">
@@ -2843,7 +2843,7 @@
         <v>2028</v>
       </c>
       <c r="D191">
-        <v>250056.6639799782</v>
+        <v>266538.6689477334</v>
       </c>
     </row>
     <row r="192">
@@ -2856,7 +2856,7 @@
         <v>2024</v>
       </c>
       <c r="D192">
-        <v>93438.75055404611</v>
+        <v>93438.75055404594</v>
       </c>
     </row>
     <row r="193">
@@ -2882,7 +2882,7 @@
         <v>2026</v>
       </c>
       <c r="D194">
-        <v>100535.7296192005</v>
+        <v>108175.5090838619</v>
       </c>
     </row>
     <row r="195">
@@ -2895,7 +2895,7 @@
         <v>2027</v>
       </c>
       <c r="D195">
-        <v>108175.2564200968</v>
+        <v>116399.0726317403</v>
       </c>
     </row>
     <row r="196">
@@ -2908,7 +2908,7 @@
         <v>2028</v>
       </c>
       <c r="D196">
-        <v>116399.0908928552</v>
+        <v>125247.8550922023</v>
       </c>
     </row>
     <row r="197">
@@ -2921,7 +2921,7 @@
         <v>2024</v>
       </c>
       <c r="D197">
-        <v>51216.42447863521</v>
+        <v>51216.42447863511</v>
       </c>
     </row>
     <row r="198">
@@ -2947,7 +2947,7 @@
         <v>2026</v>
       </c>
       <c r="D199">
-        <v>53012.33748395213</v>
+        <v>54859.17702623415</v>
       </c>
     </row>
     <row r="200">
@@ -2960,7 +2960,7 @@
         <v>2027</v>
       </c>
       <c r="D200">
-        <v>54856.48277997632</v>
+        <v>56749.53009574254</v>
       </c>
     </row>
     <row r="201">
@@ -2973,7 +2973,7 @@
         <v>2028</v>
       </c>
       <c r="D201">
-        <v>56748.90670794659</v>
+        <v>58703.08690230554</v>
       </c>
     </row>
     <row r="202">
@@ -3012,7 +3012,7 @@
         <v>2026</v>
       </c>
       <c r="D204">
-        <v>46925.26513328946</v>
+        <v>48348.39595142091</v>
       </c>
     </row>
     <row r="205">
@@ -3025,7 +3025,7 @@
         <v>2027</v>
       </c>
       <c r="D205">
-        <v>48353.05091246446</v>
+        <v>49795.47622051091</v>
       </c>
     </row>
     <row r="206">
@@ -3038,7 +3038,7 @@
         <v>2028</v>
       </c>
       <c r="D206">
-        <v>49794.7919877335</v>
+        <v>51283.75387742559</v>
       </c>
     </row>
     <row r="207">
@@ -3051,7 +3051,7 @@
         <v>2024</v>
       </c>
       <c r="D207">
-        <v>84658.74517103648</v>
+        <v>84658.74517103677</v>
       </c>
     </row>
     <row r="208">
@@ -3077,7 +3077,7 @@
         <v>2026</v>
       </c>
       <c r="D209">
-        <v>92441.82444912569</v>
+        <v>100941.6610038935</v>
       </c>
     </row>
     <row r="210">
@@ -3090,7 +3090,7 @@
         <v>2027</v>
       </c>
       <c r="D210">
-        <v>100941.7212783822</v>
+        <v>110224.5719051365</v>
       </c>
     </row>
     <row r="211">
@@ -3103,7 +3103,7 @@
         <v>2028</v>
       </c>
       <c r="D211">
-        <v>110224.5751516667</v>
+        <v>120361.1789659789</v>
       </c>
     </row>
     <row r="212">
@@ -3116,7 +3116,7 @@
         <v>2024</v>
       </c>
       <c r="D212">
-        <v>110648.2893827888</v>
+        <v>110648.2893827884</v>
       </c>
     </row>
     <row r="213">
@@ -3142,7 +3142,7 @@
         <v>2026</v>
       </c>
       <c r="D214">
-        <v>119634.7506938049</v>
+        <v>129349.6695354323</v>
       </c>
     </row>
     <row r="215">
@@ -3155,7 +3155,7 @@
         <v>2027</v>
       </c>
       <c r="D215">
-        <v>129349.7065169558</v>
+        <v>139852.1027061494</v>
       </c>
     </row>
     <row r="216">
@@ -3168,7 +3168,7 @@
         <v>2028</v>
       </c>
       <c r="D216">
-        <v>139852.1016430811</v>
+        <v>151207.2682950051</v>
       </c>
     </row>
     <row r="217">
@@ -3181,7 +3181,7 @@
         <v>2024</v>
       </c>
       <c r="D217">
-        <v>99207.61895840814</v>
+        <v>99207.61895840832</v>
       </c>
     </row>
     <row r="218">
@@ -3207,7 +3207,7 @@
         <v>2026</v>
       </c>
       <c r="D219">
-        <v>105523.3863251596</v>
+        <v>112207.9494158141</v>
       </c>
     </row>
     <row r="220">
@@ -3220,7 +3220,7 @@
         <v>2027</v>
       </c>
       <c r="D220">
-        <v>112200.2374647922</v>
+        <v>119255.9883054145</v>
       </c>
     </row>
     <row r="221">
@@ -3233,7 +3233,7 @@
         <v>2028</v>
       </c>
       <c r="D221">
-        <v>119254.0885391844</v>
+        <v>126740.673509057</v>
       </c>
     </row>
     <row r="222">
@@ -3246,7 +3246,7 @@
         <v>2024</v>
       </c>
       <c r="D222">
-        <v>143689.828066096</v>
+        <v>143689.8280660955</v>
       </c>
     </row>
     <row r="223">
@@ -3272,7 +3272,7 @@
         <v>2026</v>
       </c>
       <c r="D224">
-        <v>148374.9516073829</v>
+        <v>153122.7453094256</v>
       </c>
     </row>
     <row r="225">
@@ -3285,7 +3285,7 @@
         <v>2027</v>
       </c>
       <c r="D225">
-        <v>153105.5695530825</v>
+        <v>157876.4027682126</v>
       </c>
     </row>
     <row r="226">
@@ -3298,7 +3298,7 @@
         <v>2028</v>
       </c>
       <c r="D226">
-        <v>157873.025275961</v>
+        <v>162767.1895243743</v>
       </c>
     </row>
     <row r="227">
@@ -3337,7 +3337,7 @@
         <v>2026</v>
       </c>
       <c r="D229">
-        <v>123695.7143744277</v>
+        <v>131117.5495435575</v>
       </c>
     </row>
     <row r="230">
@@ -3350,7 +3350,7 @@
         <v>2027</v>
       </c>
       <c r="D230">
-        <v>131122.8828755282</v>
+        <v>138976.2403865086</v>
       </c>
     </row>
     <row r="231">
@@ -3363,7 +3363,7 @@
         <v>2028</v>
       </c>
       <c r="D231">
-        <v>138974.9832288119</v>
+        <v>147301.954000773</v>
       </c>
     </row>
     <row r="232">
@@ -3376,7 +3376,7 @@
         <v>2024</v>
       </c>
       <c r="D232">
-        <v>77229.38449029952</v>
+        <v>77229.38449029966</v>
       </c>
     </row>
     <row r="233">
@@ -3402,7 +3402,7 @@
         <v>2026</v>
       </c>
       <c r="D234">
-        <v>79678.52343591864</v>
+        <v>82208.52567836414</v>
       </c>
     </row>
     <row r="235">
@@ -3415,7 +3415,7 @@
         <v>2027</v>
       </c>
       <c r="D235">
-        <v>82208.19947318611</v>
+        <v>84821.14889452262</v>
       </c>
     </row>
     <row r="236">
@@ -3428,7 +3428,7 @@
         <v>2028</v>
       </c>
       <c r="D236">
-        <v>84821.18325850606</v>
+        <v>87516.90879747132</v>
       </c>
     </row>
     <row r="237">
@@ -3441,7 +3441,7 @@
         <v>2024</v>
       </c>
       <c r="D237">
-        <v>62972.01550772815</v>
+        <v>62972.01550772804</v>
       </c>
     </row>
     <row r="238">
@@ -3467,7 +3467,7 @@
         <v>2026</v>
       </c>
       <c r="D239">
-        <v>64725.01075905011</v>
+        <v>67997.2475466288</v>
       </c>
     </row>
     <row r="240">
@@ -3480,7 +3480,7 @@
         <v>2027</v>
       </c>
       <c r="D240">
-        <v>66817.49176639583</v>
+        <v>69279.01531195869</v>
       </c>
     </row>
     <row r="241">
@@ -3493,7 +3493,7 @@
         <v>2028</v>
       </c>
       <c r="D241">
-        <v>70256.57712846673</v>
+        <v>73615.27222142412</v>
       </c>
     </row>
     <row r="242">
@@ -3506,7 +3506,7 @@
         <v>2024</v>
       </c>
       <c r="D242">
-        <v>139421.9842386941</v>
+        <v>139421.9842386936</v>
       </c>
     </row>
     <row r="243">
@@ -3532,7 +3532,7 @@
         <v>2026</v>
       </c>
       <c r="D244">
-        <v>165361.3639302549</v>
+        <v>193780.9464141249</v>
       </c>
     </row>
     <row r="245">
@@ -3545,7 +3545,7 @@
         <v>2027</v>
       </c>
       <c r="D245">
-        <v>192560.4804265082</v>
+        <v>220156.0397521288</v>
       </c>
     </row>
     <row r="246">
@@ -3558,7 +3558,7 @@
         <v>2028</v>
       </c>
       <c r="D246">
-        <v>219426.8895670047</v>
+        <v>247644.0305152434</v>
       </c>
     </row>
     <row r="247">
@@ -3571,7 +3571,7 @@
         <v>2024</v>
       </c>
       <c r="D247">
-        <v>143253.5474316489</v>
+        <v>143253.5474316487</v>
       </c>
     </row>
     <row r="248">
@@ -3597,7 +3597,7 @@
         <v>2026</v>
       </c>
       <c r="D249">
-        <v>149158.9225661789</v>
+        <v>155389.5919722116</v>
       </c>
     </row>
     <row r="250">
@@ -3610,7 +3610,7 @@
         <v>2027</v>
       </c>
       <c r="D250">
-        <v>155402.6757795763</v>
+        <v>162006.7648536305</v>
       </c>
     </row>
     <row r="251">
@@ -3623,7 +3623,7 @@
         <v>2028</v>
       </c>
       <c r="D251">
-        <v>162008.9444854197</v>
+        <v>168912.5435284626</v>
       </c>
     </row>
     <row r="252">
@@ -3662,7 +3662,7 @@
         <v>2026</v>
       </c>
       <c r="D254">
-        <v>158381.7114797411</v>
+        <v>166443.8765049473</v>
       </c>
     </row>
     <row r="255">
@@ -3675,7 +3675,7 @@
         <v>2027</v>
       </c>
       <c r="D255">
-        <v>166466.6254168974</v>
+        <v>174857.8391672378</v>
       </c>
     </row>
     <row r="256">
@@ -3688,7 +3688,7 @@
         <v>2028</v>
       </c>
       <c r="D256">
-        <v>174853.455604894</v>
+        <v>183683.3238755737</v>
       </c>
     </row>
     <row r="257">
@@ -3701,7 +3701,7 @@
         <v>2024</v>
       </c>
       <c r="D257">
-        <v>62734.76880616621</v>
+        <v>62734.7688061661</v>
       </c>
     </row>
     <row r="258">
@@ -3727,7 +3727,7 @@
         <v>2026</v>
       </c>
       <c r="D259">
-        <v>66249.12478619959</v>
+        <v>69979.29804844533</v>
       </c>
     </row>
     <row r="260">
@@ -3740,7 +3740,7 @@
         <v>2027</v>
       </c>
       <c r="D260">
-        <v>69971.13475482978</v>
+        <v>73913.64463846385</v>
       </c>
     </row>
     <row r="261">
@@ -3753,7 +3753,7 @@
         <v>2028</v>
       </c>
       <c r="D261">
-        <v>73917.35981741075</v>
+        <v>78080.95915189323</v>
       </c>
     </row>
     <row r="262">
@@ -3766,7 +3766,7 @@
         <v>2024</v>
       </c>
       <c r="D262">
-        <v>125065.0309886162</v>
+        <v>125065.030988616</v>
       </c>
     </row>
     <row r="263">
@@ -3792,7 +3792,7 @@
         <v>2026</v>
       </c>
       <c r="D264">
-        <v>140796.3004815115</v>
+        <v>158945.7071426265</v>
       </c>
     </row>
     <row r="265">
@@ -3805,7 +3805,7 @@
         <v>2027</v>
       </c>
       <c r="D265">
-        <v>158818.3467690278</v>
+        <v>179499.8859602699</v>
       </c>
     </row>
     <row r="266">
@@ -3818,7 +3818,7 @@
         <v>2028</v>
       </c>
       <c r="D266">
-        <v>179541.5572977894</v>
+        <v>202853.2563117259</v>
       </c>
     </row>
     <row r="267">
@@ -3831,7 +3831,7 @@
         <v>2024</v>
       </c>
       <c r="D267">
-        <v>111597.1299528229</v>
+        <v>111597.1299528225</v>
       </c>
     </row>
     <row r="268">
@@ -3857,7 +3857,7 @@
         <v>2026</v>
       </c>
       <c r="D269">
-        <v>122426.0789142984</v>
+        <v>134601.1466369692</v>
       </c>
     </row>
     <row r="270">
@@ -3870,7 +3870,7 @@
         <v>2027</v>
       </c>
       <c r="D270">
-        <v>134727.5390542735</v>
+        <v>148730.6022152846</v>
       </c>
     </row>
     <row r="271">
@@ -3883,7 +3883,7 @@
         <v>2028</v>
       </c>
       <c r="D271">
-        <v>148790.2649922846</v>
+        <v>164541.1225038288</v>
       </c>
     </row>
     <row r="272">
@@ -3922,7 +3922,7 @@
         <v>2026</v>
       </c>
       <c r="D274">
-        <v>119902.9598677876</v>
+        <v>126268.6692090152</v>
       </c>
     </row>
     <row r="275">
@@ -3935,7 +3935,7 @@
         <v>2027</v>
       </c>
       <c r="D275">
-        <v>126270.6121180755</v>
+        <v>132966.3474409032</v>
       </c>
     </row>
     <row r="276">
@@ -3948,7 +3948,7 @@
         <v>2028</v>
       </c>
       <c r="D276">
-        <v>132966.0022847629</v>
+        <v>140018.20071781</v>
       </c>
     </row>
     <row r="277">
@@ -3987,7 +3987,7 @@
         <v>2026</v>
       </c>
       <c r="D279">
-        <v>61869.10361116731</v>
+        <v>64492.4074185487</v>
       </c>
     </row>
     <row r="280">
@@ -4000,7 +4000,7 @@
         <v>2027</v>
       </c>
       <c r="D280">
-        <v>64493.64579679496</v>
+        <v>67239.49858588609</v>
       </c>
     </row>
     <row r="281">
@@ -4013,7 +4013,7 @@
         <v>2028</v>
       </c>
       <c r="D281">
-        <v>67239.69052773064</v>
+        <v>70104.20403552426</v>
       </c>
     </row>
     <row r="282">
@@ -4026,7 +4026,7 @@
         <v>2024</v>
       </c>
       <c r="D282">
-        <v>41850.59892271184</v>
+        <v>41850.59892271169</v>
       </c>
     </row>
     <row r="283">
@@ -4052,7 +4052,7 @@
         <v>2026</v>
       </c>
       <c r="D284">
-        <v>43436.26844807777</v>
+        <v>45090.56541729684</v>
       </c>
     </row>
     <row r="285">
@@ -4065,7 +4065,7 @@
         <v>2027</v>
       </c>
       <c r="D285">
-        <v>45089.97439660803</v>
+        <v>46814.90194538218</v>
       </c>
     </row>
     <row r="286">
@@ -4078,7 +4078,7 @@
         <v>2028</v>
       </c>
       <c r="D286">
-        <v>46814.94436711397</v>
+        <v>48605.31203780503</v>
       </c>
     </row>
     <row r="287">
@@ -4091,7 +4091,7 @@
         <v>2024</v>
       </c>
       <c r="D287">
-        <v>31936.62013383395</v>
+        <v>31936.62013383389</v>
       </c>
     </row>
     <row r="288">
@@ -4117,7 +4117,7 @@
         <v>2026</v>
       </c>
       <c r="D289">
-        <v>33417.97726362572</v>
+        <v>34968.0265311121</v>
       </c>
     </row>
     <row r="290">
@@ -4130,7 +4130,7 @@
         <v>2027</v>
       </c>
       <c r="D290">
-        <v>34968.02965277944</v>
+        <v>36589.96215778614</v>
       </c>
     </row>
     <row r="291">
@@ -4143,7 +4143,7 @@
         <v>2028</v>
       </c>
       <c r="D291">
-        <v>36589.96163610787</v>
+        <v>38287.1270202357</v>
       </c>
     </row>
     <row r="292">
@@ -4182,7 +4182,7 @@
         <v>2026</v>
       </c>
       <c r="D294">
-        <v>71226.60466935168</v>
+        <v>73582.12477643377</v>
       </c>
     </row>
     <row r="295">
@@ -4195,7 +4195,7 @@
         <v>2027</v>
       </c>
       <c r="D295">
-        <v>75456.83781249226</v>
+        <v>79765.36437876003</v>
       </c>
     </row>
     <row r="296">
@@ -4208,7 +4208,7 @@
         <v>2028</v>
       </c>
       <c r="D296">
-        <v>77938.87413742214</v>
+        <v>80663.24808096263</v>
       </c>
     </row>
     <row r="297">
@@ -4221,7 +4221,7 @@
         <v>2024</v>
       </c>
       <c r="D297">
-        <v>63177.70399641003</v>
+        <v>63177.70399640991</v>
       </c>
     </row>
     <row r="298">
@@ -4247,7 +4247,7 @@
         <v>2026</v>
       </c>
       <c r="D299">
-        <v>62528.2924242144</v>
+        <v>66718.16944336158</v>
       </c>
     </row>
     <row r="300">
@@ -4260,7 +4260,7 @@
         <v>2027</v>
       </c>
       <c r="D300">
-        <v>67879.81430550347</v>
+        <v>80826.92732145711</v>
       </c>
     </row>
     <row r="301">
@@ -4273,7 +4273,7 @@
         <v>2028</v>
       </c>
       <c r="D301">
-        <v>75585.04490053542</v>
+        <v>80076.93373978487</v>
       </c>
     </row>
     <row r="302">
@@ -4286,7 +4286,7 @@
         <v>2024</v>
       </c>
       <c r="D302">
-        <v>74513.47654136349</v>
+        <v>74513.47654136336</v>
       </c>
     </row>
     <row r="303">
@@ -4312,7 +4312,7 @@
         <v>2026</v>
       </c>
       <c r="D304">
-        <v>77956.33523524409</v>
+        <v>81508.92315892079</v>
       </c>
     </row>
     <row r="305">
@@ -4325,7 +4325,7 @@
         <v>2027</v>
       </c>
       <c r="D305">
-        <v>81531.8698582325</v>
+        <v>85243.79788653918</v>
       </c>
     </row>
     <row r="306">
@@ -4338,7 +4338,7 @@
         <v>2028</v>
       </c>
       <c r="D306">
-        <v>85232.63892899654</v>
+        <v>89114.80454410518</v>
       </c>
     </row>
     <row r="307">
@@ -4351,7 +4351,7 @@
         <v>2024</v>
       </c>
       <c r="D307">
-        <v>68413.30809907055</v>
+        <v>68413.30809907043</v>
       </c>
     </row>
     <row r="308">
@@ -4377,7 +4377,7 @@
         <v>2026</v>
       </c>
       <c r="D309">
-        <v>70372.55509940986</v>
+        <v>72325.84629520269</v>
       </c>
     </row>
     <row r="310">
@@ -4390,7 +4390,7 @@
         <v>2027</v>
       </c>
       <c r="D310">
-        <v>72290.04451687</v>
+        <v>74159.38308845235</v>
       </c>
     </row>
     <row r="311">
@@ -4403,7 +4403,7 @@
         <v>2028</v>
       </c>
       <c r="D311">
-        <v>74138.19114077787</v>
+        <v>75974.233049437</v>
       </c>
     </row>
     <row r="312">
@@ -4416,7 +4416,7 @@
         <v>2024</v>
       </c>
       <c r="D312">
-        <v>48679.43070464168</v>
+        <v>48679.43070464159</v>
       </c>
     </row>
     <row r="313">
@@ -4442,7 +4442,7 @@
         <v>2026</v>
       </c>
       <c r="D314">
-        <v>50957.60940682592</v>
+        <v>53353.62712822531</v>
       </c>
     </row>
     <row r="315">
@@ -4455,7 +4455,7 @@
         <v>2027</v>
       </c>
       <c r="D315">
-        <v>53354.77788059815</v>
+        <v>55877.67181220207</v>
       </c>
     </row>
     <row r="316">
@@ -4468,7 +4468,7 @@
         <v>2028</v>
       </c>
       <c r="D316">
-        <v>55877.79539186224</v>
+        <v>58521.51186882045</v>
       </c>
     </row>
     <row r="317">
@@ -4507,7 +4507,7 @@
         <v>2026</v>
       </c>
       <c r="D319">
-        <v>136347.9241948313</v>
+        <v>142929.2429108752</v>
       </c>
     </row>
     <row r="320">
@@ -4520,7 +4520,7 @@
         <v>2027</v>
       </c>
       <c r="D320">
-        <v>142834.0335090882</v>
+        <v>149234.9227103335</v>
       </c>
     </row>
     <row r="321">
@@ -4533,7 +4533,7 @@
         <v>2028</v>
       </c>
       <c r="D321">
-        <v>149201.2684435241</v>
+        <v>155713.4000359328</v>
       </c>
     </row>
     <row r="322">
@@ -4572,7 +4572,7 @@
         <v>2026</v>
       </c>
       <c r="D324">
-        <v>152332.5781931057</v>
+        <v>155461.2375923481</v>
       </c>
     </row>
     <row r="325">
@@ -4585,7 +4585,7 @@
         <v>2027</v>
       </c>
       <c r="D325">
-        <v>155455.0309760899</v>
+        <v>158677.3984395314</v>
       </c>
     </row>
     <row r="326">
@@ -4598,7 +4598,7 @@
         <v>2028</v>
       </c>
       <c r="D326">
-        <v>158678.3483362996</v>
+        <v>161963.0034447128</v>
       </c>
     </row>
     <row r="327">
@@ -4637,7 +4637,7 @@
         <v>2026</v>
       </c>
       <c r="D329">
-        <v>86367.50533375188</v>
+        <v>86193.83319927822</v>
       </c>
     </row>
     <row r="330">
@@ -4650,7 +4650,7 @@
         <v>2027</v>
       </c>
       <c r="D330">
-        <v>86193.8339699026</v>
+        <v>86020.58190668293</v>
       </c>
     </row>
     <row r="331">
@@ -4663,7 +4663,7 @@
         <v>2028</v>
       </c>
       <c r="D331">
-        <v>86020.58191521745</v>
+        <v>85847.67887813003</v>
       </c>
     </row>
     <row r="332">
@@ -4676,7 +4676,7 @@
         <v>2024</v>
       </c>
       <c r="D332">
-        <v>37842.51206330657</v>
+        <v>37842.51206330644</v>
       </c>
     </row>
     <row r="333">
@@ -4702,7 +4702,7 @@
         <v>2026</v>
       </c>
       <c r="D334">
-        <v>37323.37797967071</v>
+        <v>36811.36551009378</v>
       </c>
     </row>
     <row r="335">
@@ -4715,7 +4715,7 @@
         <v>2027</v>
       </c>
       <c r="D335">
-        <v>36811.36550959224</v>
+        <v>36306.37695712585</v>
       </c>
     </row>
     <row r="336">
@@ -4728,7 +4728,7 @@
         <v>2028</v>
       </c>
       <c r="D336">
-        <v>36306.37695710405</v>
+        <v>35808.31597755063</v>
       </c>
     </row>
     <row r="337">
@@ -4767,7 +4767,7 @@
         <v>2026</v>
       </c>
       <c r="D339">
-        <v>218901.2453407176</v>
+        <v>234792.1279106515</v>
       </c>
     </row>
     <row r="340">
@@ -4780,7 +4780,7 @@
         <v>2027</v>
       </c>
       <c r="D340">
-        <v>232702.5679299682</v>
+        <v>247837.9387410323</v>
       </c>
     </row>
     <row r="341">
@@ -4793,7 +4793,7 @@
         <v>2028</v>
       </c>
       <c r="D341">
-        <v>249676.3793701463</v>
+        <v>267473.6802706441</v>
       </c>
     </row>
     <row r="342">
@@ -4806,7 +4806,7 @@
         <v>2024</v>
       </c>
       <c r="D342">
-        <v>125320.3980949141</v>
+        <v>125320.3980949139</v>
       </c>
     </row>
     <row r="343">
@@ -4832,7 +4832,7 @@
         <v>2026</v>
       </c>
       <c r="D344">
-        <v>132506.5503295345</v>
+        <v>139183.5577602061</v>
       </c>
     </row>
     <row r="345">
@@ -4845,7 +4845,7 @@
         <v>2027</v>
       </c>
       <c r="D345">
-        <v>139704.1603529951</v>
+        <v>146871.5712686066</v>
       </c>
     </row>
     <row r="346">
@@ -4858,7 +4858,7 @@
         <v>2028</v>
       </c>
       <c r="D346">
-        <v>146561.5766363455</v>
+        <v>154004.9606639121</v>
       </c>
     </row>
     <row r="347">
@@ -4871,7 +4871,7 @@
         <v>2024</v>
       </c>
       <c r="D347">
-        <v>147023.8133637795</v>
+        <v>147023.813363779</v>
       </c>
     </row>
     <row r="348">
@@ -4897,7 +4897,7 @@
         <v>2026</v>
       </c>
       <c r="D349">
-        <v>154971.4648646854</v>
+        <v>163400.7515382727</v>
       </c>
     </row>
     <row r="350">
@@ -4910,7 +4910,7 @@
         <v>2027</v>
       </c>
       <c r="D350">
-        <v>163423.7430758279</v>
+        <v>172416.1441408079</v>
       </c>
     </row>
     <row r="351">
@@ -4923,7 +4923,7 @@
         <v>2028</v>
       </c>
       <c r="D351">
-        <v>172426.8657065398</v>
+        <v>181962.8890222737</v>
       </c>
     </row>
     <row r="352">
@@ -4936,7 +4936,7 @@
         <v>2024</v>
       </c>
       <c r="D352">
-        <v>99756.26391615858</v>
+        <v>99756.26391615841</v>
       </c>
     </row>
     <row r="353">
@@ -4962,7 +4962,7 @@
         <v>2026</v>
       </c>
       <c r="D354">
-        <v>104978.4734149177</v>
+        <v>110281.490338823</v>
       </c>
     </row>
     <row r="355">
@@ -4975,7 +4975,7 @@
         <v>2027</v>
       </c>
       <c r="D355">
-        <v>110205.6981038504</v>
+        <v>115412.159263925</v>
       </c>
     </row>
     <row r="356">
@@ -4988,7 +4988,7 @@
         <v>2028</v>
       </c>
       <c r="D356">
-        <v>115380.8970158411</v>
+        <v>120683.4008692356</v>
       </c>
     </row>
     <row r="357">
@@ -5001,7 +5001,7 @@
         <v>2024</v>
       </c>
       <c r="D357">
-        <v>117329.5335326066</v>
+        <v>117329.5335326062</v>
       </c>
     </row>
     <row r="358">
@@ -5027,7 +5027,7 @@
         <v>2026</v>
       </c>
       <c r="D359">
-        <v>126229.6364453242</v>
+        <v>135804.8620613548</v>
       </c>
     </row>
     <row r="360">
@@ -5040,7 +5040,7 @@
         <v>2027</v>
       </c>
       <c r="D360">
-        <v>135804.8620613548</v>
+        <v>146106.4222227407</v>
       </c>
     </row>
     <row r="361">
@@ -5053,7 +5053,7 @@
         <v>2028</v>
       </c>
       <c r="D361">
-        <v>146106.4222227407</v>
+        <v>157189.413476857</v>
       </c>
     </row>
     <row r="362">
@@ -5092,7 +5092,7 @@
         <v>2026</v>
       </c>
       <c r="D364">
-        <v>86426.37379461141</v>
+        <v>90003.98137543621</v>
       </c>
     </row>
     <row r="365">
@@ -5105,7 +5105,7 @@
         <v>2027</v>
       </c>
       <c r="D365">
-        <v>88755.08719948586</v>
+        <v>91451.18674696442</v>
       </c>
     </row>
     <row r="366">
@@ -5118,7 +5118,7 @@
         <v>2028</v>
       </c>
       <c r="D366">
-        <v>92488.56158564692</v>
+        <v>96119.83328331288</v>
       </c>
     </row>
     <row r="367">
@@ -5131,7 +5131,7 @@
         <v>2024</v>
       </c>
       <c r="D367">
-        <v>89821.44794852789</v>
+        <v>89821.44794852757</v>
       </c>
     </row>
     <row r="368">
@@ -5157,7 +5157,7 @@
         <v>2026</v>
       </c>
       <c r="D369">
-        <v>97862.19679368743</v>
+        <v>106622.782241487</v>
       </c>
     </row>
     <row r="370">
@@ -5170,7 +5170,7 @@
         <v>2027</v>
       </c>
       <c r="D370">
-        <v>106622.7821664535</v>
+        <v>116167.6495079015</v>
       </c>
     </row>
     <row r="371">
@@ -5183,7 +5183,7 @@
         <v>2028</v>
       </c>
       <c r="D371">
-        <v>116167.6495080781</v>
+        <v>126566.9729166122</v>
       </c>
     </row>
     <row r="372">
@@ -5222,7 +5222,7 @@
         <v>2026</v>
       </c>
       <c r="D374">
-        <v>100645.3465631804</v>
+        <v>103477.9766117541</v>
       </c>
     </row>
     <row r="375">
@@ -5235,7 +5235,7 @@
         <v>2027</v>
       </c>
       <c r="D375">
-        <v>103481.6589753214</v>
+        <v>106373.6514753659</v>
       </c>
     </row>
     <row r="376">
@@ -5248,7 +5248,7 @@
         <v>2028</v>
       </c>
       <c r="D376">
-        <v>106373.1403419556</v>
+        <v>109348.7811233383</v>
       </c>
     </row>
     <row r="377">
@@ -5261,7 +5261,7 @@
         <v>2024</v>
       </c>
       <c r="D377">
-        <v>106667.8497935736</v>
+        <v>106667.8497935732</v>
       </c>
     </row>
     <row r="378">
@@ -5287,7 +5287,7 @@
         <v>2026</v>
       </c>
       <c r="D379">
-        <v>108526.4134542874</v>
+        <v>110433.7064659299</v>
       </c>
     </row>
     <row r="380">
@@ -5300,7 +5300,7 @@
         <v>2027</v>
       </c>
       <c r="D380">
-        <v>110430.5985301988</v>
+        <v>112381.666083164</v>
       </c>
     </row>
     <row r="381">
@@ -5313,7 +5313,7 @@
         <v>2028</v>
       </c>
       <c r="D381">
-        <v>112382.2674046796</v>
+        <v>114365.8218983203</v>
       </c>
     </row>
     <row r="382">
@@ -5326,7 +5326,7 @@
         <v>2024</v>
       </c>
       <c r="D382">
-        <v>76436.88831551559</v>
+        <v>76436.88831551546</v>
       </c>
     </row>
     <row r="383">
@@ -5352,7 +5352,7 @@
         <v>2026</v>
       </c>
       <c r="D384">
-        <v>82724.09871731821</v>
+        <v>89320.96417055884</v>
       </c>
     </row>
     <row r="385">
@@ -5365,7 +5365,7 @@
         <v>2027</v>
       </c>
       <c r="D385">
-        <v>89362.02684815528</v>
+        <v>96353.14575043804</v>
       </c>
     </row>
     <row r="386">
@@ -5378,7 +5378,7 @@
         <v>2028</v>
       </c>
       <c r="D386">
-        <v>96344.37386653859</v>
+        <v>103910.5815437639</v>
       </c>
     </row>
     <row r="387">
@@ -5391,7 +5391,7 @@
         <v>2024</v>
       </c>
       <c r="D387">
-        <v>51764.9046246649</v>
+        <v>51764.90462466471</v>
       </c>
     </row>
     <row r="388">
@@ -5417,7 +5417,7 @@
         <v>2026</v>
       </c>
       <c r="D389">
-        <v>54310.23889151205</v>
+        <v>56969.13579833922</v>
       </c>
     </row>
     <row r="390">
@@ -5430,7 +5430,7 @@
         <v>2027</v>
       </c>
       <c r="D390">
-        <v>56970.64951026256</v>
+        <v>59750.80919160879</v>
       </c>
     </row>
     <row r="391">
@@ -5443,7 +5443,7 @@
         <v>2028</v>
       </c>
       <c r="D391">
-        <v>59750.6018981458</v>
+        <v>62667.65312997046</v>
       </c>
     </row>
     <row r="392">
@@ -5482,7 +5482,7 @@
         <v>2026</v>
       </c>
       <c r="D394">
-        <v>52991.12879775577</v>
+        <v>56461.30063109626</v>
       </c>
     </row>
     <row r="395">
@@ -5495,7 +5495,7 @@
         <v>2027</v>
       </c>
       <c r="D395">
-        <v>56461.9401973718</v>
+        <v>60162.59327973132</v>
       </c>
     </row>
     <row r="396">
@@ -5508,7 +5508,7 @@
         <v>2028</v>
       </c>
       <c r="D396">
-        <v>60162.84718445648</v>
+        <v>64107.33398944121</v>
       </c>
     </row>
     <row r="397">
@@ -5521,7 +5521,7 @@
         <v>2024</v>
       </c>
       <c r="D397">
-        <v>58970.22176203752</v>
+        <v>58970.22176203741</v>
       </c>
     </row>
     <row r="398">
@@ -5547,7 +5547,7 @@
         <v>2026</v>
       </c>
       <c r="D399">
-        <v>65724.68457051071</v>
+        <v>73252.77146616897</v>
       </c>
     </row>
     <row r="400">
@@ -5560,7 +5560,7 @@
         <v>2027</v>
       </c>
       <c r="D400">
-        <v>73252.77159448319</v>
+        <v>81643.08625294312</v>
       </c>
     </row>
     <row r="401">
@@ -5573,7 +5573,7 @@
         <v>2028</v>
       </c>
       <c r="D401">
-        <v>81643.08625239767</v>
+        <v>90994.4210895877</v>
       </c>
     </row>
     <row r="402">
@@ -5586,7 +5586,7 @@
         <v>2024</v>
       </c>
       <c r="D402">
-        <v>36273.96189172559</v>
+        <v>36273.96189172552</v>
       </c>
     </row>
     <row r="403">
@@ -5612,7 +5612,7 @@
         <v>2026</v>
       </c>
       <c r="D404">
-        <v>37916.53920193628</v>
+        <v>39585.75674385083</v>
       </c>
     </row>
     <row r="405">
@@ -5625,7 +5625,7 @@
         <v>2027</v>
       </c>
       <c r="D405">
-        <v>39602.71391722582</v>
+        <v>41331.74735690729</v>
       </c>
     </row>
     <row r="406">
@@ -5638,7 +5638,7 @@
         <v>2028</v>
       </c>
       <c r="D406">
-        <v>41325.4578964832</v>
+        <v>43135.04996563186</v>
       </c>
     </row>
     <row r="407">
@@ -5651,7 +5651,7 @@
         <v>2024</v>
       </c>
       <c r="D407">
-        <v>67418.61452165103</v>
+        <v>67418.61452165092</v>
       </c>
     </row>
     <row r="408">
@@ -5677,7 +5677,7 @@
         <v>2026</v>
       </c>
       <c r="D409">
-        <v>77318.16378261498</v>
+        <v>88395.74321104247</v>
       </c>
     </row>
     <row r="410">
@@ -5690,7 +5690,7 @@
         <v>2027</v>
       </c>
       <c r="D410">
-        <v>88303.54080798526</v>
+        <v>100431.4155285311</v>
       </c>
     </row>
     <row r="411">
@@ -5703,7 +5703,7 @@
         <v>2028</v>
       </c>
       <c r="D411">
-        <v>100396.2827756582</v>
+        <v>113986.1181686139</v>
       </c>
     </row>
     <row r="412">
@@ -5742,7 +5742,7 @@
         <v>2026</v>
       </c>
       <c r="D414">
-        <v>31831.51895934964</v>
+        <v>33109.54248051847</v>
       </c>
     </row>
     <row r="415">
@@ -5755,7 +5755,7 @@
         <v>2027</v>
       </c>
       <c r="D415">
-        <v>33100.10686723531</v>
+        <v>34453.80189668532</v>
       </c>
     </row>
     <row r="416">
@@ -5768,7 +5768,7 @@
         <v>2028</v>
       </c>
       <c r="D416">
-        <v>34455.97453408521</v>
+        <v>35859.42170151387</v>
       </c>
     </row>
     <row r="417">
@@ -5781,7 +5781,7 @@
         <v>2024</v>
       </c>
       <c r="D417">
-        <v>44995.88888659293</v>
+        <v>44995.88888659301</v>
       </c>
     </row>
     <row r="418">
@@ -5807,7 +5807,7 @@
         <v>2026</v>
       </c>
       <c r="D419">
-        <v>47957.82953788736</v>
+        <v>50992.47729736369</v>
       </c>
     </row>
     <row r="420">
@@ -5820,7 +5820,7 @@
         <v>2027</v>
       </c>
       <c r="D420">
-        <v>50962.07902664151</v>
+        <v>53992.77979421714</v>
       </c>
     </row>
     <row r="421">
@@ -5833,7 +5833,7 @@
         <v>2028</v>
       </c>
       <c r="D421">
-        <v>53984.76374673569</v>
+        <v>57144.15519795743</v>
       </c>
     </row>
     <row r="422">
@@ -5846,7 +5846,7 @@
         <v>2024</v>
       </c>
       <c r="D422">
-        <v>35736.38417555395</v>
+        <v>35736.38417555377</v>
       </c>
     </row>
     <row r="423">
@@ -5872,7 +5872,7 @@
         <v>2026</v>
       </c>
       <c r="D424">
-        <v>36432.98456231494</v>
+        <v>37073.26881994028</v>
       </c>
     </row>
     <row r="425">
@@ -5885,7 +5885,7 @@
         <v>2027</v>
       </c>
       <c r="D425">
-        <v>37104.58140735218</v>
+        <v>37749.30570876833</v>
       </c>
     </row>
     <row r="426">
@@ -5898,7 +5898,7 @@
         <v>2028</v>
       </c>
       <c r="D426">
-        <v>37735.02330070998</v>
+        <v>38394.05819129366</v>
       </c>
     </row>
     <row r="427">
@@ -5937,7 +5937,7 @@
         <v>2026</v>
       </c>
       <c r="D429">
-        <v>50555.10335893002</v>
+        <v>52522.51061563106</v>
       </c>
     </row>
     <row r="430">
@@ -5950,7 +5950,7 @@
         <v>2027</v>
       </c>
       <c r="D430">
-        <v>52522.32920898971</v>
+        <v>54563.62436323531</v>
       </c>
     </row>
     <row r="431">
@@ -5963,7 +5963,7 @@
         <v>2028</v>
       </c>
       <c r="D431">
-        <v>54563.60886677282</v>
+        <v>56684.01095315234</v>
       </c>
     </row>
     <row r="432">
@@ -5976,7 +5976,7 @@
         <v>2024</v>
       </c>
       <c r="D432">
-        <v>62825.53198216988</v>
+        <v>62825.53198216977</v>
       </c>
     </row>
     <row r="433">
@@ -6002,7 +6002,7 @@
         <v>2026</v>
       </c>
       <c r="D434">
-        <v>64622.04343850017</v>
+        <v>64958.69787829099</v>
       </c>
     </row>
     <row r="435">
@@ -6015,7 +6015,7 @@
         <v>2027</v>
       </c>
       <c r="D435">
-        <v>65849.76712311561</v>
+        <v>66474.7701450086</v>
       </c>
     </row>
     <row r="436">
@@ -6028,7 +6028,7 @@
         <v>2028</v>
       </c>
       <c r="D436">
-        <v>65940.4018718141</v>
+        <v>66398.858585979</v>
       </c>
     </row>
     <row r="437">
@@ -6041,7 +6041,7 @@
         <v>2024</v>
       </c>
       <c r="D437">
-        <v>36919.70175444776</v>
+        <v>36919.70175444757</v>
       </c>
     </row>
     <row r="438">
@@ -6067,7 +6067,7 @@
         <v>2026</v>
       </c>
       <c r="D439">
-        <v>38736.14788026386</v>
+        <v>39676.71076398101</v>
       </c>
     </row>
     <row r="440">
@@ -6080,7 +6080,7 @@
         <v>2027</v>
       </c>
       <c r="D440">
-        <v>40221.88983770827</v>
+        <v>41332.94121687828</v>
       </c>
     </row>
     <row r="441">
@@ -6093,7 +6093,7 @@
         <v>2028</v>
       </c>
       <c r="D441">
-        <v>41013.92468051261</v>
+        <v>42068.98332599311</v>
       </c>
     </row>
     <row r="442">
@@ -6106,7 +6106,7 @@
         <v>2024</v>
       </c>
       <c r="D442">
-        <v>49960.54429054138</v>
+        <v>49960.54429054147</v>
       </c>
     </row>
     <row r="443">
@@ -6132,7 +6132,7 @@
         <v>2026</v>
       </c>
       <c r="D444">
-        <v>54411.51115248784</v>
+        <v>59260.30626296251</v>
       </c>
     </row>
     <row r="445">
@@ -6145,7 +6145,7 @@
         <v>2027</v>
       </c>
       <c r="D445">
-        <v>59260.24122029083</v>
+        <v>64542.38999280257</v>
       </c>
     </row>
     <row r="446">
@@ -6158,7 +6158,7 @@
         <v>2028</v>
       </c>
       <c r="D446">
-        <v>64542.39355569125</v>
+        <v>70295.29643957743</v>
       </c>
     </row>
     <row r="447">
@@ -6197,7 +6197,7 @@
         <v>2026</v>
       </c>
       <c r="D449">
-        <v>58762.94333370297</v>
+        <v>59440.30743805496</v>
       </c>
     </row>
     <row r="450">
@@ -6210,7 +6210,7 @@
         <v>2027</v>
       </c>
       <c r="D450">
-        <v>59386.57095229003</v>
+        <v>60036.1787908991</v>
       </c>
     </row>
     <row r="451">
@@ -6223,7 +6223,7 @@
         <v>2028</v>
       </c>
       <c r="D451">
-        <v>60076.21752043006</v>
+        <v>60759.42482160436</v>
       </c>
     </row>
     <row r="452">
@@ -6236,7 +6236,7 @@
         <v>2024</v>
       </c>
       <c r="D452">
-        <v>49037.38130113736</v>
+        <v>49037.38130113727</v>
       </c>
     </row>
     <row r="453">
@@ -6262,7 +6262,7 @@
         <v>2026</v>
       </c>
       <c r="D454">
-        <v>50321.84923956868</v>
+        <v>52331.03901495941</v>
       </c>
     </row>
     <row r="455">
@@ -6275,7 +6275,7 @@
         <v>2027</v>
       </c>
       <c r="D455">
-        <v>51686.42656275018</v>
+        <v>53135.77452344055</v>
       </c>
     </row>
     <row r="456">
@@ -6288,7 +6288,7 @@
         <v>2028</v>
       </c>
       <c r="D456">
-        <v>53753.37008350759</v>
+        <v>55856.11427971536</v>
       </c>
     </row>
     <row r="457">
@@ -6327,7 +6327,7 @@
         <v>2026</v>
       </c>
       <c r="D459">
-        <v>145949.3745106429</v>
+        <v>158683.2738790525</v>
       </c>
     </row>
     <row r="460">
@@ -6340,7 +6340,7 @@
         <v>2027</v>
       </c>
       <c r="D460">
-        <v>158668.2021211852</v>
+        <v>172361.1367679829</v>
       </c>
     </row>
     <row r="461">
@@ -6353,7 +6353,7 @@
         <v>2028</v>
       </c>
       <c r="D461">
-        <v>172358.8625813175</v>
+        <v>187210.5661363722</v>
       </c>
     </row>
     <row r="462">
@@ -6366,7 +6366,7 @@
         <v>2024</v>
       </c>
       <c r="D462">
-        <v>53547.11262275995</v>
+        <v>53547.11262275985</v>
       </c>
     </row>
     <row r="463">
@@ -6392,7 +6392,7 @@
         <v>2026</v>
       </c>
       <c r="D464">
-        <v>55240.70306277851</v>
+        <v>56993.02768185443</v>
       </c>
     </row>
     <row r="465">
@@ -6405,7 +6405,7 @@
         <v>2027</v>
       </c>
       <c r="D465">
-        <v>56991.87215875884</v>
+        <v>58802.69577701978</v>
       </c>
     </row>
     <row r="466">
@@ -6418,7 +6418,7 @@
         <v>2028</v>
       </c>
       <c r="D466">
-        <v>58802.96227710271</v>
+        <v>60670.65015267889</v>
       </c>
     </row>
     <row r="467">
@@ -6457,7 +6457,7 @@
         <v>2026</v>
       </c>
       <c r="D469">
-        <v>57935.04630229166</v>
+        <v>58355.9160004422</v>
       </c>
     </row>
     <row r="470">
@@ -6470,7 +6470,7 @@
         <v>2027</v>
       </c>
       <c r="D470">
-        <v>58312.70638957094</v>
+        <v>58560.48141860342</v>
       </c>
     </row>
     <row r="471">
@@ -6483,7 +6483,7 @@
         <v>2028</v>
       </c>
       <c r="D471">
-        <v>58539.30120003686</v>
+        <v>58702.02359959419</v>
       </c>
     </row>
     <row r="472">
@@ -6522,7 +6522,7 @@
         <v>2026</v>
       </c>
       <c r="D474">
-        <v>85407.03838264995</v>
+        <v>88859.82032416119</v>
       </c>
     </row>
     <row r="475">
@@ -6535,7 +6535,7 @@
         <v>2027</v>
       </c>
       <c r="D475">
-        <v>85667.6610291854</v>
+        <v>86174.31200042409</v>
       </c>
     </row>
     <row r="476">
@@ -6548,7 +6548,7 @@
         <v>2028</v>
       </c>
       <c r="D476">
-        <v>89149.33773432911</v>
+        <v>92527.55968899615</v>
       </c>
     </row>
     <row r="477">
@@ -6561,7 +6561,7 @@
         <v>2024</v>
       </c>
       <c r="D477">
-        <v>62581.59165106723</v>
+        <v>62581.59165106712</v>
       </c>
     </row>
     <row r="478">
@@ -6587,7 +6587,7 @@
         <v>2026</v>
       </c>
       <c r="D479">
-        <v>69476.11630013416</v>
+        <v>77129.29661716473</v>
       </c>
     </row>
     <row r="480">
@@ -6600,7 +6600,7 @@
         <v>2027</v>
       </c>
       <c r="D480">
-        <v>77129.33291903735</v>
+        <v>85624.63430542989</v>
       </c>
     </row>
     <row r="481">
@@ -6613,7 +6613,7 @@
         <v>2028</v>
       </c>
       <c r="D481">
-        <v>85624.63268757501</v>
+        <v>95055.67800967446</v>
       </c>
     </row>
     <row r="482">
@@ -6626,7 +6626,7 @@
         <v>2024</v>
       </c>
       <c r="D482">
-        <v>72757.61327170819</v>
+        <v>72757.61327170832</v>
       </c>
     </row>
     <row r="483">
@@ -6652,7 +6652,7 @@
         <v>2026</v>
       </c>
       <c r="D484">
-        <v>77510.07548411631</v>
+        <v>82918.57838145259</v>
       </c>
     </row>
     <row r="485">
@@ -6665,7 +6665,7 @@
         <v>2027</v>
       </c>
       <c r="D485">
-        <v>82743.18940932071</v>
+        <v>88511.71099352655</v>
       </c>
     </row>
     <row r="486">
@@ -6678,7 +6678,7 @@
         <v>2028</v>
       </c>
       <c r="D486">
-        <v>88606.77319501816</v>
+        <v>94786.86937119738</v>
       </c>
     </row>
     <row r="487">
@@ -6691,7 +6691,7 @@
         <v>2024</v>
       </c>
       <c r="D487">
-        <v>62153.0554413239</v>
+        <v>62153.05544132368</v>
       </c>
     </row>
     <row r="488">
@@ -6717,7 +6717,7 @@
         <v>2026</v>
       </c>
       <c r="D489">
-        <v>67949.47828176267</v>
+        <v>74023.67400055306</v>
       </c>
     </row>
     <row r="490">
@@ -6730,7 +6730,7 @@
         <v>2027</v>
       </c>
       <c r="D490">
-        <v>73932.56640259405</v>
+        <v>80059.23755458349</v>
       </c>
     </row>
     <row r="491">
@@ -6743,7 +6743,7 @@
         <v>2028</v>
       </c>
       <c r="D491">
-        <v>80024.98213012615</v>
+        <v>86475.81648110582</v>
       </c>
     </row>
     <row r="492">
@@ -6756,7 +6756,7 @@
         <v>2024</v>
       </c>
       <c r="D492">
-        <v>46199.99889039099</v>
+        <v>46199.99889039091</v>
       </c>
     </row>
     <row r="493">
@@ -6782,7 +6782,7 @@
         <v>2026</v>
       </c>
       <c r="D494">
-        <v>49078.26770211542</v>
+        <v>52131.05222697141</v>
       </c>
     </row>
     <row r="495">
@@ -6795,7 +6795,7 @@
         <v>2027</v>
       </c>
       <c r="D495">
-        <v>52133.15399872812</v>
+        <v>55375.32520556424</v>
       </c>
     </row>
     <row r="496">
@@ -6808,7 +6808,7 @@
         <v>2028</v>
       </c>
       <c r="D496">
-        <v>55374.34783553566</v>
+        <v>58818.38457025776</v>
       </c>
     </row>
     <row r="497">
@@ -6821,7 +6821,7 @@
         <v>2024</v>
       </c>
       <c r="D497">
-        <v>71173.75150718754</v>
+        <v>71173.75150718729</v>
       </c>
     </row>
     <row r="498">
@@ -6847,7 +6847,7 @@
         <v>2026</v>
       </c>
       <c r="D499">
-        <v>85794.12047395691</v>
+        <v>103147.4756665874</v>
       </c>
     </row>
     <row r="500">
@@ -6860,7 +6860,7 @@
         <v>2027</v>
       </c>
       <c r="D500">
-        <v>103383.2176428578</v>
+        <v>124536.7170332744</v>
       </c>
     </row>
     <row r="501">
@@ -6873,7 +6873,7 @@
         <v>2028</v>
       </c>
       <c r="D501">
-        <v>124288.9690534849</v>
+        <v>149465.768742373</v>
       </c>
     </row>
     <row r="502">
@@ -6912,7 +6912,7 @@
         <v>2026</v>
       </c>
       <c r="D504">
-        <v>49593.45433590566</v>
+        <v>51956.32457300281</v>
       </c>
     </row>
     <row r="505">
@@ -6925,7 +6925,7 @@
         <v>2027</v>
       </c>
       <c r="D505">
-        <v>51918.68627759874</v>
+        <v>54449.14161849441</v>
       </c>
     </row>
     <row r="506">
@@ -6938,7 +6938,7 @@
         <v>2028</v>
       </c>
       <c r="D506">
-        <v>54460.61251054093</v>
+        <v>57097.63311434772</v>
       </c>
     </row>
     <row r="507">
@@ -6977,7 +6977,7 @@
         <v>2026</v>
       </c>
       <c r="D509">
-        <v>44274.96013159048</v>
+        <v>45829.02517771013</v>
       </c>
     </row>
     <row r="510">
@@ -6990,7 +6990,7 @@
         <v>2027</v>
       </c>
       <c r="D510">
-        <v>45832.82129560884</v>
+        <v>47427.14588190929</v>
       </c>
     </row>
     <row r="511">
@@ -7003,7 +7003,7 @@
         <v>2028</v>
       </c>
       <c r="D511">
-        <v>47426.45314391991</v>
+        <v>49078.8445851667</v>
       </c>
     </row>
     <row r="512">
@@ -7042,7 +7042,7 @@
         <v>2026</v>
       </c>
       <c r="D514">
-        <v>54329.31232517126</v>
+        <v>57479.67776270287</v>
       </c>
     </row>
     <row r="515">
@@ -7055,7 +7055,7 @@
         <v>2027</v>
       </c>
       <c r="D515">
-        <v>57479.66575547239</v>
+        <v>60813.34636277054</v>
       </c>
     </row>
     <row r="516">
@@ -7068,7 +7068,7 @@
         <v>2028</v>
       </c>
       <c r="D516">
-        <v>60813.34660629887</v>
+        <v>64340.35965781501</v>
       </c>
     </row>
     <row r="517">
@@ -7107,7 +7107,7 @@
         <v>2026</v>
       </c>
       <c r="D519">
-        <v>51459.4085665508</v>
+        <v>54446.96108480062</v>
       </c>
     </row>
     <row r="520">
@@ -7120,7 +7120,7 @@
         <v>2027</v>
       </c>
       <c r="D520">
-        <v>54493.7153108499</v>
+        <v>57687.23060737119</v>
       </c>
     </row>
     <row r="521">
@@ -7133,7 +7133,7 @@
         <v>2028</v>
       </c>
       <c r="D521">
-        <v>57651.82220729402</v>
+        <v>61007.85850742515</v>
       </c>
     </row>
     <row r="522">
@@ -7146,7 +7146,7 @@
         <v>2024</v>
       </c>
       <c r="D522">
-        <v>75844.58111432589</v>
+        <v>75844.58111432563</v>
       </c>
     </row>
     <row r="523">
@@ -7172,7 +7172,7 @@
         <v>2026</v>
       </c>
       <c r="D524">
-        <v>80611.65323271294</v>
+        <v>85730.40332875871</v>
       </c>
     </row>
     <row r="525">
@@ -7185,7 +7185,7 @@
         <v>2027</v>
       </c>
       <c r="D525">
-        <v>85719.21338720723</v>
+        <v>91193.86114881384</v>
       </c>
     </row>
     <row r="526">
@@ -7198,7 +7198,7 @@
         <v>2028</v>
       </c>
       <c r="D526">
-        <v>91196.41959646785</v>
+        <v>97013.66087282401</v>
       </c>
     </row>
     <row r="527">
@@ -7211,7 +7211,7 @@
         <v>2024</v>
       </c>
       <c r="D527">
-        <v>101082.5495698335</v>
+        <v>101082.5495698333</v>
       </c>
     </row>
     <row r="528">
@@ -7237,7 +7237,7 @@
         <v>2026</v>
       </c>
       <c r="D529">
-        <v>104529.72138704</v>
+        <v>113331.9843441451</v>
       </c>
     </row>
     <row r="530">
@@ -7250,7 +7250,7 @@
         <v>2027</v>
       </c>
       <c r="D530">
-        <v>108565.0948238229</v>
+        <v>113247.1958274794</v>
       </c>
     </row>
     <row r="531">
@@ -7263,7 +7263,7 @@
         <v>2028</v>
       </c>
       <c r="D531">
-        <v>117754.1342399136</v>
+        <v>127217.9934213623</v>
       </c>
     </row>
     <row r="532">
@@ -7302,7 +7302,7 @@
         <v>2026</v>
       </c>
       <c r="D534">
-        <v>51269.89028638721</v>
+        <v>53717.86635510959</v>
       </c>
     </row>
     <row r="535">
@@ -7315,7 +7315,7 @@
         <v>2027</v>
       </c>
       <c r="D535">
-        <v>53756.74978015469</v>
+        <v>56356.7177428261</v>
       </c>
     </row>
     <row r="536">
@@ -7328,7 +7328,7 @@
         <v>2028</v>
       </c>
       <c r="D536">
-        <v>56322.29634631382</v>
+        <v>59016.92998709926</v>
       </c>
     </row>
     <row r="537">
@@ -7341,7 +7341,7 @@
         <v>2024</v>
       </c>
       <c r="D537">
-        <v>46127.82432571314</v>
+        <v>46127.82432571289</v>
       </c>
     </row>
     <row r="538">
@@ -7367,7 +7367,7 @@
         <v>2026</v>
       </c>
       <c r="D539">
-        <v>45678.67743931245</v>
+        <v>44979.81308680803</v>
       </c>
     </row>
     <row r="540">
@@ -7380,7 +7380,7 @@
         <v>2027</v>
       </c>
       <c r="D540">
-        <v>45192.48834148968</v>
+        <v>44670.53685603769</v>
       </c>
     </row>
     <row r="541">
@@ -7393,7 +7393,7 @@
         <v>2028</v>
       </c>
       <c r="D541">
-        <v>44494.43440430416</v>
+        <v>43840.77808376504</v>
       </c>
     </row>
     <row r="542">
@@ -7406,7 +7406,7 @@
         <v>2024</v>
       </c>
       <c r="D542">
-        <v>55525.46337452903</v>
+        <v>55525.46337452892</v>
       </c>
     </row>
     <row r="543">
@@ -7432,7 +7432,7 @@
         <v>2026</v>
       </c>
       <c r="D544">
-        <v>57528.92662427953</v>
+        <v>60145.39094821937</v>
       </c>
     </row>
     <row r="545">
@@ -7445,7 +7445,7 @@
         <v>2027</v>
       </c>
       <c r="D545">
-        <v>59615.5976422452</v>
+        <v>61789.27289827824</v>
       </c>
     </row>
     <row r="546">
@@ -7458,7 +7458,7 @@
         <v>2028</v>
       </c>
       <c r="D546">
-        <v>62327.19710194463</v>
+        <v>65150.44006285591</v>
       </c>
     </row>
     <row r="547">
@@ -7471,7 +7471,7 @@
         <v>2024</v>
       </c>
       <c r="D547">
-        <v>83472.21263539656</v>
+        <v>83472.21263539611</v>
       </c>
     </row>
     <row r="548">
@@ -7497,7 +7497,7 @@
         <v>2026</v>
       </c>
       <c r="D549">
-        <v>86014.55422685483</v>
+        <v>88633.72569894383</v>
       </c>
     </row>
     <row r="550">
@@ -7510,7 +7510,7 @@
         <v>2027</v>
       </c>
       <c r="D550">
-        <v>88633.74069248921</v>
+        <v>91332.07671159656</v>
       </c>
     </row>
     <row r="551">
@@ -7523,7 +7523,7 @@
         <v>2028</v>
       </c>
       <c r="D551">
-        <v>91332.07632748476</v>
+        <v>94112.57470481336</v>
       </c>
     </row>
     <row r="552">
@@ -7536,7 +7536,7 @@
         <v>2024</v>
       </c>
       <c r="D552">
-        <v>42817.85763911377</v>
+        <v>42817.85763911354</v>
       </c>
     </row>
     <row r="553">
@@ -7562,7 +7562,7 @@
         <v>2026</v>
       </c>
       <c r="D554">
-        <v>45525.71057926585</v>
+        <v>48418.67346716296</v>
       </c>
     </row>
     <row r="555">
@@ -7575,7 +7575,7 @@
         <v>2027</v>
       </c>
       <c r="D555">
-        <v>48417.58063485324</v>
+        <v>51506.73109885397</v>
       </c>
     </row>
     <row r="556">
@@ -7588,7 +7588,7 @@
         <v>2028</v>
       </c>
       <c r="D556">
-        <v>51506.82273742236</v>
+        <v>54792.03205191759</v>
       </c>
     </row>
     <row r="557">
@@ -7601,7 +7601,7 @@
         <v>2024</v>
       </c>
       <c r="D557">
-        <v>47796.2879511575</v>
+        <v>47796.28795115741</v>
       </c>
     </row>
     <row r="558">
@@ -7627,7 +7627,7 @@
         <v>2026</v>
       </c>
       <c r="D559">
-        <v>52465.02968801896</v>
+        <v>57667.20876255669</v>
       </c>
     </row>
     <row r="560">
@@ -7640,7 +7640,7 @@
         <v>2027</v>
       </c>
       <c r="D560">
-        <v>57682.50858669762</v>
+        <v>63520.92566045841</v>
       </c>
     </row>
     <row r="561">
@@ -7653,7 +7653,7 @@
         <v>2028</v>
       </c>
       <c r="D561">
-        <v>63524.25420679849</v>
+        <v>69979.84493492432</v>
       </c>
     </row>
     <row r="562">
@@ -7666,7 +7666,7 @@
         <v>2024</v>
       </c>
       <c r="D562">
-        <v>23026.3812018351</v>
+        <v>23026.38120183506</v>
       </c>
     </row>
     <row r="563">
@@ -7692,7 +7692,7 @@
         <v>2026</v>
       </c>
       <c r="D564">
-        <v>22874.98983092198</v>
+        <v>22927.34320786543</v>
       </c>
     </row>
     <row r="565">
@@ -7705,7 +7705,7 @@
         <v>2027</v>
       </c>
       <c r="D565">
-        <v>22860.55954903562</v>
+        <v>22982.83133270754</v>
       </c>
     </row>
     <row r="566">
@@ -7718,7 +7718,7 @@
         <v>2028</v>
       </c>
       <c r="D566">
-        <v>23004.85947554747</v>
+        <v>23104.7616255275</v>
       </c>
     </row>
     <row r="567">
@@ -7731,7 +7731,7 @@
         <v>2024</v>
       </c>
       <c r="D567">
-        <v>35162.70050793116</v>
+        <v>35162.7005079311</v>
       </c>
     </row>
     <row r="568">
@@ -7757,7 +7757,7 @@
         <v>2026</v>
       </c>
       <c r="D569">
-        <v>37027.69441438739</v>
+        <v>38344.9813039756</v>
       </c>
     </row>
     <row r="570">
@@ -7770,7 +7770,7 @@
         <v>2027</v>
       </c>
       <c r="D570">
-        <v>38884.08350327489</v>
+        <v>40720.94146559192</v>
       </c>
     </row>
     <row r="571">
@@ -7783,7 +7783,7 @@
         <v>2028</v>
       </c>
       <c r="D571">
-        <v>40249.05582117298</v>
+        <v>41758.1019478936</v>
       </c>
     </row>
     <row r="572">
@@ -7796,7 +7796,7 @@
         <v>2024</v>
       </c>
       <c r="D572">
-        <v>47780.71660834587</v>
+        <v>47780.71660834596</v>
       </c>
     </row>
     <row r="573">
@@ -7822,7 +7822,7 @@
         <v>2026</v>
       </c>
       <c r="D574">
-        <v>58595.22175993607</v>
+        <v>68573.5238030269</v>
       </c>
     </row>
     <row r="575">
@@ -7835,7 +7835,7 @@
         <v>2027</v>
       </c>
       <c r="D575">
-        <v>71735.00673268118</v>
+        <v>87671.71102873029</v>
       </c>
     </row>
     <row r="576">
@@ -7848,7 +7848,7 @@
         <v>2028</v>
       </c>
       <c r="D576">
-        <v>83945.6912074689</v>
+        <v>98396.41569902682</v>
       </c>
     </row>
     <row r="577">
@@ -7861,7 +7861,7 @@
         <v>2024</v>
       </c>
       <c r="D577">
-        <v>68029.311862128</v>
+        <v>68029.31186212777</v>
       </c>
     </row>
     <row r="578">
@@ -7887,7 +7887,7 @@
         <v>2026</v>
       </c>
       <c r="D579">
-        <v>69587.96788668822</v>
+        <v>71190.0345193705</v>
       </c>
     </row>
     <row r="580">
@@ -7900,7 +7900,7 @@
         <v>2027</v>
       </c>
       <c r="D580">
-        <v>71188.47925834029</v>
+        <v>72832.0881184101</v>
       </c>
     </row>
     <row r="581">
@@ -7913,7 +7913,7 @@
         <v>2028</v>
       </c>
       <c r="D581">
-        <v>72832.40951403276</v>
+        <v>74513.00339371669</v>
       </c>
     </row>
     <row r="582">
@@ -7952,7 +7952,7 @@
         <v>2026</v>
       </c>
       <c r="D584">
-        <v>47164.42399953344</v>
+        <v>49632.85623134057</v>
       </c>
     </row>
     <row r="585">
@@ -7965,7 +7965,7 @@
         <v>2027</v>
       </c>
       <c r="D585">
-        <v>50192.8563345957</v>
+        <v>53297.25727322357</v>
       </c>
     </row>
     <row r="586">
@@ -7978,7 +7978,7 @@
         <v>2028</v>
       </c>
       <c r="D586">
-        <v>52800.41031408894</v>
+        <v>55646.48846344915</v>
       </c>
     </row>
     <row r="587">
@@ -7991,7 +7991,7 @@
         <v>2024</v>
       </c>
       <c r="D587">
-        <v>100090.0699404067</v>
+        <v>100090.0699404065</v>
       </c>
     </row>
     <row r="588">
@@ -8017,7 +8017,7 @@
         <v>2026</v>
       </c>
       <c r="D589">
-        <v>129190.1869254891</v>
+        <v>165247.2154493271</v>
       </c>
     </row>
     <row r="590">
@@ -8030,7 +8030,7 @@
         <v>2027</v>
       </c>
       <c r="D590">
-        <v>164087.9933929206</v>
+        <v>205084.4938664131</v>
       </c>
     </row>
     <row r="591">
@@ -8043,7 +8043,7 @@
         <v>2028</v>
       </c>
       <c r="D591">
-        <v>203965.5052291364</v>
+        <v>250382.0559502545</v>
       </c>
     </row>
     <row r="592">
@@ -8056,7 +8056,7 @@
         <v>2024</v>
       </c>
       <c r="D592">
-        <v>71319.23918560837</v>
+        <v>71319.23918560824</v>
       </c>
     </row>
     <row r="593">
@@ -8082,7 +8082,7 @@
         <v>2026</v>
       </c>
       <c r="D594">
-        <v>72708.14242190265</v>
+        <v>74139.71378999873</v>
       </c>
     </row>
     <row r="595">
@@ -8095,7 +8095,7 @@
         <v>2027</v>
       </c>
       <c r="D595">
-        <v>74137.77027809781</v>
+        <v>75609.45624635683</v>
       </c>
     </row>
     <row r="596">
@@ -8108,7 +8108,7 @@
         <v>2028</v>
       </c>
       <c r="D596">
-        <v>75609.70284173691</v>
+        <v>77109.08926723071</v>
       </c>
     </row>
     <row r="597">
@@ -8121,7 +8121,7 @@
         <v>2024</v>
       </c>
       <c r="D597">
-        <v>65489.65177091752</v>
+        <v>65489.65177091741</v>
       </c>
     </row>
     <row r="598">
@@ -8147,7 +8147,7 @@
         <v>2026</v>
       </c>
       <c r="D599">
-        <v>67623.27173633623</v>
+        <v>69820.66106974312</v>
       </c>
     </row>
     <row r="600">
@@ -8160,7 +8160,7 @@
         <v>2027</v>
       </c>
       <c r="D600">
-        <v>69821.77304395409</v>
+        <v>72086.96870028313</v>
       </c>
     </row>
     <row r="601">
@@ -8173,7 +8173,7 @@
         <v>2028</v>
       </c>
       <c r="D601">
-        <v>72086.74639932447</v>
+        <v>74426.14982327986</v>
       </c>
     </row>
     <row r="602">
@@ -8212,7 +8212,7 @@
         <v>2026</v>
       </c>
       <c r="D604">
-        <v>69716.25630626579</v>
+        <v>78560.07909111925</v>
       </c>
     </row>
     <row r="605">
@@ -8225,7 +8225,7 @@
         <v>2027</v>
       </c>
       <c r="D605">
-        <v>74825.39854684728</v>
+        <v>81134.30678318065</v>
       </c>
     </row>
     <row r="606">
@@ -8238,7 +8238,7 @@
         <v>2028</v>
       </c>
       <c r="D606">
-        <v>84467.05091894977</v>
+        <v>94548.6979825439</v>
       </c>
     </row>
     <row r="607">
@@ -8277,7 +8277,7 @@
         <v>2026</v>
       </c>
       <c r="D609">
-        <v>62425.07306565712</v>
+        <v>67781.91274568439</v>
       </c>
     </row>
     <row r="610">
@@ -8290,7 +8290,7 @@
         <v>2027</v>
       </c>
       <c r="D610">
-        <v>67786.95417051406</v>
+        <v>73635.93774171062</v>
       </c>
     </row>
     <row r="611">
@@ -8303,7 +8303,7 @@
         <v>2028</v>
       </c>
       <c r="D611">
-        <v>73637.36044539372</v>
+        <v>80000.18588850059</v>
       </c>
     </row>
     <row r="612">
@@ -8316,7 +8316,7 @@
         <v>2024</v>
       </c>
       <c r="D612">
-        <v>60658.04314966587</v>
+        <v>60658.04314966576</v>
       </c>
     </row>
     <row r="613">
@@ -8342,7 +8342,7 @@
         <v>2026</v>
       </c>
       <c r="D614">
-        <v>65212.26265213275</v>
+        <v>70128.44801357595</v>
       </c>
     </row>
     <row r="615">
@@ -8355,7 +8355,7 @@
         <v>2027</v>
       </c>
       <c r="D615">
-        <v>70130.05347640732</v>
+        <v>75441.98358007084</v>
       </c>
     </row>
     <row r="616">
@@ -8368,7 +8368,7 @@
         <v>2028</v>
       </c>
       <c r="D616">
-        <v>75442.12196198967</v>
+        <v>81158.56499306399</v>
       </c>
     </row>
     <row r="617">
@@ -8381,7 +8381,7 @@
         <v>2024</v>
       </c>
       <c r="D617">
-        <v>49626.74070414465</v>
+        <v>49626.74070414455</v>
       </c>
     </row>
     <row r="618">
@@ -8407,7 +8407,7 @@
         <v>2026</v>
       </c>
       <c r="D619">
-        <v>52185.28880575826</v>
+        <v>54725.07485515117</v>
       </c>
     </row>
     <row r="620">
@@ -8420,7 +8420,7 @@
         <v>2027</v>
       </c>
       <c r="D620">
-        <v>54638.46393358325</v>
+        <v>56959.59906060217</v>
       </c>
     </row>
     <row r="621">
@@ -8433,7 +8433,7 @@
         <v>2028</v>
       </c>
       <c r="D621">
-        <v>56907.64906340119</v>
+        <v>59123.29722012053</v>
       </c>
     </row>
     <row r="622">
@@ -8446,7 +8446,7 @@
         <v>2024</v>
       </c>
       <c r="D622">
-        <v>49400.93075172626</v>
+        <v>49400.93075172635</v>
       </c>
     </row>
     <row r="623">
@@ -8472,7 +8472,7 @@
         <v>2026</v>
       </c>
       <c r="D624">
-        <v>52382.21009517887</v>
+        <v>55394.43845514459</v>
       </c>
     </row>
     <row r="625">
@@ -8485,7 +8485,7 @@
         <v>2027</v>
       </c>
       <c r="D625">
-        <v>55350.15917612628</v>
+        <v>58282.78548066413</v>
       </c>
     </row>
     <row r="626">
@@ -8498,7 +8498,7 @@
         <v>2028</v>
       </c>
       <c r="D626">
-        <v>58268.90950446868</v>
+        <v>61277.94710084998</v>
       </c>
     </row>
     <row r="627">
@@ -8511,7 +8511,7 @@
         <v>2024</v>
       </c>
       <c r="D627">
-        <v>58034.82397367044</v>
+        <v>58034.82397367034</v>
       </c>
     </row>
     <row r="628">
@@ -8537,7 +8537,7 @@
         <v>2026</v>
       </c>
       <c r="D629">
-        <v>62851.4020125247</v>
+        <v>68033.67026364466</v>
       </c>
     </row>
     <row r="630">
@@ -8550,7 +8550,7 @@
         <v>2027</v>
       </c>
       <c r="D630">
-        <v>68021.6621132625</v>
+        <v>73567.41246876599</v>
       </c>
     </row>
     <row r="631">
@@ -8563,7 +8563,7 @@
         <v>2028</v>
       </c>
       <c r="D631">
-        <v>73562.83270555998</v>
+        <v>79536.40389112067</v>
       </c>
     </row>
     <row r="632">
@@ -8576,7 +8576,7 @@
         <v>2024</v>
       </c>
       <c r="D632">
-        <v>34707.6809128891</v>
+        <v>34707.68091288897</v>
       </c>
     </row>
     <row r="633">
@@ -8602,7 +8602,7 @@
         <v>2026</v>
       </c>
       <c r="D634">
-        <v>38655.00458283955</v>
+        <v>42551.18481836062</v>
       </c>
     </row>
     <row r="635">
@@ -8615,7 +8615,7 @@
         <v>2027</v>
       </c>
       <c r="D635">
-        <v>42846.71204241036</v>
+        <v>47267.31261247693</v>
       </c>
     </row>
     <row r="636">
@@ -8628,7 +8628,7 @@
         <v>2028</v>
       </c>
       <c r="D636">
-        <v>47073.9148983604</v>
+        <v>51864.28381213889</v>
       </c>
     </row>
     <row r="637">
@@ -8641,7 +8641,7 @@
         <v>2024</v>
       </c>
       <c r="D637">
-        <v>59641.44884585789</v>
+        <v>59641.44884585778</v>
       </c>
     </row>
     <row r="638">
@@ -8667,7 +8667,7 @@
         <v>2026</v>
       </c>
       <c r="D639">
-        <v>63660.40877484971</v>
+        <v>67969.94803629542</v>
       </c>
     </row>
     <row r="640">
@@ -8680,7 +8680,7 @@
         <v>2027</v>
       </c>
       <c r="D640">
-        <v>67973.26174120113</v>
+        <v>72602.9466239865</v>
       </c>
     </row>
     <row r="641">
@@ -8693,7 +8693,7 @@
         <v>2028</v>
       </c>
       <c r="D641">
-        <v>72603.54008022022</v>
+        <v>77553.64351229083</v>
       </c>
     </row>
     <row r="642">
@@ -8706,7 +8706,7 @@
         <v>2024</v>
       </c>
       <c r="D642">
-        <v>44583.0595482791</v>
+        <v>44583.05954827894</v>
       </c>
     </row>
     <row r="643">
@@ -8732,7 +8732,7 @@
         <v>2026</v>
       </c>
       <c r="D644">
-        <v>47770.29869482583</v>
+        <v>51168.67617182888</v>
       </c>
     </row>
     <row r="645">
@@ -8745,7 +8745,7 @@
         <v>2027</v>
       </c>
       <c r="D645">
-        <v>51167.25873732541</v>
+        <v>54786.3603787664</v>
       </c>
     </row>
     <row r="646">
@@ -8758,7 +8758,7 @@
         <v>2028</v>
       </c>
       <c r="D646">
-        <v>54786.23167385747</v>
+        <v>58659.40560396439</v>
       </c>
     </row>
     <row r="647">
@@ -8771,7 +8771,7 @@
         <v>2024</v>
       </c>
       <c r="D647">
-        <v>31930.61154567494</v>
+        <v>31930.61154567483</v>
       </c>
     </row>
     <row r="648">
@@ -8797,7 +8797,7 @@
         <v>2026</v>
       </c>
       <c r="D649">
-        <v>31681.61475043946</v>
+        <v>32440.54379240262</v>
       </c>
     </row>
     <row r="650">
@@ -8810,7 +8810,7 @@
         <v>2027</v>
       </c>
       <c r="D650">
-        <v>31866.83751765249</v>
+        <v>32493.92759830844</v>
       </c>
     </row>
     <row r="651">
@@ -8823,7 +8823,7 @@
         <v>2028</v>
       </c>
       <c r="D651">
-        <v>32824.00355250052</v>
+        <v>33549.36610595004</v>
       </c>
     </row>
     <row r="652">
@@ -8862,7 +8862,7 @@
         <v>2026</v>
       </c>
       <c r="D654">
-        <v>22161.53020358783</v>
+        <v>22290.74028729888</v>
       </c>
     </row>
     <row r="655">
@@ -8875,7 +8875,7 @@
         <v>2027</v>
       </c>
       <c r="D655">
-        <v>22075.46600389663</v>
+        <v>22040.40877814201</v>
       </c>
     </row>
     <row r="656">
@@ -8888,7 +8888,7 @@
         <v>2028</v>
       </c>
       <c r="D656">
-        <v>22213.97444996025</v>
+        <v>22311.80302341483</v>
       </c>
     </row>
     <row r="657">
@@ -8901,7 +8901,7 @@
         <v>2024</v>
       </c>
       <c r="D657">
-        <v>23580.80967024457</v>
+        <v>23580.80967024461</v>
       </c>
     </row>
     <row r="658">
@@ -8927,7 +8927,7 @@
         <v>2026</v>
       </c>
       <c r="D659">
-        <v>24396.21427810435</v>
+        <v>25475.37096426547</v>
       </c>
     </row>
     <row r="660">
@@ -8940,7 +8940,7 @@
         <v>2027</v>
       </c>
       <c r="D660">
-        <v>25371.56785333119</v>
+        <v>26523.65143994015</v>
       </c>
     </row>
     <row r="661">
@@ -8953,7 +8953,7 @@
         <v>2028</v>
       </c>
       <c r="D661">
-        <v>26571.29299971156</v>
+        <v>27764.14067953611</v>
       </c>
     </row>
     <row r="662">
@@ -8966,7 +8966,7 @@
         <v>2024</v>
       </c>
       <c r="D662">
-        <v>106519.0966567703</v>
+        <v>106519.0966567701</v>
       </c>
     </row>
     <row r="663">
@@ -8992,7 +8992,7 @@
         <v>2026</v>
       </c>
       <c r="D664">
-        <v>127098.8711447209</v>
+        <v>150771.3484550508</v>
       </c>
     </row>
     <row r="665">
@@ -9005,7 +9005,7 @@
         <v>2027</v>
       </c>
       <c r="D665">
-        <v>150208.1890634143</v>
+        <v>175826.0523777193</v>
       </c>
     </row>
     <row r="666">
@@ -9018,7 +9018,7 @@
         <v>2028</v>
       </c>
       <c r="D666">
-        <v>175405.073337766</v>
+        <v>203574.9829579083</v>
       </c>
     </row>
     <row r="667">
@@ -9057,7 +9057,7 @@
         <v>2026</v>
       </c>
       <c r="D669">
-        <v>38688.96405601684</v>
+        <v>40244.86299556671</v>
       </c>
     </row>
     <row r="670">
@@ -9070,7 +9070,7 @@
         <v>2027</v>
       </c>
       <c r="D670">
-        <v>41608.64806171748</v>
+        <v>44472.71189380083</v>
       </c>
     </row>
     <row r="671">
@@ -9083,7 +9083,7 @@
         <v>2028</v>
       </c>
       <c r="D671">
-        <v>43240.06740527582</v>
+        <v>45170.51276126173</v>
       </c>
     </row>
     <row r="672">
@@ -9096,7 +9096,7 @@
         <v>2024</v>
       </c>
       <c r="D672">
-        <v>38891.74106835538</v>
+        <v>38891.7410683553</v>
       </c>
     </row>
     <row r="673">
@@ -9122,7 +9122,7 @@
         <v>2026</v>
       </c>
       <c r="D674">
-        <v>42028.25088383677</v>
+        <v>45416.32634097212</v>
       </c>
     </row>
     <row r="675">
@@ -9135,7 +9135,7 @@
         <v>2027</v>
       </c>
       <c r="D675">
-        <v>45416.44707271873</v>
+        <v>49076.42361740462</v>
       </c>
     </row>
     <row r="676">
@@ -9148,7 +9148,7 @@
         <v>2028</v>
       </c>
       <c r="D676">
-        <v>49076.41224543695</v>
+        <v>53031.4509083494</v>
       </c>
     </row>
     <row r="677">
@@ -9161,7 +9161,7 @@
         <v>2024</v>
       </c>
       <c r="D677">
-        <v>55719.97175323752</v>
+        <v>55719.97175323722</v>
       </c>
     </row>
     <row r="678">
@@ -9187,7 +9187,7 @@
         <v>2026</v>
       </c>
       <c r="D679">
-        <v>59816.17436598468</v>
+        <v>63903.01225622767</v>
       </c>
     </row>
     <row r="680">
@@ -9200,7 +9200,7 @@
         <v>2027</v>
       </c>
       <c r="D680">
-        <v>64063.53537443955</v>
+        <v>68452.24433924649</v>
       </c>
     </row>
     <row r="681">
@@ -9213,7 +9213,7 @@
         <v>2028</v>
       </c>
       <c r="D681">
-        <v>68363.41212171927</v>
+        <v>73040.23643885419</v>
       </c>
     </row>
     <row r="682">
@@ -9226,7 +9226,7 @@
         <v>2024</v>
       </c>
       <c r="D682">
-        <v>122221.0828841656</v>
+        <v>122221.0828841649</v>
       </c>
     </row>
     <row r="683">
@@ -9252,7 +9252,7 @@
         <v>2026</v>
       </c>
       <c r="D684">
-        <v>137943.9689341038</v>
+        <v>155461.3309751425</v>
       </c>
     </row>
     <row r="685">
@@ -9265,7 +9265,7 @@
         <v>2027</v>
       </c>
       <c r="D685">
-        <v>155529.0759153231</v>
+        <v>175175.2516171308</v>
       </c>
     </row>
     <row r="686">
@@ -9278,7 +9278,7 @@
         <v>2028</v>
       </c>
       <c r="D686">
-        <v>175152.5811860401</v>
+        <v>197312.4521260976</v>
       </c>
     </row>
     <row r="687">
@@ -9291,7 +9291,7 @@
         <v>2024</v>
       </c>
       <c r="D687">
-        <v>68726.66435327419</v>
+        <v>68726.66435327406</v>
       </c>
     </row>
     <row r="688">
@@ -9317,7 +9317,7 @@
         <v>2026</v>
       </c>
       <c r="D689">
-        <v>76990.78384519729</v>
+        <v>86307.09909657386</v>
       </c>
     </row>
     <row r="690">
@@ -9330,7 +9330,7 @@
         <v>2027</v>
       </c>
       <c r="D690">
-        <v>86336.59624343667</v>
+        <v>96915.62728292058</v>
       </c>
     </row>
     <row r="691">
@@ -9343,7 +9343,7 @@
         <v>2028</v>
       </c>
       <c r="D691">
-        <v>96932.32815848792</v>
+        <v>108884.3846486806</v>
       </c>
     </row>
     <row r="692">
@@ -9356,7 +9356,7 @@
         <v>2024</v>
       </c>
       <c r="D692">
-        <v>45496.48940420077</v>
+        <v>45496.48940420085</v>
       </c>
     </row>
     <row r="693">
@@ -9382,7 +9382,7 @@
         <v>2026</v>
       </c>
       <c r="D694">
-        <v>49446.46309718352</v>
+        <v>53742.02040680301</v>
       </c>
     </row>
     <row r="695">
@@ -9395,7 +9395,7 @@
         <v>2027</v>
       </c>
       <c r="D695">
-        <v>53742.1346380956</v>
+        <v>58413.99765233816</v>
       </c>
     </row>
     <row r="696">
@@ -9408,7 +9408,7 @@
         <v>2028</v>
       </c>
       <c r="D696">
-        <v>58414.00300506576</v>
+        <v>63492.14327859904</v>
       </c>
     </row>
     <row r="697">
@@ -9447,7 +9447,7 @@
         <v>2026</v>
       </c>
       <c r="D699">
-        <v>55319.20511276252</v>
+        <v>60679.33380238518</v>
       </c>
     </row>
     <row r="700">
@@ -9460,7 +9460,7 @@
         <v>2027</v>
       </c>
       <c r="D700">
-        <v>60601.93168305344</v>
+        <v>66040.41956511725</v>
       </c>
     </row>
     <row r="701">
@@ -9473,7 +9473,7 @@
         <v>2028</v>
       </c>
       <c r="D701">
-        <v>66013.45928113193</v>
+        <v>71787.17230810355</v>
       </c>
     </row>
     <row r="702">
@@ -9512,7 +9512,7 @@
         <v>2026</v>
       </c>
       <c r="D704">
-        <v>31960.69689788452</v>
+        <v>33356.33679754152</v>
       </c>
     </row>
     <row r="705">
@@ -9525,7 +9525,7 @@
         <v>2027</v>
       </c>
       <c r="D705">
-        <v>33352.2083251607</v>
+        <v>34822.66140941066</v>
       </c>
     </row>
     <row r="706">
@@ -9538,7 +9538,7 @@
         <v>2028</v>
       </c>
       <c r="D706">
-        <v>34823.48081610447</v>
+        <v>36356.01111641566</v>
       </c>
     </row>
     <row r="707">
@@ -9551,7 +9551,7 @@
         <v>2024</v>
       </c>
       <c r="D707">
-        <v>41331.71107393371</v>
+        <v>41331.71107393379</v>
       </c>
     </row>
     <row r="708">
@@ -9577,7 +9577,7 @@
         <v>2026</v>
       </c>
       <c r="D709">
-        <v>43017.65152375653</v>
+        <v>44771.71798933684</v>
       </c>
     </row>
     <row r="710">
@@ -9590,7 +9590,7 @@
         <v>2027</v>
       </c>
       <c r="D710">
-        <v>44771.91092478266</v>
+        <v>46597.23923072054</v>
       </c>
     </row>
     <row r="711">
@@ -9603,7 +9603,7 @@
         <v>2028</v>
       </c>
       <c r="D711">
-        <v>46597.1791012841</v>
+        <v>48497.00649985706</v>
       </c>
     </row>
     <row r="712">
@@ -9642,7 +9642,7 @@
         <v>2026</v>
       </c>
       <c r="D714">
-        <v>59315.70982101625</v>
+        <v>62565.33431219664</v>
       </c>
     </row>
     <row r="715">
@@ -9655,7 +9655,7 @@
         <v>2027</v>
       </c>
       <c r="D715">
-        <v>62589.95895187004</v>
+        <v>65927.21294610568</v>
       </c>
     </row>
     <row r="716">
@@ -9668,7 +9668,7 @@
         <v>2028</v>
       </c>
       <c r="D716">
-        <v>65922.52541973827</v>
+        <v>69454.92122566924</v>
       </c>
     </row>
     <row r="717">
@@ -9681,7 +9681,7 @@
         <v>2024</v>
       </c>
       <c r="D717">
-        <v>31925.92067771765</v>
+        <v>31925.92067771759</v>
       </c>
     </row>
     <row r="718">
@@ -9707,7 +9707,7 @@
         <v>2026</v>
       </c>
       <c r="D719">
-        <v>33126.42906377931</v>
+        <v>34609.72932056433</v>
       </c>
     </row>
     <row r="720">
@@ -9720,7 +9720,7 @@
         <v>2027</v>
       </c>
       <c r="D720">
-        <v>34457.91197408374</v>
+        <v>35932.41723393002</v>
       </c>
     </row>
     <row r="721">
@@ -9733,7 +9733,7 @@
         <v>2028</v>
       </c>
       <c r="D721">
-        <v>36033.34648464635</v>
+        <v>37620.89789292751</v>
       </c>
     </row>
     <row r="722">
@@ -9746,7 +9746,7 @@
         <v>2024</v>
       </c>
       <c r="D722">
-        <v>49459.8252722851</v>
+        <v>49459.82527228493</v>
       </c>
     </row>
     <row r="723">
@@ -9772,7 +9772,7 @@
         <v>2026</v>
       </c>
       <c r="D724">
-        <v>56560.15690880183</v>
+        <v>58998.63053000651</v>
       </c>
     </row>
     <row r="725">
@@ -9785,7 +9785,7 @@
         <v>2027</v>
       </c>
       <c r="D725">
-        <v>64240.50520088667</v>
+        <v>72468.22164740687</v>
       </c>
     </row>
     <row r="726">
@@ -9798,7 +9798,7 @@
         <v>2028</v>
       </c>
       <c r="D726">
-        <v>66976.25767388582</v>
+        <v>70270.50871379895</v>
       </c>
     </row>
     <row r="727">
@@ -9837,7 +9837,7 @@
         <v>2026</v>
       </c>
       <c r="D729">
-        <v>47227.26695316038</v>
+        <v>52177.31902255276</v>
       </c>
     </row>
     <row r="730">
@@ -9850,7 +9850,7 @@
         <v>2027</v>
       </c>
       <c r="D730">
-        <v>48459.20513054405</v>
+        <v>49941.0157703064</v>
       </c>
     </row>
     <row r="731">
@@ -9863,7 +9863,7 @@
         <v>2028</v>
       </c>
       <c r="D731">
-        <v>53551.43748881522</v>
+        <v>58935.1329614984</v>
       </c>
     </row>
     <row r="732">
@@ -9876,7 +9876,7 @@
         <v>2024</v>
       </c>
       <c r="D732">
-        <v>57556.25394626195</v>
+        <v>57556.25394626184</v>
       </c>
     </row>
     <row r="733">
@@ -9902,7 +9902,7 @@
         <v>2026</v>
       </c>
       <c r="D734">
-        <v>62037.0821218051</v>
+        <v>67159.81810721706</v>
       </c>
     </row>
     <row r="735">
@@ -9915,7 +9915,7 @@
         <v>2027</v>
       </c>
       <c r="D735">
-        <v>66988.89252405224</v>
+        <v>72468.09176106226</v>
       </c>
     </row>
     <row r="736">
@@ -9928,7 +9928,7 @@
         <v>2028</v>
       </c>
       <c r="D736">
-        <v>72575.77803400722</v>
+        <v>78545.03979489631</v>
       </c>
     </row>
     <row r="737">
@@ -9941,7 +9941,7 @@
         <v>2024</v>
       </c>
       <c r="D737">
-        <v>43322.7733513564</v>
+        <v>43322.77335135633</v>
       </c>
     </row>
     <row r="738">
@@ -9967,7 +9967,7 @@
         <v>2026</v>
       </c>
       <c r="D739">
-        <v>50199.32865550501</v>
+        <v>58197.44075976358</v>
       </c>
     </row>
     <row r="740">
@@ -9980,7 +9980,7 @@
         <v>2027</v>
       </c>
       <c r="D740">
-        <v>58200.44518233403</v>
+        <v>67515.18207581573</v>
       </c>
     </row>
     <row r="741">
@@ -9993,7 +9993,7 @@
         <v>2028</v>
       </c>
       <c r="D741">
-        <v>67515.53042276729</v>
+        <v>78325.95914371815</v>
       </c>
     </row>
     <row r="742">
@@ -10006,7 +10006,7 @@
         <v>2024</v>
       </c>
       <c r="D742">
-        <v>47108.46953987145</v>
+        <v>47108.46953987129</v>
       </c>
     </row>
     <row r="743">
@@ -10032,7 +10032,7 @@
         <v>2026</v>
       </c>
       <c r="D744">
-        <v>52123.86829573707</v>
+        <v>57698.26991566316</v>
       </c>
     </row>
     <row r="745">
@@ -10045,7 +10045,7 @@
         <v>2027</v>
       </c>
       <c r="D745">
-        <v>57694.06606790877</v>
+        <v>63882.59087471469</v>
       </c>
     </row>
     <row r="746">
@@ -10058,7 +10058,7 @@
         <v>2028</v>
       </c>
       <c r="D746">
-        <v>63883.37221159413</v>
+        <v>70732.36625873919</v>
       </c>
     </row>
     <row r="747">
@@ -10071,7 +10071,7 @@
         <v>2024</v>
       </c>
       <c r="D747">
-        <v>73140.70963701699</v>
+        <v>73140.70963701673</v>
       </c>
     </row>
     <row r="748">
@@ -10097,7 +10097,7 @@
         <v>2026</v>
       </c>
       <c r="D749">
-        <v>76297.41781712661</v>
+        <v>79590.36747682402</v>
       </c>
     </row>
     <row r="750">
@@ -10110,7 +10110,7 @@
         <v>2027</v>
       </c>
       <c r="D750">
-        <v>79590.36748354032</v>
+        <v>83025.43872636466</v>
       </c>
     </row>
     <row r="751">
@@ -10123,7 +10123,7 @@
         <v>2028</v>
       </c>
       <c r="D751">
-        <v>83025.43872593623</v>
+        <v>86608.76553442098</v>
       </c>
     </row>
     <row r="752">
@@ -10136,7 +10136,7 @@
         <v>2024</v>
       </c>
       <c r="D752">
-        <v>100121.8333687023</v>
+        <v>100121.8333687021</v>
       </c>
     </row>
     <row r="753">
@@ -10162,7 +10162,7 @@
         <v>2026</v>
       </c>
       <c r="D754">
-        <v>105175.1601321552</v>
+        <v>115275.5521706039</v>
       </c>
     </row>
     <row r="755">
@@ -10175,7 +10175,7 @@
         <v>2027</v>
       </c>
       <c r="D755">
-        <v>110687.4350147843</v>
+        <v>116703.5906938063</v>
       </c>
     </row>
     <row r="756">
@@ -10188,7 +10188,7 @@
         <v>2028</v>
       </c>
       <c r="D756">
-        <v>121326.9069481685</v>
+        <v>132754.7130967052</v>
       </c>
     </row>
     <row r="757">
@@ -10201,7 +10201,7 @@
         <v>2024</v>
       </c>
       <c r="D757">
-        <v>72501.94941045184</v>
+        <v>72501.94941045197</v>
       </c>
     </row>
     <row r="758">
@@ -10227,7 +10227,7 @@
         <v>2026</v>
       </c>
       <c r="D759">
-        <v>75367.80985320899</v>
+        <v>78307.4326903102</v>
       </c>
     </row>
     <row r="760">
@@ -10240,7 +10240,7 @@
         <v>2027</v>
       </c>
       <c r="D760">
-        <v>78318.788163445</v>
+        <v>81356.05391835395</v>
       </c>
     </row>
     <row r="761">
@@ -10253,7 +10253,7 @@
         <v>2028</v>
       </c>
       <c r="D761">
-        <v>81352.6637304005</v>
+        <v>84512.79628687013</v>
       </c>
     </row>
     <row r="762">
@@ -10266,7 +10266,7 @@
         <v>2024</v>
       </c>
       <c r="D762">
-        <v>60845.46406488895</v>
+        <v>60845.46406488885</v>
       </c>
     </row>
     <row r="763">
@@ -10292,7 +10292,7 @@
         <v>2026</v>
       </c>
       <c r="D764">
-        <v>64785.0382163477</v>
+        <v>68968.33042537219</v>
       </c>
     </row>
     <row r="765">
@@ -10305,7 +10305,7 @@
         <v>2027</v>
       </c>
       <c r="D765">
-        <v>68966.58044457431</v>
+        <v>73404.06800406404</v>
       </c>
     </row>
     <row r="766">
@@ -10318,7 +10318,7 @@
         <v>2028</v>
       </c>
       <c r="D766">
-        <v>73403.78101434208</v>
+        <v>78124.17624033109</v>
       </c>
     </row>
     <row r="767">
@@ -10331,7 +10331,7 @@
         <v>2024</v>
       </c>
       <c r="D767">
-        <v>50092.59973730775</v>
+        <v>50092.59973730766</v>
       </c>
     </row>
     <row r="768">
@@ -10357,7 +10357,7 @@
         <v>2026</v>
       </c>
       <c r="D769">
-        <v>55300.94720767012</v>
+        <v>60994.04370353738</v>
       </c>
     </row>
     <row r="770">
@@ -10370,7 +10370,7 @@
         <v>2027</v>
       </c>
       <c r="D770">
-        <v>61033.01827077683</v>
+        <v>67339.58016742853</v>
       </c>
     </row>
     <row r="771">
@@ -10383,7 +10383,7 @@
         <v>2028</v>
       </c>
       <c r="D771">
-        <v>67310.05884126907</v>
+        <v>74247.54181166459</v>
       </c>
     </row>
     <row r="772">
@@ -10422,7 +10422,7 @@
         <v>2026</v>
       </c>
       <c r="D774">
-        <v>94304.6876057154</v>
+        <v>112861.6932247942</v>
       </c>
     </row>
     <row r="775">
@@ -10435,7 +10435,7 @@
         <v>2027</v>
       </c>
       <c r="D775">
-        <v>112787.8637865303</v>
+        <v>135176.6896048796</v>
       </c>
     </row>
     <row r="776">
@@ -10448,7 +10448,7 @@
         <v>2028</v>
       </c>
       <c r="D776">
-        <v>135197.7356767623</v>
+        <v>161979.4372567242</v>
       </c>
     </row>
     <row r="777">
@@ -10487,7 +10487,7 @@
         <v>2026</v>
       </c>
       <c r="D779">
-        <v>41180.88777196481</v>
+        <v>44011.88300255658</v>
       </c>
     </row>
     <row r="780">
@@ -10500,7 +10500,7 @@
         <v>2027</v>
       </c>
       <c r="D780">
-        <v>44011.8830057068</v>
+        <v>47037.49455599157</v>
       </c>
     </row>
     <row r="781">
@@ -10513,7 +10513,7 @@
         <v>2028</v>
       </c>
       <c r="D781">
-        <v>47037.49455598397</v>
+        <v>50271.10278320393</v>
       </c>
     </row>
     <row r="782">
@@ -10526,7 +10526,7 @@
         <v>2024</v>
       </c>
       <c r="D782">
-        <v>44484.25794480482</v>
+        <v>44484.25794480459</v>
       </c>
     </row>
     <row r="783">
@@ -10552,7 +10552,7 @@
         <v>2026</v>
       </c>
       <c r="D784">
-        <v>50880.19803793559</v>
+        <v>54796.03244163607</v>
       </c>
     </row>
     <row r="785">
@@ -10565,7 +10565,7 @@
         <v>2027</v>
       </c>
       <c r="D785">
-        <v>57482.05087807302</v>
+        <v>64144.10289266341</v>
       </c>
     </row>
     <row r="786">
@@ -10578,7 +10578,7 @@
         <v>2028</v>
       </c>
       <c r="D786">
-        <v>61749.58118179013</v>
+        <v>66987.874700353</v>
       </c>
     </row>
     <row r="787">
@@ -10591,7 +10591,7 @@
         <v>2024</v>
       </c>
       <c r="D787">
-        <v>30644.49933893853</v>
+        <v>30644.49933893858</v>
       </c>
     </row>
     <row r="788">
@@ -10617,7 +10617,7 @@
         <v>2026</v>
       </c>
       <c r="D789">
-        <v>31592.77010770344</v>
+        <v>32569.72831336978</v>
       </c>
     </row>
     <row r="790">
@@ -10630,7 +10630,7 @@
         <v>2027</v>
       </c>
       <c r="D790">
-        <v>32569.95748836383</v>
+        <v>33576.92988019205</v>
       </c>
     </row>
     <row r="791">
@@ -10643,7 +10643,7 @@
         <v>2028</v>
       </c>
       <c r="D791">
-        <v>33576.84735171096</v>
+        <v>34615.0233797898</v>
       </c>
     </row>
     <row r="792">
@@ -10682,7 +10682,7 @@
         <v>2026</v>
       </c>
       <c r="D794">
-        <v>45392.38794073962</v>
+        <v>46858.84694032945</v>
       </c>
     </row>
     <row r="795">
@@ -10695,7 +10695,7 @@
         <v>2027</v>
       </c>
       <c r="D795">
-        <v>46856.37987963182</v>
+        <v>48352.19610155509</v>
       </c>
     </row>
     <row r="796">
@@ -10708,7 +10708,7 @@
         <v>2028</v>
       </c>
       <c r="D796">
-        <v>48351.69152554758</v>
+        <v>49891.57499991239</v>
       </c>
     </row>
     <row r="797">
@@ -10721,7 +10721,7 @@
         <v>2024</v>
       </c>
       <c r="D797">
-        <v>44350.93515774824</v>
+        <v>44350.93515774816</v>
       </c>
     </row>
     <row r="798">
@@ -10747,7 +10747,7 @@
         <v>2026</v>
       </c>
       <c r="D799">
-        <v>47587.57022570842</v>
+        <v>51098.61202704818</v>
       </c>
     </row>
     <row r="800">
@@ -10760,7 +10760,7 @@
         <v>2027</v>
       </c>
       <c r="D800">
-        <v>51078.19767633426</v>
+        <v>54843.96979471387</v>
       </c>
     </row>
     <row r="801">
@@ -10773,7 +10773,7 @@
         <v>2028</v>
       </c>
       <c r="D801">
-        <v>54855.67928938744</v>
+        <v>58901.56112524042</v>
       </c>
     </row>
     <row r="802">
@@ -10812,7 +10812,7 @@
         <v>2026</v>
       </c>
       <c r="D804">
-        <v>62946.57277167943</v>
+        <v>68067.10434274671</v>
       </c>
     </row>
     <row r="805">
@@ -10825,7 +10825,7 @@
         <v>2027</v>
       </c>
       <c r="D805">
-        <v>64898.68456240536</v>
+        <v>67740.17248520337</v>
       </c>
     </row>
     <row r="806">
@@ -10838,7 +10838,7 @@
         <v>2028</v>
       </c>
       <c r="D806">
-        <v>70233.99970041629</v>
+        <v>75137.82691015191</v>
       </c>
     </row>
     <row r="807">
@@ -10877,7 +10877,7 @@
         <v>2026</v>
       </c>
       <c r="D809">
-        <v>40347.27439723369</v>
+        <v>42600.77404381409</v>
       </c>
     </row>
     <row r="810">
@@ -10890,7 +10890,7 @@
         <v>2027</v>
       </c>
       <c r="D810">
-        <v>42782.51978302545</v>
+        <v>45149.32442518276</v>
       </c>
     </row>
     <row r="811">
@@ -10903,7 +10903,7 @@
         <v>2028</v>
       </c>
       <c r="D811">
-        <v>45058.67064000191</v>
+        <v>47562.68654460188</v>
       </c>
     </row>
     <row r="812">
@@ -10916,7 +10916,7 @@
         <v>2024</v>
       </c>
       <c r="D812">
-        <v>38195.36481812993</v>
+        <v>38195.36481812986</v>
       </c>
     </row>
     <row r="813">
@@ -10942,7 +10942,7 @@
         <v>2026</v>
       </c>
       <c r="D814">
-        <v>39853.9329563253</v>
+        <v>41582.01797151998</v>
       </c>
     </row>
     <row r="815">
@@ -10955,7 +10955,7 @@
         <v>2027</v>
       </c>
       <c r="D815">
-        <v>41581.70362416621</v>
+        <v>43381.43769164757</v>
       </c>
     </row>
     <row r="816">
@@ -10968,7 +10968,7 @@
         <v>2028</v>
       </c>
       <c r="D816">
-        <v>43381.39651321896</v>
+        <v>45258.59659697262</v>
       </c>
     </row>
     <row r="817">
@@ -10981,7 +10981,7 @@
         <v>2024</v>
       </c>
       <c r="D817">
-        <v>135206.5591223641</v>
+        <v>135206.5591223636</v>
       </c>
     </row>
     <row r="818">
@@ -11007,7 +11007,7 @@
         <v>2026</v>
       </c>
       <c r="D819">
-        <v>160412.6176286397</v>
+        <v>192399.8172589829</v>
       </c>
     </row>
     <row r="820">
@@ -11020,7 +11020,7 @@
         <v>2027</v>
       </c>
       <c r="D820">
-        <v>191230.4378711449</v>
+        <v>229062.1020032231</v>
       </c>
     </row>
     <row r="821">
@@ -11033,7 +11033,7 @@
         <v>2028</v>
       </c>
       <c r="D821">
-        <v>229845.8781780385</v>
+        <v>275519.4500747338</v>
       </c>
     </row>
     <row r="822">
@@ -11046,7 +11046,7 @@
         <v>2024</v>
       </c>
       <c r="D822">
-        <v>102326.9636510618</v>
+        <v>102326.963651062</v>
       </c>
     </row>
     <row r="823">
@@ -11072,7 +11072,7 @@
         <v>2026</v>
       </c>
       <c r="D824">
-        <v>108192.0062449362</v>
+        <v>114454.3369694304</v>
       </c>
     </row>
     <row r="825">
@@ -11085,7 +11085,7 @@
         <v>2027</v>
       </c>
       <c r="D825">
-        <v>114431.5033644198</v>
+        <v>121071.3474387922</v>
       </c>
     </row>
     <row r="826">
@@ -11098,7 +11098,7 @@
         <v>2028</v>
       </c>
       <c r="D826">
-        <v>121080.3701698635</v>
+        <v>128099.5459474895</v>
       </c>
     </row>
     <row r="827">
@@ -11111,7 +11111,7 @@
         <v>2024</v>
       </c>
       <c r="D827">
-        <v>41335.63010916683</v>
+        <v>41335.63010916676</v>
       </c>
     </row>
     <row r="828">
@@ -11137,7 +11137,7 @@
         <v>2026</v>
       </c>
       <c r="D829">
-        <v>45372.79689932288</v>
+        <v>48205.24492911835</v>
       </c>
     </row>
     <row r="830">
@@ -11150,7 +11150,7 @@
         <v>2027</v>
       </c>
       <c r="D830">
-        <v>49166.915034978</v>
+        <v>52596.49296512862</v>
       </c>
     </row>
     <row r="831">
@@ -11163,7 +11163,7 @@
         <v>2028</v>
       </c>
       <c r="D831">
-        <v>51971.34983951616</v>
+        <v>55365.714559825</v>
       </c>
     </row>
     <row r="832">
@@ -11202,7 +11202,7 @@
         <v>2026</v>
       </c>
       <c r="D834">
-        <v>53660.30017520483</v>
+        <v>57414.66318540816</v>
       </c>
     </row>
     <row r="835">
@@ -11215,7 +11215,7 @@
         <v>2027</v>
       </c>
       <c r="D835">
-        <v>57410.68687514441</v>
+        <v>61448.40773076336</v>
       </c>
     </row>
     <row r="836">
@@ -11228,7 +11228,7 @@
         <v>2028</v>
       </c>
       <c r="D836">
-        <v>61449.02220276602</v>
+        <v>65767.52138323149</v>
       </c>
     </row>
     <row r="837">
@@ -11241,7 +11241,7 @@
         <v>2024</v>
       </c>
       <c r="D837">
-        <v>85691.47955557628</v>
+        <v>85691.47955557659</v>
       </c>
     </row>
     <row r="838">
@@ -11267,7 +11267,7 @@
         <v>2026</v>
       </c>
       <c r="D839">
-        <v>100621.017044013</v>
+        <v>117819.7817171672</v>
       </c>
     </row>
     <row r="840">
@@ -11280,7 +11280,7 @@
         <v>2027</v>
       </c>
       <c r="D840">
-        <v>117883.0609202161</v>
+        <v>137792.5526343885</v>
       </c>
     </row>
     <row r="841">
@@ -11293,7 +11293,7 @@
         <v>2028</v>
       </c>
       <c r="D841">
-        <v>137778.4295726237</v>
+        <v>161101.5546373449</v>
       </c>
     </row>
     <row r="842">
@@ -11306,7 +11306,7 @@
         <v>2024</v>
       </c>
       <c r="D842">
-        <v>94439.62977106174</v>
+        <v>94439.62977106124</v>
       </c>
     </row>
     <row r="843">
@@ -11332,7 +11332,7 @@
         <v>2026</v>
       </c>
       <c r="D844">
-        <v>109326.9299270173</v>
+        <v>126562.9012913784</v>
       </c>
     </row>
     <row r="845">
@@ -11345,7 +11345,7 @@
         <v>2027</v>
       </c>
       <c r="D845">
-        <v>126562.8663363888</v>
+        <v>146518.2503685484</v>
       </c>
     </row>
     <row r="846">
@@ -11358,7 +11358,7 @@
         <v>2028</v>
       </c>
       <c r="D846">
-        <v>146518.2511278365</v>
+        <v>169619.9897897857</v>
       </c>
     </row>
     <row r="847">
@@ -11371,7 +11371,7 @@
         <v>2024</v>
       </c>
       <c r="D847">
-        <v>75297.13539637625</v>
+        <v>75297.13539637586</v>
       </c>
     </row>
     <row r="848">
@@ -11397,7 +11397,7 @@
         <v>2026</v>
       </c>
       <c r="D849">
-        <v>84033.97403233765</v>
+        <v>93590.42494859136</v>
       </c>
     </row>
     <row r="850">
@@ -11410,7 +11410,7 @@
         <v>2027</v>
       </c>
       <c r="D850">
-        <v>93520.89748039194</v>
+        <v>103786.2321174106</v>
       </c>
     </row>
     <row r="851">
@@ -11423,7 +11423,7 @@
         <v>2028</v>
       </c>
       <c r="D851">
-        <v>103758.573545792</v>
+        <v>115000.7871106979</v>
       </c>
     </row>
     <row r="852">
@@ -11462,7 +11462,7 @@
         <v>2026</v>
       </c>
       <c r="D854">
-        <v>27796.83309176828</v>
+        <v>29211.61272586993</v>
       </c>
     </row>
     <row r="855">
@@ -11475,7 +11475,7 @@
         <v>2027</v>
       </c>
       <c r="D855">
-        <v>29206.72173640156</v>
+        <v>30699.77708957656</v>
       </c>
     </row>
     <row r="856">
@@ -11488,7 +11488,7 @@
         <v>2028</v>
       </c>
       <c r="D856">
-        <v>30701.35024678715</v>
+        <v>32268.71506024647</v>
       </c>
     </row>
     <row r="857">
@@ -11501,7 +11501,7 @@
         <v>2024</v>
       </c>
       <c r="D857">
-        <v>32582.61100899266</v>
+        <v>32582.6110089926</v>
       </c>
     </row>
     <row r="858">
@@ -11527,7 +11527,7 @@
         <v>2026</v>
       </c>
       <c r="D859">
-        <v>33566.91054379502</v>
+        <v>34675.5597171733</v>
       </c>
     </row>
     <row r="860">
@@ -11540,7 +11540,7 @@
         <v>2027</v>
       </c>
       <c r="D860">
-        <v>34595.99967570321</v>
+        <v>35672.16130411202</v>
       </c>
     </row>
     <row r="861">
@@ -11553,7 +11553,7 @@
         <v>2028</v>
       </c>
       <c r="D861">
-        <v>35741.11562376971</v>
+        <v>36910.62594725708</v>
       </c>
     </row>
     <row r="862">
@@ -11566,7 +11566,7 @@
         <v>2024</v>
       </c>
       <c r="D862">
-        <v>38455.26352134695</v>
+        <v>38455.26352134682</v>
       </c>
     </row>
     <row r="863">
@@ -11592,7 +11592,7 @@
         <v>2026</v>
       </c>
       <c r="D864">
-        <v>39518.15976569234</v>
+        <v>40610.33375954521</v>
       </c>
     </row>
     <row r="865">
@@ -11605,7 +11605,7 @@
         <v>2027</v>
       </c>
       <c r="D865">
-        <v>40610.31011757875</v>
+        <v>41732.51629353721</v>
       </c>
     </row>
     <row r="866">
@@ -11618,7 +11618,7 @@
         <v>2028</v>
       </c>
       <c r="D866">
-        <v>41732.51057837314</v>
+        <v>42885.69040032964</v>
       </c>
     </row>
     <row r="867">
@@ -11631,7 +11631,7 @@
         <v>2024</v>
       </c>
       <c r="D867">
-        <v>50092.54729377281</v>
+        <v>50092.54729377272</v>
       </c>
     </row>
     <row r="868">
@@ -11657,7 +11657,7 @@
         <v>2026</v>
       </c>
       <c r="D869">
-        <v>54731.18523223929</v>
+        <v>62040.58790206074</v>
       </c>
     </row>
     <row r="870">
@@ -11670,7 +11670,7 @@
         <v>2027</v>
       </c>
       <c r="D870">
-        <v>60037.44963915976</v>
+        <v>66120.36823884134</v>
       </c>
     </row>
     <row r="871">
@@ -11683,7 +11683,7 @@
         <v>2028</v>
       </c>
       <c r="D871">
-        <v>68084.71809621004</v>
+        <v>76937.44550712797</v>
       </c>
     </row>
     <row r="872">
@@ -11722,7 +11722,7 @@
         <v>2026</v>
       </c>
       <c r="D874">
-        <v>48609.34686361155</v>
+        <v>51455.22178994053</v>
       </c>
     </row>
     <row r="875">
@@ -11735,7 +11735,7 @@
         <v>2027</v>
       </c>
       <c r="D875">
-        <v>51331.26080090526</v>
+        <v>54363.49091238466</v>
       </c>
     </row>
     <row r="876">
@@ -11748,7 +11748,7 @@
         <v>2028</v>
       </c>
       <c r="D876">
-        <v>54422.96509882477</v>
+        <v>57624.84991074384</v>
       </c>
     </row>
     <row r="877">
@@ -11761,7 +11761,7 @@
         <v>2024</v>
       </c>
       <c r="D877">
-        <v>67503.71388366746</v>
+        <v>67503.71388366721</v>
       </c>
     </row>
     <row r="878">
@@ -11787,7 +11787,7 @@
         <v>2026</v>
       </c>
       <c r="D879">
-        <v>72119.68546190282</v>
+        <v>77051.58548328318</v>
       </c>
     </row>
     <row r="880">
@@ -11800,7 +11800,7 @@
         <v>2027</v>
       </c>
       <c r="D880">
-        <v>77051.61159275309</v>
+        <v>82321.13993680193</v>
       </c>
     </row>
     <row r="881">
@@ -11813,7 +11813,7 @@
         <v>2028</v>
       </c>
       <c r="D881">
-        <v>82321.1425041952</v>
+        <v>87951.08721049053</v>
       </c>
     </row>
     <row r="882">
@@ -11826,7 +11826,7 @@
         <v>2024</v>
       </c>
       <c r="D882">
-        <v>18832.94670207547</v>
+        <v>18832.94670207541</v>
       </c>
     </row>
     <row r="883">
@@ -11852,7 +11852,7 @@
         <v>2026</v>
       </c>
       <c r="D884">
-        <v>17492.08045360662</v>
+        <v>16244.29973279845</v>
       </c>
     </row>
     <row r="885">
@@ -11865,7 +11865,7 @@
         <v>2027</v>
       </c>
       <c r="D885">
-        <v>16243.6176297377</v>
+        <v>15081.41713055232</v>
       </c>
     </row>
     <row r="886">
@@ -11878,7 +11878,7 @@
         <v>2028</v>
       </c>
       <c r="D886">
-        <v>15081.23571751189</v>
+        <v>14001.27666987228</v>
       </c>
     </row>
     <row r="887">
@@ -11917,7 +11917,7 @@
         <v>2026</v>
       </c>
       <c r="D889">
-        <v>45325.4707689269</v>
+        <v>47625.4211701233</v>
       </c>
     </row>
     <row r="890">
@@ -11930,7 +11930,7 @@
         <v>2027</v>
       </c>
       <c r="D890">
-        <v>47654.80001053155</v>
+        <v>50232.09758822898</v>
       </c>
     </row>
     <row r="891">
@@ -11943,7 +11943,7 @@
         <v>2028</v>
       </c>
       <c r="D891">
-        <v>50241.94575815366</v>
+        <v>53012.61258711426</v>
       </c>
     </row>
     <row r="892">
@@ -11956,7 +11956,7 @@
         <v>2024</v>
       </c>
       <c r="D892">
-        <v>35246.28848609493</v>
+        <v>35246.28848609481</v>
       </c>
     </row>
     <row r="893">
@@ -11982,7 +11982,7 @@
         <v>2026</v>
       </c>
       <c r="D894">
-        <v>38690.65373758001</v>
+        <v>42412.36177311977</v>
       </c>
     </row>
     <row r="895">
@@ -11995,7 +11995,7 @@
         <v>2027</v>
       </c>
       <c r="D895">
-        <v>42431.70234449091</v>
+        <v>46490.7503391459</v>
       </c>
     </row>
     <row r="896">
@@ -12008,7 +12008,7 @@
         <v>2028</v>
       </c>
       <c r="D896">
-        <v>46483.82890616434</v>
+        <v>50938.56066132572</v>
       </c>
     </row>
     <row r="897">
@@ -12021,7 +12021,7 @@
         <v>2024</v>
       </c>
       <c r="D897">
-        <v>34069.39880057824</v>
+        <v>34069.3988005783</v>
       </c>
     </row>
     <row r="898">
@@ -12047,7 +12047,7 @@
         <v>2026</v>
       </c>
       <c r="D899">
-        <v>36368.00186733863</v>
+        <v>38824.02638724035</v>
       </c>
     </row>
     <row r="900">
@@ -12060,7 +12060,7 @@
         <v>2027</v>
       </c>
       <c r="D900">
-        <v>38824.18166246497</v>
+        <v>41448.90665553486</v>
       </c>
     </row>
     <row r="901">
@@ -12073,7 +12073,7 @@
         <v>2028</v>
       </c>
       <c r="D901">
-        <v>41448.91766147098</v>
+        <v>44251.28950706401</v>
       </c>
     </row>
     <row r="902">
@@ -12086,7 +12086,7 @@
         <v>2024</v>
       </c>
       <c r="D902">
-        <v>45838.74311783342</v>
+        <v>45838.74311783351</v>
       </c>
     </row>
     <row r="903">
@@ -12112,7 +12112,7 @@
         <v>2026</v>
       </c>
       <c r="D904">
-        <v>48067.85185690089</v>
+        <v>50399.41478411267</v>
       </c>
     </row>
     <row r="905">
@@ -12125,7 +12125,7 @@
         <v>2027</v>
       </c>
       <c r="D905">
-        <v>50398.85109171199</v>
+        <v>52836.06521765098</v>
       </c>
     </row>
     <row r="906">
@@ -12138,7 +12138,7 @@
         <v>2028</v>
       </c>
       <c r="D906">
-        <v>52836.00919046266</v>
+        <v>55390.343695117</v>
       </c>
     </row>
     <row r="907">
@@ -12151,7 +12151,7 @@
         <v>2024</v>
       </c>
       <c r="D907">
-        <v>49365.08783086486</v>
+        <v>49365.08783086468</v>
       </c>
     </row>
     <row r="908">
@@ -12177,7 +12177,7 @@
         <v>2026</v>
       </c>
       <c r="D909">
-        <v>52697.98825198926</v>
+        <v>55956.05732519522</v>
       </c>
     </row>
     <row r="910">
@@ -12190,7 +12190,7 @@
         <v>2027</v>
       </c>
       <c r="D910">
-        <v>55806.93337685849</v>
+        <v>58627.62217983959</v>
       </c>
     </row>
     <row r="911">
@@ -12203,7 +12203,7 @@
         <v>2028</v>
       </c>
       <c r="D911">
-        <v>58549.55443291154</v>
+        <v>61181.67974301552</v>
       </c>
     </row>
     <row r="912">
@@ -12242,7 +12242,7 @@
         <v>2026</v>
       </c>
       <c r="D914">
-        <v>58129.80177203244</v>
+        <v>61221.66215032227</v>
       </c>
     </row>
     <row r="915">
@@ -12255,7 +12255,7 @@
         <v>2027</v>
       </c>
       <c r="D915">
-        <v>61087.99513810786</v>
+        <v>63718.17357319986</v>
       </c>
     </row>
     <row r="916">
@@ -12268,7 +12268,7 @@
         <v>2028</v>
       </c>
       <c r="D916">
-        <v>63660.72924143935</v>
+        <v>66137.28955015349</v>
       </c>
     </row>
     <row r="917">
@@ -12281,7 +12281,7 @@
         <v>2024</v>
       </c>
       <c r="D917">
-        <v>26435.77692405094</v>
+        <v>26435.77692405084</v>
       </c>
     </row>
     <row r="918">
@@ -12307,7 +12307,7 @@
         <v>2026</v>
       </c>
       <c r="D919">
-        <v>26598.92522327929</v>
+        <v>26766.16316415018</v>
       </c>
     </row>
     <row r="920">
@@ -12320,7 +12320,7 @@
         <v>2027</v>
       </c>
       <c r="D920">
-        <v>26765.95268359675</v>
+        <v>26936.9196284389</v>
       </c>
     </row>
     <row r="921">
@@ -12333,7 +12333,7 @@
         <v>2028</v>
       </c>
       <c r="D921">
-        <v>26936.93409025408</v>
+        <v>27108.8091068543</v>
       </c>
     </row>
     <row r="922">
@@ -12346,7 +12346,7 @@
         <v>2024</v>
       </c>
       <c r="D922">
-        <v>46939.81569755397</v>
+        <v>46939.81569755389</v>
       </c>
     </row>
     <row r="923">
@@ -12372,7 +12372,7 @@
         <v>2026</v>
       </c>
       <c r="D924">
-        <v>49121.08354100351</v>
+        <v>51485.96240349488</v>
       </c>
     </row>
     <row r="925">
@@ -12385,7 +12385,7 @@
         <v>2027</v>
       </c>
       <c r="D925">
-        <v>51456.76180860565</v>
+        <v>53959.12802732814</v>
       </c>
     </row>
     <row r="926">
@@ -12398,7 +12398,7 @@
         <v>2028</v>
       </c>
       <c r="D926">
-        <v>53969.99162065534</v>
+        <v>56585.25713832514</v>
       </c>
     </row>
     <row r="927">
@@ -12437,7 +12437,7 @@
         <v>2026</v>
       </c>
       <c r="D929">
-        <v>42564.23148368297</v>
+        <v>42870.51091617309</v>
       </c>
     </row>
     <row r="930">
@@ -12450,7 +12450,7 @@
         <v>2027</v>
       </c>
       <c r="D930">
-        <v>42870.511072899</v>
+        <v>43178.99628982475</v>
       </c>
     </row>
     <row r="931">
@@ -12463,7 +12463,7 @@
         <v>2028</v>
       </c>
       <c r="D931">
-        <v>43178.99630566825</v>
+        <v>43489.70149421893</v>
       </c>
     </row>
     <row r="932">
@@ -12502,7 +12502,7 @@
         <v>2026</v>
       </c>
       <c r="D934">
-        <v>27688.19190663528</v>
+        <v>26852.25328375745</v>
       </c>
     </row>
     <row r="935">
@@ -12515,7 +12515,7 @@
         <v>2027</v>
       </c>
       <c r="D935">
-        <v>26993.7169250515</v>
+        <v>26245.01542654597</v>
       </c>
     </row>
     <row r="936">
@@ -12528,7 +12528,7 @@
         <v>2028</v>
       </c>
       <c r="D936">
-        <v>26154.3777314155</v>
+        <v>25386.66240107343</v>
       </c>
     </row>
     <row r="937">
@@ -12567,7 +12567,7 @@
         <v>2026</v>
       </c>
       <c r="D939">
-        <v>74408.01963591926</v>
+        <v>78520.73936635899</v>
       </c>
     </row>
     <row r="940">
@@ -12580,7 +12580,7 @@
         <v>2027</v>
       </c>
       <c r="D940">
-        <v>78846.88555954832</v>
+        <v>83356.32842392653</v>
       </c>
     </row>
     <row r="941">
@@ -12593,7 +12593,7 @@
         <v>2028</v>
       </c>
       <c r="D941">
-        <v>83135.34885401976</v>
+        <v>87787.80961039511</v>
       </c>
     </row>
     <row r="942">
@@ -12632,7 +12632,7 @@
         <v>2026</v>
       </c>
       <c r="D944">
-        <v>74091.3147422464</v>
+        <v>79145.0909099964</v>
       </c>
     </row>
     <row r="945">
@@ -12645,7 +12645,7 @@
         <v>2027</v>
       </c>
       <c r="D945">
-        <v>79896.16133084112</v>
+        <v>86112.69839544244</v>
       </c>
     </row>
     <row r="946">
@@ -12658,7 +12658,7 @@
         <v>2028</v>
       </c>
       <c r="D946">
-        <v>85343.73778652339</v>
+        <v>91206.08169229855</v>
       </c>
     </row>
     <row r="947">
@@ -12671,7 +12671,7 @@
         <v>2024</v>
       </c>
       <c r="D947">
-        <v>78346.43263709643</v>
+        <v>78346.43263709657</v>
       </c>
     </row>
     <row r="948">
@@ -12697,7 +12697,7 @@
         <v>2026</v>
       </c>
       <c r="D949">
-        <v>82934.54984750936</v>
+        <v>88316.6503062023</v>
       </c>
     </row>
     <row r="950">
@@ -12710,7 +12710,7 @@
         <v>2027</v>
       </c>
       <c r="D950">
-        <v>88167.6156662358</v>
+        <v>94132.59688508329</v>
       </c>
     </row>
     <row r="951">
@@ -12723,7 +12723,7 @@
         <v>2028</v>
       </c>
       <c r="D951">
-        <v>94177.61752345196</v>
+        <v>100475.5680374655</v>
       </c>
     </row>
     <row r="952">
@@ -12762,7 +12762,7 @@
         <v>2026</v>
       </c>
       <c r="D954">
-        <v>67353.41175042384</v>
+        <v>69690.45581879212</v>
       </c>
     </row>
     <row r="955">
@@ -12775,7 +12775,7 @@
         <v>2027</v>
       </c>
       <c r="D955">
-        <v>69419.04858094646</v>
+        <v>72025.66177966846</v>
       </c>
     </row>
     <row r="956">
@@ -12788,7 +12788,7 @@
         <v>2028</v>
       </c>
       <c r="D956">
-        <v>72129.63285231005</v>
+        <v>74761.94688469077</v>
       </c>
     </row>
     <row r="957">
@@ -12801,7 +12801,7 @@
         <v>2024</v>
       </c>
       <c r="D957">
-        <v>79812.45602593833</v>
+        <v>79812.45602593804</v>
       </c>
     </row>
     <row r="958">
@@ -12827,7 +12827,7 @@
         <v>2026</v>
       </c>
       <c r="D959">
-        <v>83805.70418429072</v>
+        <v>88135.55766829159</v>
       </c>
     </row>
     <row r="960">
@@ -12840,7 +12840,7 @@
         <v>2027</v>
       </c>
       <c r="D960">
-        <v>88108.50932918598</v>
+        <v>92747.77449747533</v>
       </c>
     </row>
     <row r="961">
@@ -12853,7 +12853,7 @@
         <v>2028</v>
       </c>
       <c r="D961">
-        <v>92753.3994636571</v>
+        <v>97619.1120367472</v>
       </c>
     </row>
     <row r="962">
@@ -12892,7 +12892,7 @@
         <v>2026</v>
       </c>
       <c r="D964">
-        <v>42176.46103812353</v>
+        <v>42609.60667580227</v>
       </c>
     </row>
     <row r="965">
@@ -12905,7 +12905,7 @@
         <v>2027</v>
       </c>
       <c r="D965">
-        <v>42629.56090419812</v>
+        <v>43024.73750940362</v>
       </c>
     </row>
     <row r="966">
@@ -12918,7 +12918,7 @@
         <v>2028</v>
       </c>
       <c r="D966">
-        <v>43019.84235788081</v>
+        <v>43429.08597794577</v>
       </c>
     </row>
     <row r="967">
@@ -12931,7 +12931,7 @@
         <v>2024</v>
       </c>
       <c r="D967">
-        <v>82240.35411922089</v>
+        <v>82240.35411922031</v>
       </c>
     </row>
     <row r="968">
@@ -12957,7 +12957,7 @@
         <v>2026</v>
       </c>
       <c r="D969">
-        <v>85883.8489952114</v>
+        <v>89688.76172763373</v>
       </c>
     </row>
     <row r="970">
@@ -12970,7 +12970,7 @@
         <v>2027</v>
       </c>
       <c r="D970">
-        <v>89688.76172762146</v>
+        <v>93662.24361994644</v>
       </c>
     </row>
     <row r="971">
@@ -12983,7 +12983,7 @@
         <v>2028</v>
       </c>
       <c r="D971">
-        <v>93662.24361994644</v>
+        <v>97811.76271072667</v>
       </c>
     </row>
     <row r="972">
@@ -12996,7 +12996,7 @@
         <v>2024</v>
       </c>
       <c r="D972">
-        <v>40585.07116588888</v>
+        <v>40585.07116588896</v>
       </c>
     </row>
     <row r="973">
@@ -13022,7 +13022,7 @@
         <v>2026</v>
       </c>
       <c r="D974">
-        <v>42360.66985731878</v>
+        <v>44213.65311024124</v>
       </c>
     </row>
     <row r="975">
@@ -13035,7 +13035,7 @@
         <v>2027</v>
       </c>
       <c r="D975">
-        <v>44213.63903403688</v>
+        <v>46147.33636185129</v>
       </c>
     </row>
     <row r="976">
@@ -13048,7 +13048,7 @@
         <v>2028</v>
       </c>
       <c r="D976">
-        <v>46147.33566778144</v>
+        <v>48165.5870392701</v>
       </c>
     </row>
     <row r="977">
@@ -13061,7 +13061,7 @@
         <v>2024</v>
       </c>
       <c r="D977">
-        <v>39943.547604812</v>
+        <v>39943.54760481186</v>
       </c>
     </row>
     <row r="978">
@@ -13087,7 +13087,7 @@
         <v>2026</v>
       </c>
       <c r="D979">
-        <v>39875.39868566982</v>
+        <v>39805.02601277824</v>
       </c>
     </row>
     <row r="980">
@@ -13100,7 +13100,7 @@
         <v>2027</v>
       </c>
       <c r="D980">
-        <v>39804.85853332666</v>
+        <v>39731.94025683151</v>
       </c>
     </row>
     <row r="981">
@@ -13113,7 +13113,7 @@
         <v>2028</v>
       </c>
       <c r="D981">
-        <v>39731.92829165792</v>
+        <v>39658.95286357563</v>
       </c>
     </row>
     <row r="982">
@@ -13126,7 +13126,7 @@
         <v>2024</v>
       </c>
       <c r="D982">
-        <v>99074.06118973985</v>
+        <v>99074.06118973967</v>
       </c>
     </row>
     <row r="983">
@@ -13152,7 +13152,7 @@
         <v>2026</v>
       </c>
       <c r="D984">
-        <v>103668.2003089534</v>
+        <v>108590.0702574666</v>
       </c>
     </row>
     <row r="985">
@@ -13165,7 +13165,7 @@
         <v>2027</v>
       </c>
       <c r="D985">
-        <v>108555.0561820929</v>
+        <v>113755.7760194834</v>
       </c>
     </row>
     <row r="986">
@@ -13178,7 +13178,7 @@
         <v>2028</v>
       </c>
       <c r="D986">
-        <v>113766.9716381958</v>
+        <v>119202.4060950152</v>
       </c>
     </row>
     <row r="987">
@@ -13217,7 +13217,7 @@
         <v>2026</v>
       </c>
       <c r="D989">
-        <v>89096.34816337297</v>
+        <v>95440.38939998257</v>
       </c>
     </row>
     <row r="990">
@@ -13230,7 +13230,7 @@
         <v>2027</v>
       </c>
       <c r="D990">
-        <v>95235.12791887719</v>
+        <v>101274.7582560045</v>
       </c>
     </row>
     <row r="991">
@@ -13243,7 +13243,7 @@
         <v>2028</v>
       </c>
       <c r="D991">
-        <v>101117.831497768</v>
+        <v>106967.002181627</v>
       </c>
     </row>
     <row r="992">
@@ -13256,7 +13256,7 @@
         <v>2024</v>
       </c>
       <c r="D992">
-        <v>74693.73129582603</v>
+        <v>74693.7312958259</v>
       </c>
     </row>
     <row r="993">
@@ -13282,7 +13282,7 @@
         <v>2026</v>
       </c>
       <c r="D994">
-        <v>80682.7597661676</v>
+        <v>87054.20125292023</v>
       </c>
     </row>
     <row r="995">
@@ -13295,7 +13295,7 @@
         <v>2027</v>
       </c>
       <c r="D995">
-        <v>87076.07951481764</v>
+        <v>93894.14726828987</v>
       </c>
     </row>
     <row r="996">
@@ -13308,7 +13308,7 @@
         <v>2028</v>
       </c>
       <c r="D996">
-        <v>93888.86665699389</v>
+        <v>101254.4299131399</v>
       </c>
     </row>
     <row r="997">
@@ -13321,7 +13321,7 @@
         <v>2024</v>
       </c>
       <c r="D997">
-        <v>66512.10170414424</v>
+        <v>66512.10170414412</v>
       </c>
     </row>
     <row r="998">
@@ -13347,7 +13347,7 @@
         <v>2026</v>
       </c>
       <c r="D999">
-        <v>70445.97786713662</v>
+        <v>74234.62911579473</v>
       </c>
     </row>
     <row r="1000">
@@ -13360,7 +13360,7 @@
         <v>2027</v>
       </c>
       <c r="D1000">
-        <v>74338.17221223137</v>
+        <v>78156.96767736513</v>
       </c>
     </row>
     <row r="1001">
@@ -13373,7 +13373,7 @@
         <v>2028</v>
       </c>
       <c r="D1001">
-        <v>78127.06935690304</v>
+        <v>82192.15296667226</v>
       </c>
     </row>
     <row r="1002">
@@ -13386,7 +13386,7 @@
         <v>2024</v>
       </c>
       <c r="D1002">
-        <v>55843.92564386366</v>
+        <v>55843.92564386356</v>
       </c>
     </row>
     <row r="1003">
@@ -13412,7 +13412,7 @@
         <v>2026</v>
       </c>
       <c r="D1004">
-        <v>56189.52713233895</v>
+        <v>56537.63997619472</v>
       </c>
     </row>
     <row r="1005">
@@ -13425,7 +13425,7 @@
         <v>2027</v>
       </c>
       <c r="D1005">
-        <v>56537.54454563934</v>
+        <v>56887.99626908291</v>
       </c>
     </row>
     <row r="1006">
@@ -13438,7 +13438,7 @@
         <v>2028</v>
       </c>
       <c r="D1006">
-        <v>56888.02086684847</v>
+        <v>57240.59792429325</v>
       </c>
     </row>
     <row r="1007">
@@ -13477,7 +13477,7 @@
         <v>2026</v>
       </c>
       <c r="D1009">
-        <v>89714.05950274457</v>
+        <v>97920.55023825828</v>
       </c>
     </row>
     <row r="1010">
@@ -13490,7 +13490,7 @@
         <v>2027</v>
       </c>
       <c r="D1010">
-        <v>97851.71279266928</v>
+        <v>106849.546865241</v>
       </c>
     </row>
     <row r="1011">
@@ -13503,7 +13503,7 @@
         <v>2028</v>
       </c>
       <c r="D1011">
-        <v>106878.1746211014</v>
+        <v>116686.4839361607</v>
       </c>
     </row>
     <row r="1012">
@@ -13516,7 +13516,7 @@
         <v>2024</v>
       </c>
       <c r="D1012">
-        <v>82539.87023574361</v>
+        <v>82539.87023574376</v>
       </c>
     </row>
     <row r="1013">
@@ -13542,7 +13542,7 @@
         <v>2026</v>
       </c>
       <c r="D1014">
-        <v>84424.64866834129</v>
+        <v>86007.39496463267</v>
       </c>
     </row>
     <row r="1015">
@@ -13555,7 +13555,7 @@
         <v>2027</v>
       </c>
       <c r="D1015">
-        <v>86321.15646087483</v>
+        <v>88228.26640723676</v>
       </c>
     </row>
     <row r="1016">
@@ -13568,7 +13568,7 @@
         <v>2028</v>
       </c>
       <c r="D1016">
-        <v>87936.5692528137</v>
+        <v>89611.76157028123</v>
       </c>
     </row>
     <row r="1017">
@@ -13581,7 +13581,7 @@
         <v>2024</v>
       </c>
       <c r="D1017">
-        <v>96149.68965910863</v>
+        <v>96149.68965910829</v>
       </c>
     </row>
     <row r="1018">
@@ -13607,7 +13607,7 @@
         <v>2026</v>
       </c>
       <c r="D1019">
-        <v>99572.39910267288</v>
+        <v>104540.1731532233</v>
       </c>
     </row>
     <row r="1020">
@@ -13620,7 +13620,7 @@
         <v>2027</v>
       </c>
       <c r="D1020">
-        <v>103219.7851129209</v>
+        <v>107107.485836128</v>
       </c>
     </row>
     <row r="1021">
@@ -13633,7 +13633,7 @@
         <v>2028</v>
       </c>
       <c r="D1021">
-        <v>108377.3863577081</v>
+        <v>113687.5689230735</v>
       </c>
     </row>
     <row r="1022">
@@ -13646,7 +13646,7 @@
         <v>2024</v>
       </c>
       <c r="D1022">
-        <v>54501.31683810545</v>
+        <v>54501.31683810555</v>
       </c>
     </row>
     <row r="1023">
@@ -13672,7 +13672,7 @@
         <v>2026</v>
       </c>
       <c r="D1024">
-        <v>51549.14418264663</v>
+        <v>41274.78064151917</v>
       </c>
     </row>
     <row r="1025">
@@ -13685,7 +13685,7 @@
         <v>2027</v>
       </c>
       <c r="D1025">
-        <v>48577.99007219791</v>
+        <v>45610.12289117277</v>
       </c>
     </row>
     <row r="1026">
@@ -13698,7 +13698,7 @@
         <v>2028</v>
       </c>
       <c r="D1026">
-        <v>38892.6587403843</v>
+        <v>31250.49368943677</v>
       </c>
     </row>
     <row r="1027">
@@ -13737,7 +13737,7 @@
         <v>2026</v>
       </c>
       <c r="D1029">
-        <v>58489.50964323614</v>
+        <v>60702.5480194045</v>
       </c>
     </row>
     <row r="1030">
@@ -13750,7 +13750,7 @@
         <v>2027</v>
       </c>
       <c r="D1030">
-        <v>60702.60332064174</v>
+        <v>62998.64081831115</v>
       </c>
     </row>
     <row r="1031">
@@ -13763,7 +13763,7 @@
         <v>2028</v>
       </c>
       <c r="D1031">
-        <v>62998.63694935375</v>
+        <v>65381.57199708919</v>
       </c>
     </row>
     <row r="1032">
@@ -13802,7 +13802,7 @@
         <v>2026</v>
       </c>
       <c r="D1034">
-        <v>35341.77984863238</v>
+        <v>35757.60701207263</v>
       </c>
     </row>
     <row r="1035">
@@ -13815,7 +13815,7 @@
         <v>2027</v>
       </c>
       <c r="D1035">
-        <v>35704.13119184947</v>
+        <v>36098.25613102834</v>
       </c>
     </row>
     <row r="1036">
@@ -13828,7 +13828,7 @@
         <v>2028</v>
       </c>
       <c r="D1036">
-        <v>36133.82721991666</v>
+        <v>36549.98655940922</v>
       </c>
     </row>
     <row r="1037">
@@ -13867,7 +13867,7 @@
         <v>2026</v>
       </c>
       <c r="D1039">
-        <v>88442.5412447644</v>
+        <v>91639.7567051017</v>
       </c>
     </row>
     <row r="1040">
@@ -13880,7 +13880,7 @@
         <v>2027</v>
       </c>
       <c r="D1040">
-        <v>91639.81041808378</v>
+        <v>94952.89377033217</v>
       </c>
     </row>
     <row r="1041">
@@ -13893,7 +13893,7 @@
         <v>2028</v>
       </c>
       <c r="D1041">
-        <v>94952.9115040098</v>
+        <v>98385.86887530463</v>
       </c>
     </row>
     <row r="1042">
@@ -13906,7 +13906,7 @@
         <v>2024</v>
       </c>
       <c r="D1042">
-        <v>86684.27987790425</v>
+        <v>86684.27987790393</v>
       </c>
     </row>
     <row r="1043">
@@ -13932,7 +13932,7 @@
         <v>2026</v>
       </c>
       <c r="D1044">
-        <v>92270.60738248887</v>
+        <v>95978.01521928333</v>
       </c>
     </row>
     <row r="1045">
@@ -13945,7 +13945,7 @@
         <v>2027</v>
       </c>
       <c r="D1045">
-        <v>98073.22956518555</v>
+        <v>104088.2335130328</v>
       </c>
     </row>
     <row r="1046">
@@ -13958,7 +13958,7 @@
         <v>2028</v>
       </c>
       <c r="D1046">
-        <v>102004.2999934945</v>
+        <v>106238.5260501547</v>
       </c>
     </row>
     <row r="1047">
@@ -13997,7 +13997,7 @@
         <v>2026</v>
       </c>
       <c r="D1049">
-        <v>119845.1004543074</v>
+        <v>140242.5790633125</v>
       </c>
     </row>
     <row r="1050">
@@ -14010,7 +14010,7 @@
         <v>2027</v>
       </c>
       <c r="D1050">
-        <v>125278.2124812404</v>
+        <v>132468.8828265839</v>
       </c>
     </row>
     <row r="1051">
@@ -14023,7 +14023,7 @@
         <v>2028</v>
       </c>
       <c r="D1051">
-        <v>146755.7387447453</v>
+        <v>170134.1576609833</v>
       </c>
     </row>
     <row r="1052">
@@ -14036,7 +14036,7 @@
         <v>2024</v>
       </c>
       <c r="D1052">
-        <v>96057.46450593241</v>
+        <v>96057.46450593189</v>
       </c>
     </row>
     <row r="1053">
@@ -14062,7 +14062,7 @@
         <v>2026</v>
       </c>
       <c r="D1054">
-        <v>99616.16238346955</v>
+        <v>108245.1027872165</v>
       </c>
     </row>
     <row r="1055">
@@ -14075,7 +14075,7 @@
         <v>2027</v>
       </c>
       <c r="D1055">
-        <v>103916.7315987447</v>
+        <v>109043.0861768665</v>
       </c>
     </row>
     <row r="1056">
@@ -14088,7 +14088,7 @@
         <v>2028</v>
       </c>
       <c r="D1056">
-        <v>113002.0514062291</v>
+        <v>122251.0480820044</v>
       </c>
     </row>
     <row r="1057">
@@ -14101,7 +14101,7 @@
         <v>2024</v>
       </c>
       <c r="D1057">
-        <v>61412.75455296961</v>
+        <v>61412.7545529695</v>
       </c>
     </row>
     <row r="1058">
@@ -14127,7 +14127,7 @@
         <v>2026</v>
       </c>
       <c r="D1059">
-        <v>61000.99924811172</v>
+        <v>60591.97720584594</v>
       </c>
     </row>
     <row r="1060">
@@ -14140,7 +14140,7 @@
         <v>2027</v>
       </c>
       <c r="D1060">
-        <v>60591.98500829133</v>
+        <v>60185.69371880092</v>
       </c>
     </row>
     <row r="1061">
@@ -14153,7 +14153,7 @@
         <v>2028</v>
       </c>
       <c r="D1061">
-        <v>60185.69151519026</v>
+        <v>59782.12789178247</v>
       </c>
     </row>
     <row r="1062">
@@ -14166,7 +14166,7 @@
         <v>2024</v>
       </c>
       <c r="D1062">
-        <v>141380.3214315736</v>
+        <v>141380.3214315731</v>
       </c>
     </row>
     <row r="1063">
@@ -14192,7 +14192,7 @@
         <v>2026</v>
       </c>
       <c r="D1064">
-        <v>150265.0599463685</v>
+        <v>163488.0947600093</v>
       </c>
     </row>
     <row r="1065">
@@ -14205,7 +14205,7 @@
         <v>2027</v>
       </c>
       <c r="D1065">
-        <v>159994.2522071573</v>
+        <v>170658.5614906384</v>
       </c>
     </row>
     <row r="1066">
@@ -14218,7 +14218,7 @@
         <v>2028</v>
       </c>
       <c r="D1066">
-        <v>174097.2785395731</v>
+        <v>189130.5710097758</v>
       </c>
     </row>
     <row r="1067">
@@ -14257,7 +14257,7 @@
         <v>2026</v>
       </c>
       <c r="D1069">
-        <v>104556.1343311466</v>
+        <v>112015.5223169806</v>
       </c>
     </row>
     <row r="1070">
@@ -14270,7 +14270,7 @@
         <v>2027</v>
       </c>
       <c r="D1070">
-        <v>110059.7131713839</v>
+        <v>115964.8529215976</v>
       </c>
     </row>
     <row r="1071">
@@ -14283,7 +14283,7 @@
         <v>2028</v>
       </c>
       <c r="D1071">
-        <v>117911.9798470935</v>
+        <v>126202.8623499254</v>
       </c>
     </row>
     <row r="1072">
@@ -14296,7 +14296,7 @@
         <v>2024</v>
       </c>
       <c r="D1072">
-        <v>39710.67406473596</v>
+        <v>39710.6740647359</v>
       </c>
     </row>
     <row r="1073">
@@ -14322,7 +14322,7 @@
         <v>2026</v>
       </c>
       <c r="D1074">
-        <v>41461.61929925629</v>
+        <v>43349.96137833947</v>
       </c>
     </row>
     <row r="1075">
@@ -14335,7 +14335,7 @@
         <v>2027</v>
       </c>
       <c r="D1075">
-        <v>43373.22351902907</v>
+        <v>45460.43437671974</v>
       </c>
     </row>
     <row r="1076">
@@ -14348,7 +14348,7 @@
         <v>2028</v>
       </c>
       <c r="D1076">
-        <v>45469.85125941517</v>
+        <v>47703.28694083135</v>
       </c>
     </row>
     <row r="1077">
@@ -14361,7 +14361,7 @@
         <v>2024</v>
       </c>
       <c r="D1077">
-        <v>33932.75085085634</v>
+        <v>33932.7508508564</v>
       </c>
     </row>
     <row r="1078">
@@ -14387,7 +14387,7 @@
         <v>2026</v>
       </c>
       <c r="D1079">
-        <v>34556.13195714245</v>
+        <v>35190.97110003585</v>
       </c>
     </row>
     <row r="1080">
@@ -14400,7 +14400,7 @@
         <v>2027</v>
       </c>
       <c r="D1080">
-        <v>35190.97190856466</v>
+        <v>35837.48146128425</v>
       </c>
     </row>
     <row r="1081">
@@ -14413,7 +14413,7 @@
         <v>2028</v>
       </c>
       <c r="D1081">
-        <v>35837.48157497454</v>
+        <v>36495.86952460392</v>
       </c>
     </row>
     <row r="1082">
@@ -14452,7 +14452,7 @@
         <v>2026</v>
       </c>
       <c r="D1084">
-        <v>51779.78256391112</v>
+        <v>56506.53350064596</v>
       </c>
     </row>
     <row r="1085">
@@ -14465,7 +14465,7 @@
         <v>2027</v>
       </c>
       <c r="D1085">
-        <v>56512.97715736867</v>
+        <v>61644.79524157091</v>
       </c>
     </row>
     <row r="1086">
@@ -14478,7 +14478,7 @@
         <v>2028</v>
       </c>
       <c r="D1086">
-        <v>61643.59184659819</v>
+        <v>67246.35188541749</v>
       </c>
     </row>
     <row r="1087">
@@ -14517,7 +14517,7 @@
         <v>2026</v>
       </c>
       <c r="D1089">
-        <v>66799.72406920955</v>
+        <v>80681.2807733276</v>
       </c>
     </row>
     <row r="1090">
@@ -14530,7 +14530,7 @@
         <v>2027</v>
       </c>
       <c r="D1090">
-        <v>80516.43418303903</v>
+        <v>97105.44545148892</v>
       </c>
     </row>
     <row r="1091">
@@ -14543,7 +14543,7 @@
         <v>2028</v>
       </c>
       <c r="D1091">
-        <v>97260.66613174822</v>
+        <v>117434.4046637331</v>
       </c>
     </row>
     <row r="1092">
@@ -14556,7 +14556,7 @@
         <v>2024</v>
       </c>
       <c r="D1092">
-        <v>46409.50269266976</v>
+        <v>46409.50269266968</v>
       </c>
     </row>
     <row r="1093">
@@ -14582,7 +14582,7 @@
         <v>2026</v>
       </c>
       <c r="D1094">
-        <v>47521.18539737445</v>
+        <v>49661.70108353876</v>
       </c>
     </row>
     <row r="1095">
@@ -14595,7 +14595,7 @@
         <v>2027</v>
       </c>
       <c r="D1095">
-        <v>48804.64530995172</v>
+        <v>50272.28217743557</v>
       </c>
     </row>
     <row r="1096">
@@ -14608,7 +14608,7 @@
         <v>2028</v>
       </c>
       <c r="D1096">
-        <v>51025.17123155707</v>
+        <v>53211.22042819299</v>
       </c>
     </row>
     <row r="1097">
@@ -14621,7 +14621,7 @@
         <v>2024</v>
       </c>
       <c r="D1097">
-        <v>69538.04506068175</v>
+        <v>69538.04506068188</v>
       </c>
     </row>
     <row r="1098">
@@ -14647,7 +14647,7 @@
         <v>2026</v>
       </c>
       <c r="D1099">
-        <v>74064.14688812928</v>
+        <v>78899.79471571956</v>
       </c>
     </row>
     <row r="1100">
@@ -14660,7 +14660,7 @@
         <v>2027</v>
       </c>
       <c r="D1100">
-        <v>78901.31521590517</v>
+        <v>84071.95190129246</v>
       </c>
     </row>
     <row r="1101">
@@ -14673,7 +14673,7 @@
         <v>2028</v>
       </c>
       <c r="D1101">
-        <v>84072.11665852286</v>
+        <v>89583.68873363257</v>
       </c>
     </row>
     <row r="1102">
@@ -14686,7 +14686,7 @@
         <v>2024</v>
       </c>
       <c r="D1102">
-        <v>56968.82850535684</v>
+        <v>56968.82850535674</v>
       </c>
     </row>
     <row r="1103">
@@ -14712,7 +14712,7 @@
         <v>2026</v>
       </c>
       <c r="D1104">
-        <v>58014.7179565109</v>
+        <v>59092.87501892307</v>
       </c>
     </row>
     <row r="1105">
@@ -14725,7 +14725,7 @@
         <v>2027</v>
       </c>
       <c r="D1105">
-        <v>59090.87632178199</v>
+        <v>60198.27201613585</v>
       </c>
     </row>
     <row r="1106">
@@ -14738,7 +14738,7 @@
         <v>2028</v>
       </c>
       <c r="D1106">
-        <v>60198.58344799395</v>
+        <v>61325.29845329606</v>
       </c>
     </row>
     <row r="1107">
@@ -14777,7 +14777,7 @@
         <v>2026</v>
       </c>
       <c r="D1109">
-        <v>51634.70299132593</v>
+        <v>53257.22375229534</v>
       </c>
     </row>
     <row r="1110">
@@ -14790,7 +14790,7 @@
         <v>2027</v>
       </c>
       <c r="D1110">
-        <v>53253.35776656603</v>
+        <v>54900.73414106223</v>
       </c>
     </row>
     <row r="1111">
@@ -14803,7 +14803,7 @@
         <v>2028</v>
       </c>
       <c r="D1111">
-        <v>54899.85321182232</v>
+        <v>56592.23872779899</v>
       </c>
     </row>
     <row r="1112">
@@ -14842,7 +14842,7 @@
         <v>2026</v>
       </c>
       <c r="D1114">
-        <v>42385.24653347578</v>
+        <v>43366.01299718161</v>
       </c>
     </row>
     <row r="1115">
@@ -14855,7 +14855,7 @@
         <v>2027</v>
       </c>
       <c r="D1115">
-        <v>43370.31596707128</v>
+        <v>44360.97555935435</v>
       </c>
     </row>
     <row r="1116">
@@ -14868,7 +14868,7 @@
         <v>2028</v>
       </c>
       <c r="D1116">
-        <v>44360.08287779501</v>
+        <v>45376.02648464937</v>
       </c>
     </row>
     <row r="1117">
@@ -14881,7 +14881,7 @@
         <v>2024</v>
       </c>
       <c r="D1117">
-        <v>75056.1464041276</v>
+        <v>75056.14640412734</v>
       </c>
     </row>
     <row r="1118">
@@ -14907,7 +14907,7 @@
         <v>2026</v>
       </c>
       <c r="D1119">
-        <v>82554.87251465123</v>
+        <v>91161.30024043027</v>
       </c>
     </row>
     <row r="1120">
@@ -14920,7 +14920,7 @@
         <v>2027</v>
       </c>
       <c r="D1120">
-        <v>91044.86141621067</v>
+        <v>100675.6511125887</v>
       </c>
     </row>
     <row r="1121">
@@ -14933,7 +14933,7 @@
         <v>2028</v>
       </c>
       <c r="D1121">
-        <v>100717.3946425472</v>
+        <v>111321.3567560242</v>
       </c>
     </row>
     <row r="1122">
@@ -14946,7 +14946,7 @@
         <v>2024</v>
       </c>
       <c r="D1122">
-        <v>63906.2236693072</v>
+        <v>63906.22366930697</v>
       </c>
     </row>
     <row r="1123">
@@ -14972,7 +14972,7 @@
         <v>2026</v>
       </c>
       <c r="D1124">
-        <v>68662.57148704806</v>
+        <v>73986.06486655076</v>
       </c>
     </row>
     <row r="1125">
@@ -14985,7 +14985,7 @@
         <v>2027</v>
       </c>
       <c r="D1125">
-        <v>73870.24268071655</v>
+        <v>79577.72878501558</v>
       </c>
     </row>
     <row r="1126">
@@ -14998,7 +14998,7 @@
         <v>2028</v>
       </c>
       <c r="D1126">
-        <v>79645.4600041613</v>
+        <v>85810.73187571131</v>
       </c>
     </row>
     <row r="1127">
@@ -15011,7 +15011,7 @@
         <v>2024</v>
       </c>
       <c r="D1127">
-        <v>57840.77880185098</v>
+        <v>57840.77880185088</v>
       </c>
     </row>
     <row r="1128">
@@ -15037,7 +15037,7 @@
         <v>2026</v>
       </c>
       <c r="D1129">
-        <v>59199.25703638168</v>
+        <v>60565.39362574646</v>
       </c>
     </row>
     <row r="1130">
@@ -15050,7 +15050,7 @@
         <v>2027</v>
       </c>
       <c r="D1130">
-        <v>60559.96047051399</v>
+        <v>61921.59180901928</v>
       </c>
     </row>
     <row r="1131">
@@ -15063,7 +15063,7 @@
         <v>2028</v>
       </c>
       <c r="D1131">
-        <v>61920.34679219095</v>
+        <v>63304.33977253352</v>
       </c>
     </row>
     <row r="1132">
@@ -15076,7 +15076,7 @@
         <v>2024</v>
       </c>
       <c r="D1132">
-        <v>94078.55609528084</v>
+        <v>94078.556095281</v>
       </c>
     </row>
     <row r="1133">
@@ -15102,7 +15102,7 @@
         <v>2026</v>
       </c>
       <c r="D1134">
-        <v>99141.61804311877</v>
+        <v>104314.603175069</v>
       </c>
     </row>
     <row r="1135">
@@ -15115,7 +15115,7 @@
         <v>2027</v>
       </c>
       <c r="D1135">
-        <v>104230.7020554872</v>
+        <v>109322.5176353756</v>
       </c>
     </row>
     <row r="1136">
@@ -15128,7 +15128,7 @@
         <v>2028</v>
       </c>
       <c r="D1136">
-        <v>109277.0722147978</v>
+        <v>114428.0289666315</v>
       </c>
     </row>
     <row r="1137">
@@ -15141,7 +15141,7 @@
         <v>2024</v>
       </c>
       <c r="D1137">
-        <v>74021.73809453649</v>
+        <v>74021.73809453609</v>
       </c>
     </row>
     <row r="1138">
@@ -15167,7 +15167,7 @@
         <v>2026</v>
       </c>
       <c r="D1139">
-        <v>75166.14893964463</v>
+        <v>76051.43737812393</v>
       </c>
     </row>
     <row r="1140">
@@ -15180,7 +15180,7 @@
         <v>2027</v>
       </c>
       <c r="D1140">
-        <v>76130.22486219474</v>
+        <v>76906.61836969231</v>
       </c>
     </row>
     <row r="1141">
@@ -15193,7 +15193,7 @@
         <v>2028</v>
       </c>
       <c r="D1141">
-        <v>76883.92726298964</v>
+        <v>77702.597195325</v>
       </c>
     </row>
     <row r="1142">
@@ -15206,7 +15206,7 @@
         <v>2024</v>
       </c>
       <c r="D1142">
-        <v>32350.30174907124</v>
+        <v>32350.30174907119</v>
       </c>
     </row>
     <row r="1143">
@@ -15232,7 +15232,7 @@
         <v>2026</v>
       </c>
       <c r="D1144">
-        <v>32450.41396834496</v>
+        <v>31781.86535929296</v>
       </c>
     </row>
     <row r="1145">
@@ -15245,7 +15245,7 @@
         <v>2027</v>
       </c>
       <c r="D1145">
-        <v>32392.96576775777</v>
+        <v>32178.79283212307</v>
       </c>
     </row>
     <row r="1146">
@@ -15258,7 +15258,7 @@
         <v>2028</v>
       </c>
       <c r="D1146">
-        <v>31694.24957830177</v>
+        <v>31130.9439260405</v>
       </c>
     </row>
     <row r="1147">
@@ -15271,7 +15271,7 @@
         <v>2024</v>
       </c>
       <c r="D1147">
-        <v>92360.88692223812</v>
+        <v>92360.88692223794</v>
       </c>
     </row>
     <row r="1148">
@@ -15297,7 +15297,7 @@
         <v>2026</v>
       </c>
       <c r="D1149">
-        <v>96862.58282548373</v>
+        <v>102071.3150714906</v>
       </c>
     </row>
     <row r="1150">
@@ -15310,7 +15310,7 @@
         <v>2027</v>
       </c>
       <c r="D1150">
-        <v>101769.6581994467</v>
+        <v>107121.0711345549</v>
       </c>
     </row>
     <row r="1151">
@@ -15323,7 +15323,7 @@
         <v>2028</v>
       </c>
       <c r="D1151">
-        <v>107317.2069543792</v>
+        <v>113039.3018691986</v>
       </c>
     </row>
     <row r="1152">
@@ -15336,7 +15336,7 @@
         <v>2024</v>
       </c>
       <c r="D1152">
-        <v>44342.0678714024</v>
+        <v>44342.06787140232</v>
       </c>
     </row>
     <row r="1153">
@@ -15362,7 +15362,7 @@
         <v>2026</v>
       </c>
       <c r="D1154">
-        <v>43840.96389337717</v>
+        <v>43378.53708334555</v>
       </c>
     </row>
     <row r="1155">
@@ -15375,7 +15375,7 @@
         <v>2027</v>
       </c>
       <c r="D1155">
-        <v>43373.32636731564</v>
+        <v>42938.20159429874</v>
       </c>
     </row>
     <row r="1156">
@@ -15388,7 +15388,7 @@
         <v>2028</v>
       </c>
       <c r="D1156">
-        <v>42939.01546086195</v>
+        <v>42504.75281120958</v>
       </c>
     </row>
     <row r="1157">
@@ -15401,7 +15401,7 @@
         <v>2024</v>
       </c>
       <c r="D1157">
-        <v>40686.12705130325</v>
+        <v>40686.12705130318</v>
       </c>
     </row>
     <row r="1158">
@@ -15427,7 +15427,7 @@
         <v>2026</v>
       </c>
       <c r="D1159">
-        <v>43320.25307700888</v>
+        <v>46693.19099381713</v>
       </c>
     </row>
     <row r="1160">
@@ -15440,7 +15440,7 @@
         <v>2027</v>
       </c>
       <c r="D1160">
-        <v>46199.53221734236</v>
+        <v>49349.88333325471</v>
       </c>
     </row>
     <row r="1161">
@@ -15453,7 +15453,7 @@
         <v>2028</v>
       </c>
       <c r="D1161">
-        <v>49807.27767079512</v>
+        <v>53621.47180516581</v>
       </c>
     </row>
     <row r="1162">
@@ -15466,7 +15466,7 @@
         <v>2024</v>
       </c>
       <c r="D1162">
-        <v>89849.10294392925</v>
+        <v>89849.10294392941</v>
       </c>
     </row>
     <row r="1163">
@@ -15492,7 +15492,7 @@
         <v>2026</v>
       </c>
       <c r="D1164">
-        <v>95303.55503079036</v>
+        <v>101089.1374838809</v>
       </c>
     </row>
     <row r="1165">
@@ -15505,7 +15505,7 @@
         <v>2027</v>
       </c>
       <c r="D1165">
-        <v>101089.1374656593</v>
+        <v>107225.9530835279</v>
       </c>
     </row>
     <row r="1166">
@@ -15518,7 +15518,7 @@
         <v>2028</v>
       </c>
       <c r="D1166">
-        <v>107225.9530835719</v>
+        <v>113735.3161858606</v>
       </c>
     </row>
     <row r="1167">
@@ -15531,7 +15531,7 @@
         <v>2024</v>
       </c>
       <c r="D1167">
-        <v>67150.83142379597</v>
+        <v>67150.83142379609</v>
       </c>
     </row>
     <row r="1168">
@@ -15557,7 +15557,7 @@
         <v>2026</v>
       </c>
       <c r="D1169">
-        <v>70806.80819537902</v>
+        <v>74655.39958668183</v>
       </c>
     </row>
     <row r="1170">
@@ -15570,7 +15570,7 @@
         <v>2027</v>
       </c>
       <c r="D1170">
-        <v>74656.56552259157</v>
+        <v>78710.08137133424</v>
       </c>
     </row>
     <row r="1171">
@@ -15583,7 +15583,7 @@
         <v>2028</v>
       </c>
       <c r="D1171">
-        <v>78709.8585465419</v>
+        <v>82984.27613082627</v>
       </c>
     </row>
     <row r="1172">
@@ -15596,7 +15596,7 @@
         <v>2024</v>
       </c>
       <c r="D1172">
-        <v>73296.3562634827</v>
+        <v>73296.35626348256</v>
       </c>
     </row>
     <row r="1173">
@@ -15622,7 +15622,7 @@
         <v>2026</v>
       </c>
       <c r="D1174">
-        <v>74905.78181641201</v>
+        <v>76826.30468074404</v>
       </c>
     </row>
     <row r="1175">
@@ -15635,7 +15635,7 @@
         <v>2027</v>
       </c>
       <c r="D1175">
-        <v>76597.90690816836</v>
+        <v>78376.7171345479</v>
       </c>
     </row>
     <row r="1176">
@@ -15648,7 +15648,7 @@
         <v>2028</v>
       </c>
       <c r="D1176">
-        <v>78570.17235820202</v>
+        <v>80551.95857302861</v>
       </c>
     </row>
     <row r="1177">
@@ -15661,7 +15661,7 @@
         <v>2024</v>
       </c>
       <c r="D1177">
-        <v>46989.43765873329</v>
+        <v>46989.43765873337</v>
       </c>
     </row>
     <row r="1178">
@@ -15687,7 +15687,7 @@
         <v>2026</v>
       </c>
       <c r="D1179">
-        <v>49202.43440932662</v>
+        <v>51519.09104968037</v>
       </c>
     </row>
     <row r="1180">
@@ -15700,7 +15700,7 @@
         <v>2027</v>
       </c>
       <c r="D1180">
-        <v>51518.90669519111</v>
+        <v>53943.65744151264</v>
       </c>
     </row>
     <row r="1181">
@@ -15713,7 +15713,7 @@
         <v>2028</v>
       </c>
       <c r="D1181">
-        <v>53943.59418440655</v>
+        <v>56482.12889498018</v>
       </c>
     </row>
     <row r="1182">
@@ -15726,7 +15726,7 @@
         <v>2024</v>
       </c>
       <c r="D1182">
-        <v>30263.85205224957</v>
+        <v>30263.85205224947</v>
       </c>
     </row>
     <row r="1183">
@@ -15752,7 +15752,7 @@
         <v>2026</v>
       </c>
       <c r="D1184">
-        <v>30939.57180311884</v>
+        <v>31630.64138927662</v>
       </c>
     </row>
     <row r="1185">
@@ -15765,7 +15765,7 @@
         <v>2027</v>
       </c>
       <c r="D1185">
-        <v>31630.65165803092</v>
+        <v>32337.44676476874</v>
       </c>
     </row>
     <row r="1186">
@@ -15778,7 +15778,7 @@
         <v>2028</v>
       </c>
       <c r="D1186">
-        <v>32337.44717525606</v>
+        <v>33060.04738307645</v>
       </c>
     </row>
     <row r="1187">
@@ -15817,7 +15817,7 @@
         <v>2026</v>
       </c>
       <c r="D1189">
-        <v>64878.56345395649</v>
+        <v>68566.19086650237</v>
       </c>
     </row>
     <row r="1190">
@@ -15830,7 +15830,7 @@
         <v>2027</v>
       </c>
       <c r="D1190">
-        <v>68261.22913598995</v>
+        <v>72245.38376421059</v>
       </c>
     </row>
     <row r="1191">
@@ -15843,7 +15843,7 @@
         <v>2028</v>
       </c>
       <c r="D1191">
-        <v>72384.09036023471</v>
+        <v>76561.28914522879</v>
       </c>
     </row>
     <row r="1192">
@@ -15856,7 +15856,7 @@
         <v>2024</v>
       </c>
       <c r="D1192">
-        <v>80375.66456497551</v>
+        <v>80375.66456497565</v>
       </c>
     </row>
     <row r="1193">
@@ -15882,7 +15882,7 @@
         <v>2026</v>
       </c>
       <c r="D1194">
-        <v>83612.16765788765</v>
+        <v>89241.22059931362</v>
       </c>
     </row>
     <row r="1195">
@@ -15895,7 +15895,7 @@
         <v>2027</v>
       </c>
       <c r="D1195">
-        <v>87070.44147848543</v>
+        <v>90767.08079200165</v>
       </c>
     </row>
     <row r="1196">
@@ -15908,7 +15908,7 @@
         <v>2028</v>
       </c>
       <c r="D1196">
-        <v>92936.31361358914</v>
+        <v>99097.44465032432</v>
       </c>
     </row>
     <row r="1197">
@@ -15921,7 +15921,7 @@
         <v>2024</v>
       </c>
       <c r="D1197">
-        <v>95102.33471061055</v>
+        <v>95102.33471061004</v>
       </c>
     </row>
     <row r="1198">
@@ -15947,7 +15947,7 @@
         <v>2026</v>
       </c>
       <c r="D1199">
-        <v>99644.6234427484</v>
+        <v>104372.706342604</v>
       </c>
     </row>
     <row r="1200">
@@ -15960,7 +15960,7 @@
         <v>2027</v>
       </c>
       <c r="D1200">
-        <v>104387.838525225</v>
+        <v>109340.053772864</v>
       </c>
     </row>
     <row r="1201">
@@ -15973,7 +15973,7 @@
         <v>2028</v>
       </c>
       <c r="D1201">
-        <v>109332.3544566975</v>
+        <v>114519.6136499634</v>
       </c>
     </row>
     <row r="1202">
@@ -15986,7 +15986,7 @@
         <v>2024</v>
       </c>
       <c r="D1202">
-        <v>48831.36641397745</v>
+        <v>48831.36641397736</v>
       </c>
     </row>
     <row r="1203">
@@ -16012,7 +16012,7 @@
         <v>2026</v>
       </c>
       <c r="D1204">
-        <v>50152.06215320399</v>
+        <v>51470.27874475882</v>
       </c>
     </row>
     <row r="1205">
@@ -16025,7 +16025,7 @@
         <v>2027</v>
       </c>
       <c r="D1205">
-        <v>51462.40791873691</v>
+        <v>52759.75870436143</v>
       </c>
     </row>
     <row r="1206">
@@ -16038,7 +16038,7 @@
         <v>2028</v>
       </c>
       <c r="D1206">
-        <v>52758.09545113577</v>
+        <v>54076.42927537979</v>
       </c>
     </row>
     <row r="1207">
@@ -16051,7 +16051,7 @@
         <v>2024</v>
       </c>
       <c r="D1207">
-        <v>84451.67483675075</v>
+        <v>84451.67483675061</v>
       </c>
     </row>
     <row r="1208">
@@ -16077,7 +16077,7 @@
         <v>2026</v>
       </c>
       <c r="D1209">
-        <v>96079.0891448352</v>
+        <v>109312.8907168673</v>
       </c>
     </row>
     <row r="1210">
@@ -16090,7 +16090,7 @@
         <v>2027</v>
       </c>
       <c r="D1210">
-        <v>109312.7008880456</v>
+        <v>124375.1192462983</v>
       </c>
     </row>
     <row r="1211">
@@ -16103,7 +16103,7 @@
         <v>2028</v>
       </c>
       <c r="D1211">
-        <v>124375.1266871421</v>
+        <v>141512.7983758608</v>
       </c>
     </row>
     <row r="1212">
@@ -16116,7 +16116,7 @@
         <v>2024</v>
       </c>
       <c r="D1212">
-        <v>102410.1618392527</v>
+        <v>102410.1618392524</v>
       </c>
     </row>
     <row r="1213">
@@ -16142,7 +16142,7 @@
         <v>2026</v>
       </c>
       <c r="D1214">
-        <v>109414.3879922502</v>
+        <v>117103.986876837</v>
       </c>
     </row>
     <row r="1215">
@@ -16155,7 +16155,7 @@
         <v>2027</v>
       </c>
       <c r="D1215">
-        <v>117023.9572092939</v>
+        <v>125297.9846294559</v>
       </c>
     </row>
     <row r="1216">
@@ -16168,7 +16168,7 @@
         <v>2028</v>
       </c>
       <c r="D1216">
-        <v>125331.1962912794</v>
+        <v>134171.9675261125</v>
       </c>
     </row>
     <row r="1217">
@@ -16181,7 +16181,7 @@
         <v>2024</v>
       </c>
       <c r="D1217">
-        <v>108968.6397859805</v>
+        <v>108968.6397859801</v>
       </c>
     </row>
     <row r="1218">
@@ -16207,7 +16207,7 @@
         <v>2026</v>
       </c>
       <c r="D1219">
-        <v>112844.8015893635</v>
+        <v>116794.4855943698</v>
       </c>
     </row>
     <row r="1220">
@@ -16220,7 +16220,7 @@
         <v>2027</v>
       </c>
       <c r="D1220">
-        <v>116777.1667056007</v>
+        <v>120762.1009517825</v>
       </c>
     </row>
     <row r="1221">
@@ -16233,7 +16233,7 @@
         <v>2028</v>
       </c>
       <c r="D1221">
-        <v>120757.280137178</v>
+        <v>124849.5466776685</v>
       </c>
     </row>
     <row r="1222">
@@ -16272,7 +16272,7 @@
         <v>2026</v>
       </c>
       <c r="D1224">
-        <v>142625.6959658147</v>
+        <v>153114.3045758169</v>
       </c>
     </row>
     <row r="1225">
@@ -16285,7 +16285,7 @@
         <v>2027</v>
       </c>
       <c r="D1225">
-        <v>153653.0775486037</v>
+        <v>164795.5370097047</v>
       </c>
     </row>
     <row r="1226">
@@ -16298,7 +16298,7 @@
         <v>2028</v>
       </c>
       <c r="D1226">
-        <v>164540.8716875754</v>
+        <v>176546.929633437</v>
       </c>
     </row>
     <row r="1227">
@@ -16311,7 +16311,7 @@
         <v>2024</v>
       </c>
       <c r="D1227">
-        <v>94541.03030345074</v>
+        <v>94541.0303034504</v>
       </c>
     </row>
     <row r="1228">
@@ -16337,7 +16337,7 @@
         <v>2026</v>
       </c>
       <c r="D1229">
-        <v>98539.38593081669</v>
+        <v>102706.8457073268</v>
       </c>
     </row>
     <row r="1230">
@@ -16350,7 +16350,7 @@
         <v>2027</v>
       </c>
       <c r="D1230">
-        <v>102706.8450561424</v>
+        <v>107050.5597838476</v>
       </c>
     </row>
     <row r="1231">
@@ -16363,7 +16363,7 @@
         <v>2028</v>
       </c>
       <c r="D1231">
-        <v>107050.5598804004</v>
+        <v>111577.9800472026</v>
       </c>
     </row>
     <row r="1232">
@@ -16376,7 +16376,7 @@
         <v>2024</v>
       </c>
       <c r="D1232">
-        <v>123855.6937608205</v>
+        <v>123855.6937608201</v>
       </c>
     </row>
     <row r="1233">
@@ -16402,7 +16402,7 @@
         <v>2026</v>
       </c>
       <c r="D1234">
-        <v>129257.1032781289</v>
+        <v>133345.0445493021</v>
       </c>
     </row>
     <row r="1235">
@@ -16415,7 +16415,7 @@
         <v>2027</v>
       </c>
       <c r="D1235">
-        <v>134808.4016324184</v>
+        <v>140508.8236872739</v>
       </c>
     </row>
     <row r="1236">
@@ -16428,7 +16428,7 @@
         <v>2028</v>
       </c>
       <c r="D1236">
-        <v>139067.0510640382</v>
+        <v>143546.3842531655</v>
       </c>
     </row>
     <row r="1237">
@@ -16467,7 +16467,7 @@
         <v>2026</v>
       </c>
       <c r="D1239">
-        <v>77477.76956074612</v>
+        <v>80243.12097678454</v>
       </c>
     </row>
     <row r="1240">
@@ -16480,7 +16480,7 @@
         <v>2027</v>
       </c>
       <c r="D1240">
-        <v>80251.77034011351</v>
+        <v>83114.97250493447</v>
       </c>
     </row>
     <row r="1241">
@@ -16493,7 +16493,7 @@
         <v>2028</v>
       </c>
       <c r="D1241">
-        <v>83110.7656296947</v>
+        <v>86076.53416954164</v>
       </c>
     </row>
     <row r="1242">
@@ -16506,7 +16506,7 @@
         <v>2024</v>
       </c>
       <c r="D1242">
-        <v>86935.91878404436</v>
+        <v>86935.91878404406</v>
       </c>
     </row>
     <row r="1243">
@@ -16532,7 +16532,7 @@
         <v>2026</v>
       </c>
       <c r="D1244">
-        <v>90777.475996352</v>
+        <v>94816.98990489841</v>
       </c>
     </row>
     <row r="1245">
@@ -16545,7 +16545,7 @@
         <v>2027</v>
       </c>
       <c r="D1245">
-        <v>94814.19074914305</v>
+        <v>99056.95331281857</v>
       </c>
     </row>
     <row r="1246">
@@ -16558,7 +16558,7 @@
         <v>2028</v>
       </c>
       <c r="D1246">
-        <v>99057.2435032896</v>
+        <v>103487.4261022655</v>
       </c>
     </row>
     <row r="1247">
@@ -16571,7 +16571,7 @@
         <v>2024</v>
       </c>
       <c r="D1247">
-        <v>132281.3526487503</v>
+        <v>132281.3526487501</v>
       </c>
     </row>
     <row r="1248">
@@ -16597,7 +16597,7 @@
         <v>2026</v>
       </c>
       <c r="D1249">
-        <v>142401.5760027133</v>
+        <v>153296.050021401</v>
       </c>
     </row>
     <row r="1250">
@@ -16610,7 +16610,7 @@
         <v>2027</v>
       </c>
       <c r="D1250">
-        <v>153296.0500214056</v>
+        <v>165024.0089822848</v>
       </c>
     </row>
     <row r="1251">
@@ -16623,7 +16623,7 @@
         <v>2028</v>
       </c>
       <c r="D1251">
-        <v>165024.0089822851</v>
+        <v>177649.2188597381</v>
       </c>
     </row>
     <row r="1252">
@@ -16662,7 +16662,7 @@
         <v>2026</v>
       </c>
       <c r="D1254">
-        <v>142548.3051108558</v>
+        <v>145567.748380413</v>
       </c>
     </row>
     <row r="1255">
@@ -16675,7 +16675,7 @@
         <v>2027</v>
       </c>
       <c r="D1255">
-        <v>145511.330383111</v>
+        <v>148576.2519410279</v>
       </c>
     </row>
     <row r="1256">
@@ -16688,7 +16688,7 @@
         <v>2028</v>
       </c>
       <c r="D1256">
-        <v>148610.1369245785</v>
+        <v>151750.7129361736</v>
       </c>
     </row>
     <row r="1257">
@@ -16701,7 +16701,7 @@
         <v>2024</v>
       </c>
       <c r="D1257">
-        <v>92647.36091496449</v>
+        <v>92647.36091496417</v>
       </c>
     </row>
     <row r="1258">
@@ -16727,7 +16727,7 @@
         <v>2026</v>
       </c>
       <c r="D1259">
-        <v>95326.55973108993</v>
+        <v>100526.7000137702</v>
       </c>
     </row>
     <row r="1260">
@@ -16740,7 +16740,7 @@
         <v>2027</v>
       </c>
       <c r="D1260">
-        <v>98242.44750677262</v>
+        <v>101411.8752485336</v>
       </c>
     </row>
     <row r="1261">
@@ -16753,7 +16753,7 @@
         <v>2028</v>
       </c>
       <c r="D1261">
-        <v>103612.7278953836</v>
+        <v>109111.1376273451</v>
       </c>
     </row>
     <row r="1262">
@@ -16766,7 +16766,7 @@
         <v>2024</v>
       </c>
       <c r="D1262">
-        <v>93350.47269720194</v>
+        <v>93350.47269720143</v>
       </c>
     </row>
     <row r="1263">
@@ -16792,7 +16792,7 @@
         <v>2026</v>
       </c>
       <c r="D1264">
-        <v>91169.83959089189</v>
+        <v>88890.43331625599</v>
       </c>
     </row>
     <row r="1265">
@@ -16805,7 +16805,7 @@
         <v>2027</v>
       </c>
       <c r="D1265">
-        <v>88932.41442809739</v>
+        <v>86644.93870425144</v>
       </c>
     </row>
     <row r="1266">
@@ -16818,7 +16818,7 @@
         <v>2028</v>
       </c>
       <c r="D1266">
-        <v>86633.46057339208</v>
+        <v>84422.60828851108</v>
       </c>
     </row>
     <row r="1267">
@@ -16831,7 +16831,7 @@
         <v>2024</v>
       </c>
       <c r="D1267">
-        <v>121916.3913682328</v>
+        <v>121916.3913682326</v>
       </c>
     </row>
     <row r="1268">
@@ -16857,7 +16857,7 @@
         <v>2026</v>
       </c>
       <c r="D1269">
-        <v>137129.1210197722</v>
+        <v>154149.5898571802</v>
       </c>
     </row>
     <row r="1270">
@@ -16870,7 +16870,7 @@
         <v>2027</v>
       </c>
       <c r="D1270">
-        <v>154161.8044975024</v>
+        <v>173222.1314745879</v>
       </c>
     </row>
     <row r="1271">
@@ -16883,7 +16883,7 @@
         <v>2028</v>
       </c>
       <c r="D1271">
-        <v>173220.2786339367</v>
+        <v>194648.2245698964</v>
       </c>
     </row>
     <row r="1272">
@@ -16896,7 +16896,7 @@
         <v>2024</v>
       </c>
       <c r="D1272">
-        <v>60724.33634642434</v>
+        <v>60724.33634642424</v>
       </c>
     </row>
     <row r="1273">
@@ -16922,7 +16922,7 @@
         <v>2026</v>
       </c>
       <c r="D1274">
-        <v>61181.62406121305</v>
+        <v>61606.0582808765</v>
       </c>
     </row>
     <row r="1275">
@@ -16935,7 +16935,7 @@
         <v>2027</v>
       </c>
       <c r="D1275">
-        <v>61613.58984827412</v>
+        <v>62019.6503460591</v>
       </c>
     </row>
     <row r="1276">
@@ -16948,7 +16948,7 @@
         <v>2028</v>
       </c>
       <c r="D1276">
-        <v>62018.07682079166</v>
+        <v>62431.26691337946</v>
       </c>
     </row>
     <row r="1277">
@@ -16961,7 +16961,7 @@
         <v>2024</v>
       </c>
       <c r="D1277">
-        <v>56083.57870412775</v>
+        <v>56083.57870412765</v>
       </c>
     </row>
     <row r="1278">
@@ -16987,7 +16987,7 @@
         <v>2026</v>
       </c>
       <c r="D1279">
-        <v>61360.02017732526</v>
+        <v>67088.39997150915</v>
       </c>
     </row>
     <row r="1280">
@@ -17000,7 +17000,7 @@
         <v>2027</v>
       </c>
       <c r="D1280">
-        <v>67078.68252906993</v>
+        <v>73271.11653396912</v>
       </c>
     </row>
     <row r="1281">
@@ -17013,7 +17013,7 @@
         <v>2028</v>
       </c>
       <c r="D1281">
-        <v>73268.79679737381</v>
+        <v>80016.01808190928</v>
       </c>
     </row>
     <row r="1282">
@@ -17026,7 +17026,7 @@
         <v>2024</v>
       </c>
       <c r="D1282">
-        <v>46182.42363061028</v>
+        <v>46182.42363061003</v>
       </c>
     </row>
     <row r="1283">
@@ -17052,7 +17052,7 @@
         <v>2026</v>
       </c>
       <c r="D1284">
-        <v>47316.79023639853</v>
+        <v>48479.01998076468</v>
       </c>
     </row>
     <row r="1285">
@@ -17065,7 +17065,7 @@
         <v>2027</v>
       </c>
       <c r="D1285">
-        <v>48479.01998043571</v>
+        <v>49669.79725722254</v>
       </c>
     </row>
     <row r="1286">
@@ -17078,7 +17078,7 @@
         <v>2028</v>
       </c>
       <c r="D1286">
-        <v>49669.79725720683</v>
+        <v>50889.82327922764</v>
       </c>
     </row>
     <row r="1287">
@@ -17091,7 +17091,7 @@
         <v>2024</v>
       </c>
       <c r="D1287">
-        <v>71573.08919703495</v>
+        <v>71573.08919703482</v>
       </c>
     </row>
     <row r="1288">
@@ -17117,7 +17117,7 @@
         <v>2026</v>
       </c>
       <c r="D1289">
-        <v>75683.0886780361</v>
+        <v>81139.33837763913</v>
       </c>
     </row>
     <row r="1290">
@@ -17130,7 +17130,7 @@
         <v>2027</v>
       </c>
       <c r="D1290">
-        <v>80118.52792854738</v>
+        <v>84908.68265124182</v>
       </c>
     </row>
     <row r="1291">
@@ -17143,7 +17143,7 @@
         <v>2028</v>
       </c>
       <c r="D1291">
-        <v>85902.31982010005</v>
+        <v>92009.16973700454</v>
       </c>
     </row>
     <row r="1292">
@@ -17156,7 +17156,7 @@
         <v>2024</v>
       </c>
       <c r="D1292">
-        <v>64106.55966497779</v>
+        <v>64106.5596649779</v>
       </c>
     </row>
     <row r="1293">
@@ -17182,7 +17182,7 @@
         <v>2026</v>
       </c>
       <c r="D1294">
-        <v>70725.30311880889</v>
+        <v>78084.76249856442</v>
       </c>
     </row>
     <row r="1295">
@@ -17195,7 +17195,7 @@
         <v>2027</v>
       </c>
       <c r="D1295">
-        <v>78097.95980957945</v>
+        <v>86317.14842776222</v>
       </c>
     </row>
     <row r="1296">
@@ -17208,7 +17208,7 @@
         <v>2028</v>
       </c>
       <c r="D1296">
-        <v>86320.50339141952</v>
+        <v>95428.59170882498</v>
       </c>
     </row>
     <row r="1297">
@@ -17221,7 +17221,7 @@
         <v>2024</v>
       </c>
       <c r="D1297">
-        <v>65467.07634108393</v>
+        <v>65467.0763410837</v>
       </c>
     </row>
     <row r="1298">
@@ -17247,7 +17247,7 @@
         <v>2026</v>
       </c>
       <c r="D1299">
-        <v>66857.27876668732</v>
+        <v>68267.96027167761</v>
       </c>
     </row>
     <row r="1300">
@@ -17260,7 +17260,7 @@
         <v>2027</v>
       </c>
       <c r="D1300">
-        <v>68271.60131201305</v>
+        <v>69710.32809719644</v>
       </c>
     </row>
     <row r="1301">
@@ -17273,7 +17273,7 @@
         <v>2028</v>
       </c>
       <c r="D1301">
-        <v>69708.83094946462</v>
+        <v>71178.58407995047</v>
       </c>
     </row>
     <row r="1302">
@@ -17286,7 +17286,7 @@
         <v>2024</v>
       </c>
       <c r="D1302">
-        <v>76339.37528869073</v>
+        <v>76339.37528869045</v>
       </c>
     </row>
     <row r="1303">
@@ -17312,7 +17312,7 @@
         <v>2026</v>
       </c>
       <c r="D1304">
-        <v>80636.46135904481</v>
+        <v>84921.30518332</v>
       </c>
     </row>
     <row r="1305">
@@ -17325,7 +17325,7 @@
         <v>2027</v>
       </c>
       <c r="D1305">
-        <v>85035.98808961459</v>
+        <v>89528.74691800112</v>
       </c>
     </row>
     <row r="1306">
@@ -17338,7 +17338,7 @@
         <v>2028</v>
       </c>
       <c r="D1306">
-        <v>89474.19230919826</v>
+        <v>94213.72901587623</v>
       </c>
     </row>
     <row r="1307">
@@ -17351,7 +17351,7 @@
         <v>2024</v>
       </c>
       <c r="D1307">
-        <v>86897.702911951</v>
+        <v>86897.70291195114</v>
       </c>
     </row>
     <row r="1308">
@@ -17377,7 +17377,7 @@
         <v>2026</v>
       </c>
       <c r="D1309">
-        <v>92493.56905907982</v>
+        <v>98700.09098884813</v>
       </c>
     </row>
     <row r="1310">
@@ -17390,7 +17390,7 @@
         <v>2027</v>
       </c>
       <c r="D1310">
-        <v>98603.30801965883</v>
+        <v>105280.5483234249</v>
       </c>
     </row>
     <row r="1311">
@@ -17403,7 +17403,7 @@
         <v>2028</v>
       </c>
       <c r="D1311">
-        <v>105320.4615895967</v>
+        <v>112427.5043271145</v>
       </c>
     </row>
     <row r="1312">
@@ -17442,7 +17442,7 @@
         <v>2026</v>
       </c>
       <c r="D1314">
-        <v>83343.76174334601</v>
+        <v>88419.55646323544</v>
       </c>
     </row>
     <row r="1315">
@@ -17455,7 +17455,7 @@
         <v>2027</v>
       </c>
       <c r="D1315">
-        <v>88419.55646335636</v>
+        <v>93804.47680161399</v>
       </c>
     </row>
     <row r="1316">
@@ -17468,7 +17468,7 @@
         <v>2028</v>
       </c>
       <c r="D1316">
-        <v>93804.476801606</v>
+        <v>99517.34910229973</v>
       </c>
     </row>
     <row r="1317">
@@ -17481,7 +17481,7 @@
         <v>2024</v>
       </c>
       <c r="D1317">
-        <v>112297.3869603245</v>
+        <v>112297.3869603249</v>
       </c>
     </row>
     <row r="1318">
@@ -17507,7 +17507,7 @@
         <v>2026</v>
       </c>
       <c r="D1319">
-        <v>122959.8325989132</v>
+        <v>137213.0813411593</v>
       </c>
     </row>
     <row r="1320">
@@ -17520,7 +17520,7 @@
         <v>2027</v>
       </c>
       <c r="D1320">
-        <v>135116.5194895776</v>
+        <v>149006.4986654504</v>
       </c>
     </row>
     <row r="1321">
@@ -17533,7 +17533,7 @@
         <v>2028</v>
       </c>
       <c r="D1321">
-        <v>150880.4288191198</v>
+        <v>167995.6366940554</v>
       </c>
     </row>
   </sheetData>
